--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2470,6 +2470,40 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>emp_travel_recalling</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>{@Peer} がその場所を返すのを待っています…</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Waiting for {@Peer} to hand the zone back…</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>emp_travel_recalled</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ホストが来ます。合流します…</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>The host is coming, rejoining them…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2504,6 +2504,40 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>emp_travel_zone_closed</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>この場所の主がいなくなりました。ホストに合流します</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>The owner of this place is gone, rejoining the host</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>emp_travel_handoff</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>この場所の主はあなたになりました</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>You are now the owner of this place</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2538,6 +2538,57 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_independent_travel</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>単独行動を許可</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Independent travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_player_shipping</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>出荷はプレイヤーごと</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Shipping per player</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_combat_time</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>戦闘は各プレイヤーの時間で進行</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Combat on each player's time</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2589,6 +2589,108 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>emp_ui_bot_add</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Add a bot player</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Add a bot player</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>emp_ui_bot_stop</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Stop the bots ({0})</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Stop the bots ({0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>emp_ui_bot_all_actions</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bots also take quests and sell</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Bots also take quests and sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>emp_ui_bot_need_local</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Bots need a local server: disconnect, then add a bot to start one</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Bots need a local server: disconnect, then add a bot to start one</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>emp_ui_bot_no_launcher</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>No second copy of the game found (see _tools/make_lab.py)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>No second copy of the game found (see _tools/make_lab.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>emp_ui_bot_started</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Bot player starting, it joins in about a minute</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Bot player starting, it joins in about a minute</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2691,6 +2691,23 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_personal_quests</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Random quests and fame per player</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Random quests and fame per player</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -2631,12 +2631,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bots also take quests and sell</t>
+          <t>Bots do everything (quests, selling, digging, chests)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Bots also take quests and sell</t>
+          <t>Bots do everything (quests, selling, digging, chests)</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2708,6 +2708,57 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_choose_chara</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Players choose their character when joining</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Players choose their character when joining</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_pick</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Who do you want to play?</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Who do you want to play?</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_new</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>A new character</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>A new character</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2759,6 +2759,414 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_player_trade</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Trade window between players</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Trade window between players</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>emp_act_trade</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>emp_ui_trade</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>emp_trade_invite</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>{0} wants to trade with you</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>{0} wants to trade with you</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>emp_trade_you_offer</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>You offer</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>You offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>emp_trade_they_offer</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>{0} offers</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>{0} offers</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>emp_trade_nothing</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>(nothing yet)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>(nothing yet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>emp_trade_add</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Add an item</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Add an item</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>emp_trade_gold</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Gold: {0}</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Gold: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>emp_trade_clear</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Take everything back</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Take everything back</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>emp_trade_confirm</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>emp_trade_cancel</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>emp_trade_you_ready</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>You confirmed</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>You confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>emp_trade_you_wait</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>You have not confirmed</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>You have not confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>emp_trade_they_ready</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>the other player confirmed</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>the other player confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>emp_trade_they_wait</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>the other player has not confirmed</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>the other player has not confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>emp_trade_pick</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Which item?</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Which item?</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>emp_trade_howmany</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>How many?</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>How many?</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>emp_trade_howmuch</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>How much gold?</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>How much gold?</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>emp_trade_done</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Trade done</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Trade done</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>emp_trade_cancelled</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Trade cancelled</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Trade cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>emp_trade_invalid</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Trade cancelled: something offered is not there anymore</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Trade cancelled: something offered is not there anymore</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>emp_trade_far</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Trade cancelled: too far from each other</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Trade cancelled: too far from each other</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>emp_trade_busy</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>That player is already trading</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>That player is already trading</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Random quests and fame per player</t>
+          <t>ランダムクエスト・名声・カルマはプレイヤーごと</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Random quests and fame per player</t>
+          <t>Random quests, fame and karma per player</t>
         </is>
       </c>
     </row>
@@ -3164,6 +3164,244 @@
       <c r="D160" t="inlineStr">
         <is>
           <t>That player is already trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_note_live</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ホストのルールです。変更はすぐに全員に適用されます。</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>These rules are the host's. A change applies at once, for everyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_players</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>プレイヤーと移動</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Players and travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_own</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>プレイヤーごとのもの</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>To each player its own</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_time</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>時間と戦闘</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Time and combat</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_checks</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>参加時の検証（上級者向け）</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Joining checks (advanced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_choose_chara</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>参加時に、この世界の自分のキャラクターから選ぶか、新しく作る。</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>A joining player picks one of its characters in this world, or makes a new one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_independent_travel</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>誰でも好きな場所へ、一人でも一緒でも行ける。オフ：全員がホストについて行く。</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Everyone goes where they want, alone or together. Off: everyone follows the host.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_personal_quests</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>各自ランダムクエスト5件、報酬・名声・カルマも各自。メインクエストは共有。</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>5 random quests each, with their reward, fame and karma. Story quests stay shared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_player_shipping</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>出荷箱の売上はアイテムを入れたプレイヤーへ。オフ：すべてホストへ。</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Shipping box money goes to the player who put the item in. Off: all to the host.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_player_trade</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>他のプレイヤーをクリックしてアイテムと金貨を交換。双方が確認する。</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Click another player to trade items and gold. Both confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_combat_time</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>モンスターは戦っている相手が動いた時に動く。誰も待たない。ターン制より優先。</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>A monster acts when the player it fights acts: nobody waits. Takes over turn-based.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_turn_combat</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>戦闘中、プレイヤーは順番に行動する。</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>In a fight, players act in turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_shared_speed</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>全プレイヤーが平均速度を共有。オフ：各自の速度。</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>One speed for all players, the average. Off: each keeps its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_validation</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>参加するプレイヤーのゲームがホストと一致すべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9510" yWindow="2685" windowWidth="31695" windowHeight="18195" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="General" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>戦闘中、プレイヤーは順番に行動する。</t>
+          <t>戦闘中、プレイヤーは順番に行動する。「戦闘は各プレイヤーの時間で進行」がオンの間は無効。</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>In a fight, players act in turn.</t>
+          <t>In a fight, players act in turn. No effect while "Combat on each player's time" is on.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9510" yWindow="2685" windowWidth="31695" windowHeight="18195" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3405,6 +3405,40 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_player_clock</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>各プレイヤーは自分の時計で動く</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Each player on its own clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_player_clock</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ゲストもホストと同じように滑らかに動く（通信の速さに左右されない）。上のオプションが必要。</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>A guest walks and acts as smoothly as the host, not at the pace of the network. Needs the option above.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9510" yWindow="2685" windowWidth="31695" windowHeight="18195" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="General" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3439,6 +3439,40 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_step_pace</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>各プレイヤーはソロと同じ歩調で動く</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Every player walks at the pace of a solo game</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_step_pace</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>歩く速さが他のプレイヤーの速度に左右されなくなります。戦闘では速度は今まで通り有効。「戦闘は各プレイヤーの時間で」が必要。</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>The length of a step no longer depends on the other players' speed. Speed still counts in a fight. Needs combat on each player's time.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3473,6 +3473,142 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_import_chara</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>自分のセーブのキャラクターで参加できる</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Players can bring a character from their own saves</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_import_chara</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>キャラクター本人、装備、持ち物、所持金、名声、カルマ。仲間、拠点、クエスト、銀行は含まれません。セーブは読むだけで変更しません。</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>The character, its equipment, bag and gold, its fame and karma. Not its companions, base, quests or bank. The save is only read, never changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_import</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>自分のセーブのキャラクター…</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>A character from one of my saves…</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_import_pick</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>どのセーブのキャラクターで参加しますか？（セーブは変更されません）</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Which save to bring the character of? (the save is not changed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_import_back</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>戻る</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_import_none</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>読み込めるセーブがありません。</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>No save this game can read was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_import_fail</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>このキャラクターは読み込めませんでした。</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>That character could not be brought.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_import_twice</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>このセーブのキャラクターはすでにこの世界にいます。</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>The character of that save is already in this world.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:D188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -3609,6 +3608,40 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_world_time</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>世界の時間は全員で一つ</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>One date for the whole world</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_world_time</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>一人で別のマップにいるプレイヤーの時間も世界の時間になります。一番進んだ日付が世界の日付。オフ：ホストの日付だけ。</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Time passed by a player alone on another map counts for everyone: the most advanced date is the world's. Off: only the host's date counts.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D188"/>
+  <dimension ref="A1:D190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3642,6 +3642,40 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_world_keeper</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>世界の出来事は一度だけ起きる</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>What time does to the world happens once</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_world_keeper</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>天気、依頼の期限切れ、税金、給料、手紙は一つのゲームだけが処理します。オフ：マップを持つ各プレイヤーのゲームでも起きます。</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Weather, expired quests, taxes, salaries and letters are handled by one game only, the same for everyone. Off: every player holding a map runs them too.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3676,6 +3676,142 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_take</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>デポから世界を取り出してホストする</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Take the world from the depot and host it</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_put</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>このセーブをデポに置く</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Put this save in the depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_held</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>{0} がデポの世界をホスト中</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>{0} is hosting the world of the depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_empty</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>デポに世界がありません。ホストがセーブを読み込んで「このセーブをデポに置く」を押してください。</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>The depot holds no world yet. Load a save and use "Put this save in the depot".</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_fail</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>デポのフォルダを読み書きできませんでした。</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>The depot folder could not be read or written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_put_done</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>この世界はデポに置かれました。誰でも取り出してホストできます。</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>This world is now in the depot: any player of the group can take it and host it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_folder</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>デポのフォルダ: {0}</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Depot folder: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_folder_ask</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>セーブデポのフォルダ（グループ全員が使える共有フォルダ。空欄でオフ）</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Folder of the save depot (a folder the whole group can reach; empty for none)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D198"/>
+  <dimension ref="A1:D200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3812,6 +3812,40 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>emp_ui_join_address</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>アドレスで参加</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Join by address</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>emp_ui_join_address_ask</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>サーバーのアドレス（ホスト:ポート、ポートは 55556）</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Address of the server (host:port, the port is 55556)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D200"/>
+  <dimension ref="A1:D202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -3786,12 +3787,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>デポのフォルダ: {0}</t>
+          <t>デポ（フォルダまたはサーバーのアドレス）: {0}</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Depot folder: {0}</t>
+          <t>Depot (folder or server address): {0}</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3804,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>セーブデポのフォルダ（グループ全員が使える共有フォルダ。空欄でオフ）</t>
+          <t>セーブデポ：Elin Together Server のアドレス（ホスト:55557）または共有フォルダ。空欄でオフ</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Folder of the save depot (a folder the whole group can reach; empty for none)</t>
+          <t>Save depot: the address of Elin Together Server (host:55557), or a folder the whole group can reach. Empty for none</t>
         </is>
       </c>
     </row>
@@ -3843,6 +3844,40 @@
       <c r="D200" t="inlineStr">
         <is>
           <t>Address of the server (host:port, the port is 55556)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_password</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>デポのパスワード: {0}</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Depot password: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_password_ask</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>デポのパスワード（サーバーで設定した場合）</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Password of the depot (when one was set in Elin Together Server)</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D202"/>
+  <dimension ref="A1:D203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>サーバーのアドレス（ホスト:ポート、ポートは 55556）</t>
+          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、Elin なしは 55557）</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Address of the server (host:port, the port is 55556)</t>
+          <t>Address of the server (host:port; the port is 55556 with Elin, 55557 without)</t>
         </is>
       </c>
     </row>
@@ -3878,6 +3878,23 @@
       <c r="D202" t="inlineStr">
         <is>
           <t>Password of the depot (when one was set in Elin Together Server)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>emp_ui_timeout</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>サーバーが応答しません。アドレス、ポート、サーバーのモードを確認してください。</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>The server does not answer. Check the address, the port and the mode of the server.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D203"/>
+  <dimension ref="A1:D204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3753,12 +3753,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>デポのフォルダを読み書きできませんでした。</t>
+          <t>デポに接続できない、または読み書きできませんでした。</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>The depot folder could not be read or written.</t>
+          <t>The depot could not be reached, read or written.</t>
         </is>
       </c>
     </row>
@@ -3895,6 +3895,23 @@
       <c r="D203" t="inlineStr">
         <is>
           <t>The server does not answer. Check the address, the port and the mode of the server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_password_wrong</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>サーバーがパスワードを拒否しました。「Client Settings」の「デポのパスワード」で設定してください。</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>The server refused the password. Set it in Client Settings, "Depot password".</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D204"/>
+  <dimension ref="A1:D207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>デポから世界を取り出してホストする</t>
+          <t>サーバーから世界を取り出してホストする</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Take the world from the depot and host it</t>
+          <t>Take the world from the server and host it</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>このセーブをデポに置く</t>
+          <t>このセーブをサーバーに置く</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Put this save in the depot</t>
+          <t>Put this save on the server</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{0} がデポの世界をホスト中</t>
+          <t>{0} が世界をホスト中です。Steam で参加してください（招待してもらうか、Steam のフレンド一覧で「ゲームに参加」）。相手が抜けた直後なら、最大3分待ってください。</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>{0} is hosting the world of the depot</t>
+          <t>{0} is hosting the world. Join them through Steam: ask for an invite, or use "Join Game" on their name in your Steam friends list. If they have just left, wait up to 3 minutes.</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3736,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>デポに世界がありません。ホストがセーブを読み込んで「このセーブをデポに置く」を押してください。</t>
+          <t>サーバーにまだ世界がありません。ゲームを開始または読み込み、このパネルの「Lobby」で「このセーブをサーバーに置く」を押してください。</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>The depot holds no world yet. Load a save and use "Put this save in the depot".</t>
+          <t>The server holds no world yet. Start or load a game, then open this panel again: Lobby tab, "Put this save on the server".</t>
         </is>
       </c>
     </row>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>この世界はデポに置かれました。誰でも取り出してホストできます。</t>
+          <t>この世界はサーバーに置かれました。これからサーバーから読み込み直します。以後のセーブはすべてサーバーに送られます。</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>This world is now in the depot: any player of the group can take it and host it.</t>
+          <t>This world is now on the server. The game reloads it from there: from now on every save goes to the server.</t>
         </is>
       </c>
     </row>
@@ -3912,6 +3912,57 @@
       <c r="D204" t="inlineStr">
         <is>
           <t>The server refused the password. Set it in Client Settings, "Depot password".</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_lost</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>接続が切れている間に {0} がサーバーの世界を引き継ぎました。ここからのプレイはサーバーに届きません。タイトルに戻って相手に参加してください。</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>{0} took over the world on the server while this game was cut off. What you play from here no longer reaches the server: go back to the title screen and join them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_unsaved</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>このセーブはサーバーに届きませんでした。このPCには保存されています。次のセーブで再送します。</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>The server did not receive this save. It is kept on this PC; the next save tries again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_unsent</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>前回のプレイの最後のセーブがサーバーに届いていません。今送りますか？（はい：サーバーにある世界は別に保管されます。いいえ：このPCの分を破棄し、サーバーの世界を使います）</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>The last save of your previous session never reached the server. Send it now? (Yes: the world the server holds now is kept aside. No: your save is dropped and the server's world is used.)</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D207"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3966,6 +3966,57 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>emp_quest_follow_ask</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>{0}がクエストに出発します。同行しますか？報酬は{0}のものです。</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>emp_quest_follow_declined</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>{0}は同行を断りました。</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>{0} declined to come along.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>emp_quest_follow_no_answer</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>{0}から返事がありません。</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>{0} did not answer.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D210"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4017,6 +4017,23 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>emp_quest_follow_asked</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>{0}に同行するか尋ねています…</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Asking {0} to come along...</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4034,6 +4034,159 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>emp_base_host_only</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>今のところ、これはホストだけができます。</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Only the host can do this for now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>emp_trade_equipped</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>取引中止：提示したアイテムが装備されています</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Trade cancelled: an offered item is now equipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>emp_trade_nodrop</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>取引中止：提示したアイテムは手放せません</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Trade cancelled: an offered item cannot be dropped or given away</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>emp_trade_npcprop</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>取引中止：提示したアイテムはNPCの所有物です</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Trade cancelled: an offered item belongs to an NPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>emp_trade_gifted</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>取引中止：提示したアイテムは贈り物のため取引できません</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Trade cancelled: an offered item is a gift and cannot be traded</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>emp_trade_bound</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>取引中止：提示したアイテムはキャラクターに結び付いています</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Trade cancelled: an offered item is bound to a character</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>emp_trade_full</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>取引中止：受け取るアイテムに対してバッグの空きが足りません</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Trade cancelled: a bag does not have enough free slots for what it would receive</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>emp_travel_recalled_by</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>{@Peer} がこの場所に来ます。画面が再読み込みされ、合流します…</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>{@Peer} is coming to this place: the screen will reload to rejoin them…</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>emp_ui_thing_gone</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>遅かったようです。他のプレイヤーが先に取りました</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Too late: someone else already took it</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4187,6 +4187,40 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>emp_base_refused</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ホストに断られました。拠点または所持金では、もう支払えません。</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>The host refused: the base or your purse can no longer pay for this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>emp_base_pending</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>前回の依頼はまだホストの返事を待っています。</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Your last request is still waiting for the host's answer.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D222"/>
+  <dimension ref="A1:D225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4221,6 +4221,57 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>emp_game_version_differs</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>{0} のElinのバージョンが異なります（{1} ／ こちら {2}）。接続は許可されます。問題が起きたら同じバージョンに揃えてください。</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>{0} runs another version of Elin ({1}, here {2}). The connection is allowed; if something goes wrong, use the same version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_same_game_version</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>同じElinバージョンを必須にする</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Require the same Elin version</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_same_game_version</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>オン：Elinのバージョンが違うプレイヤーを拒否。オフ：警告のうえ参加を許可。Modのバージョンは常に同じである必要があります。</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>On: players on another version of Elin are refused. Off: they are let in with a warning. The same version of the mod is always required.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4272,6 +4271,40 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_guest_build</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>他のプレイヤーも建築モードを使える</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Other players can use build mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_guest_build</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>オン：他のプレイヤーも拠点の建築モード（床・壁・家具・採掘・伐採）を使えます。ホストのゲームが代わりに建て、費用と素材は本人が払います。オフ：ホストだけが建てられます。</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>On: the other players can use the build mode of the base (floors, walls, furniture, mining, cutting). The game of the host builds for them; they pay the gold and the materials. Off: only the host builds.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D227"/>
+  <dimension ref="A1:D236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>デポ（フォルダまたはサーバーのアドレス）: {0}</t>
+          <t>デポ（フォルダ、サーバーのアドレス、または GitHub）: {0}</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Depot (folder or server address): {0}</t>
+          <t>Depot (folder, server address or GitHub): {0}</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>セーブデポ：Elin Together Server のアドレス（ホスト:55557）または共有フォルダ。空欄でオフ</t>
+          <t>セーブデポ：Elin Together Server のアドレス（ホスト:55557）、共有フォルダ、または非公開の GitHub リポジトリ（github:所有者/リポジトリ）。空欄でオフ</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Save depot: the address of Elin Together Server (host:55557), or a folder the whole group can reach. Empty for none</t>
+          <t>Save depot: the address of Elin Together Server (host:55557), a folder the whole group can reach, or a private GitHub repository (github:owner/repository). Empty for none</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3854,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>デポのパスワード: {0}</t>
+          <t>デポのパスワード／GitHub のキー: {0}</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Depot password: {0}</t>
+          <t>Depot password or GitHub key: {0}</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>デポのパスワード（サーバーで設定した場合）</t>
+          <t>デポのパスワード（サーバーで設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。空欄のままなら現在のキーを保持します</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Password of the depot (when one was set in Elin Together Server)</t>
+          <t>Password of the depot (when one was set in Elin Together Server), or the GitHub access key. A key is never shown again: leave empty to keep it</t>
         </is>
       </c>
     </row>
@@ -4302,6 +4302,167 @@
       <c r="D227" t="inlineStr">
         <is>
           <t>On: the other players can use the build mode of the base (floors, walls, furniture, mining, cutting). The game of the host builds for them; they pay the gold and the materials. Off: only the host builds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_help</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>非公開の GitHub リポジトリをデポにできます（サーバーも共有フォルダも不要、フレンドは GitHub アカウント不要）：
+1. github.com で、この世界専用の空の非公開（Private）リポジトリを作成します。
+2. そのリポジトリ用のアクセスキーを1つ作成します：Settings → Developer settings → Fine-grained tokens、このリポジトリのみ、Contents: Read and write。
+3. キーを「デポのパスワード／GitHub のキー」に貼り付け、「デポ」に github:所有者/リポジトリ と入力します。
+4. 同じ2行をフレンドに送り、フレンドもここに入力します。このキーで開けるのはこのリポジトリだけです。</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>A private GitHub repository can be the depot (no server, no shared folder, your friends need no GitHub account):
+1. On github.com, create an empty private repository, only for this world.
+2. Create one access key for it: Settings, Developer settings, Fine-grained tokens; only this repository; Contents: Read and write.
+3. Paste the key in "Depot password or GitHub key" and write github:owner/repository in "Depot".
+4. Send the same two lines to your friends: they type them here too. The key only opens this one repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_key</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>GitHub がアクセスキーを拒否しました。キーの有効期限、このリポジトリが対象になっているか、「Contents: Read and write」の権限があるかを確認し、「Client Settings」で貼り付け直してください。</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>GitHub refused the access key. Check that it has not expired, that it covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_missing</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>GitHub でデポのリポジトリが見つかりません。「Client Settings」の名前（github:所有者/リポジトリ）と、アクセスキーがそのリポジトリを対象にしているかを確認してください。</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>GitHub does not find the repository of the depot. Check its name (github:owner/repository) in Client Settings, and that your access key covers it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_public</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>この GitHub リポジトリは公開されています。世界とその履歴がすべて誰にでも見えてしまいます。非公開にしてから（Settings → Danger Zone → Change visibility）、もう一度お試しください。</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>This GitHub repository is public: your world and all its history would be visible to everyone. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_big</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>この世界は 20 MB を超えており、GitHub のデポには大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに保存されています。</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>This world is over 20 MB: too big for a GitHub depot. Use Elin Together Server or a shared folder instead. The save is kept on this PC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_changed</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>接続が切れている間に、他のプレイヤーがデポの世界をホストしてセーブしました。あなたのセーブはこのPCに残り、デポには届きません。タイトルに戻って、もう一度世界を取り出してください。</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>The world in the depot changed while this game was cut off: someone else hosted it and saved. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_down</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>GitHub から応答がありません。接続を確認して、しばらくしてからもう一度お試しください。</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_player_kill</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>プレイヤー同士で殺せる</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Players can kill each other</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_player_kill</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>オン：プレイヤー（とその仲間）の攻撃で他のプレイヤーのキャラクターが死にます。オフ：致命的な一撃でも相手のHPは0で止まり、死にません。</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>On: a strike of a player (or of its companions) can kill another player's character. Off: a strike that would kill it leaves it at 0 hit points, alive.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4466,6 +4466,40 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_host_manages_base</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>拠点の管理はホストだけ</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Only the host manages the base</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_host_manages_base</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>オン：他のプレイヤーによる拠点の操作（研究、炉の技能、政策、名前、物の設定、住民、建築モード）は拒否されます。オフ：全員がホストと同じように拠点を管理できます。拠点の放棄は常にホストだけです。</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>On: what the other players ask of the base (research, hearth skills, policies, names, settings of an object, residents, build mode) is refused. Off: every player manages the base as the host does. Leaving the base for good always stays the host's.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4500,6 +4501,210 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_duels</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>プレイヤー同士の決闘</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Duels between players</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_duels</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>オン：相手キャラクターのメニューから決闘を申し込めます。誰も死なず、終了時に両者が回復し、何も失いません。オフ：決闘なし。</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>On: a player can challenge another from the menu on its character. Nobody dies, both are healed, nothing is lost. Off: no duels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>emp_act_duel</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>決闘を申し込む</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Challenge to a duel</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>emp_duel_invite</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>{0} が決闘を申し込んできました。誰も死なず何も失いませんが、決闘中に使ったポーション・矢・チャージは戻りません。受けますか？</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>{0} challenges you to a duel. Nobody dies and nothing is lost, but potions, arrows and charges used during the duel stay spent. Accept?</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>emp_duel_asked</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>{0} に決闘を申し込みました…</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>You challenge {0} to a duel…</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>emp_duel_countdown</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>決闘：{0} 対 {1}。3秒後に開始！</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Duel: {0} against {1}. It starts in 3 seconds!</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>emp_duel_fight</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>始め！</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Fight!</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>emp_duel_won</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>{0} が {1} との決闘に勝ちました。</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>{0} won the duel against {1}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>emp_duel_declined</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>決闘は断られました。</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>The duel was declined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>emp_duel_noanswer</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>返事がなく、決闘は行われません。</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>No answer: no duel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>emp_duel_busy</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>そのプレイヤーは決闘中か取引中です。</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>That player is already in a duel or a trade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>emp_duel_over</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>決闘は勝者なしで終わりました。</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>The duel is over, without a winner.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -1771,336 +1770,330 @@
     <row r="80" ht="60" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>emp_connection_rejected</t>
+          <t>emp_dc_host_kick</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>接続が拒否されました
-ビルドバージョンが一致しません
-ホストバージョン: {0}
-クライアントバージョン: {1}</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>Connection rejected
-Build version mismatch
-Host version: {0}
-Client version: {1}</t>
+          <t>切断: ホストによりキックされました</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Disconnected: Kicked by host</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>emp_dc_host_kick</t>
+          <t>emp_ui_tab_client</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>切断: ホストによりキックされました</t>
+          <t>クライアント設定</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Disconnected: Kicked by host</t>
+          <t>Client Settings</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>emp_ui_tab_client</t>
+          <t>emp_tab_client</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>クライアント設定</t>
+          <t>クライアント</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Client Settings</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>emp_tab_client</t>
+          <t>emp_ui_kick</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>クライアント</t>
+          <t>キック</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>emp_ui_kick</t>
+          <t>emp_ui_ping_keymap</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>キック</t>
+          <t>ピンキー設定: {0}</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Bind Ping Key: {0}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>emp_ui_ping_keymap</t>
+          <t>emp_ui_ping_action</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ピンキー設定: {0}</t>
+          <t>ピン</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Bind Ping Key: {0}</t>
+          <t>Ping</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>emp_ui_ping_action</t>
+          <t>emp_ui_unknown_player</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ピン</t>
+          <t>プレイヤー {0}</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ping</t>
+          <t>Player {0}</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>emp_ui_unknown_player</t>
+          <t>emp_ui_source_mismatch_header</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>プレイヤー {0}</t>
+          <t>ソース検証失敗 — {0} 件の不一致</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Player {0}</t>
+          <t>Source validation failed — {0} mismatches</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_header</t>
+          <t>emp_ui_source_mismatch_sources</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ソース検証失敗 — {0} 件の不一致</t>
+          <t>ソース不一致:</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Source validation failed — {0} mismatches</t>
+          <t>Source mismatches:</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_sources</t>
+          <t>emp_ui_source_mismatch_plugins</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ソース不一致:</t>
+          <t>プラグイン不一致:</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Source mismatches:</t>
+          <t>Plugin mismatches:</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_plugins</t>
+          <t>emp_ui_source_mismatch_files</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>プラグイン不一致:</t>
+          <t>ファイル不一致:</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Plugin mismatches:</t>
+          <t>File mismatches:</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_files</t>
+          <t>emp_ui_source_mismatch_more</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ファイル不一致:</t>
+          <t>… 他 {0} 件</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>File mismatches:</t>
+          <t>… and {0} more</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_more</t>
+          <t>emp_ui_source_mismatch_continue</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>… 他 {0} 件</t>
+          <t>それでも続行しますか？</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>… and {0} more</t>
+          <t>Continue anyway?</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_continue</t>
+          <t>emp_ui_sv_cfg_validation_sets</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>それでも続行しますか？</t>
+          <t>検証セット</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Continue anyway?</t>
+          <t>Validation Sets</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_validation_sets</t>
+          <t>emp_validation_none</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>検証セット</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Validation Sets</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>emp_validation_none</t>
+          <t>emp_validation_sources</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>ソース</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>emp_validation_sources</t>
+          <t>emp_validation_plugins</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ソース</t>
+          <t>プラグイン</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Plugin</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>emp_validation_plugins</t>
+          <t>emp_validation_all</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>プラグイン</t>
+          <t>すべて</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Plugin</t>
+          <t>All</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>emp_validation_all</t>
+          <t>emp_ui_reconnect</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>すべて</t>
+          <t>再接続</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Reconnect</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect</t>
+          <t>emp_dc_reconnect_request</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2110,145 +2103,128 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Reconnect</t>
+          <t>Reconnect Request</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>emp_dc_reconnect_request</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>再接続</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Reconnect Request</t>
+          <t>emp_lobby_create_failed</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>Steamロビーの作成に失敗しました: {Result}
+後でもう一度試してください</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>Failed to create Steam lobby: {Result}
+Try again later</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>emp_lobby_create_failed</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>Steamロビーの作成に失敗しました: {Result}
-後でもう一度試してください</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>Failed to create Steam lobby: {Result}
-Try again later</t>
+          <t>emp_lobby_enter_failed</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Steamロビーへの参加に失敗しました: {Response}</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Failed to enter Steam lobby: {Response}</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>emp_lobby_enter_failed</t>
+          <t>emp_lobby_already_joined</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Steamロビーへの参加に失敗しました: {Response}</t>
+          <t>すでに同じロビーに参加しています</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Failed to enter Steam lobby: {Response}</t>
+          <t>Already in the same lobby</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>emp_lobby_already_joined</t>
+          <t>emp_ui_quest_client</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>すでに同じロビーに参加しています</t>
+          <t>（暫定）このクエストはクライアントプレイヤーからは開始できません。</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Already in the same lobby</t>
+          <t>(Temp) This quest cannot be started by client players.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>emp_ui_quest_client</t>
+          <t>emp_dc_version_mismatch</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>（暫定）このクエストはクライアントプレイヤーからは開始できません。</t>
+          <t>切断: 無効なVersion</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(Temp) This quest cannot be started by client players.</t>
+          <t>Disconnected: invalid version</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>emp_dc_version_mismatch</t>
+          <t>emp_dc_act_mismatch</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>切断: 無効なVersion</t>
+          <t>切断: Act 不一致</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Disconnected: invalid version</t>
+          <t>Act mapping mismatch</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>emp_dc_act_mismatch</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>切断: Act 不一致</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Act mapping mismatch</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
-        <is>
           <t>emp_ui_reject_acts</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>参加できません：Actマッピングが一致しません（{0}件）
 Act ID同期エラー：不一致は動作不良の原因になります。
 双方とも同じModを導入しているか確認してください。</t>
         </is>
       </c>
-      <c r="D107" s="1" t="inlineStr">
+      <c r="D106" s="1" t="inlineStr">
         <is>
           <t>Could not join: Act mapping mismatch ({0})
 Act ID is used for action sync. Game cannot run with mismatch acts.
@@ -2256,30 +2232,30 @@
         </is>
       </c>
     </row>
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>emp_ui_reject_integrity</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>参加できません：ホストの厳密チェックにより、データ整合性が不一致です（{0}件）</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Could not join: Host has strict verification enabled. Data integrity mismatch ({0})</t>
+        </is>
+      </c>
+    </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>emp_ui_reject_integrity</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>参加できません：ホストの厳密チェックにより、データ整合性が不一致です（{0}件）</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Could not join: Host has strict verification enabled. Data integrity mismatch ({0})</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
-        <is>
           <t>emp_version_rejected_host</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>{0}の接続を拒否しました
 バージョンがホストと一致しません
@@ -2287,7 +2263,7 @@
 ホストゲーム：{2}</t>
         </is>
       </c>
-      <c r="D109" s="1" t="inlineStr">
+      <c r="D108" s="1" t="inlineStr">
         <is>
           <t>Connection request from {0} rejected
 Version mismatch with host
@@ -2296,495 +2272,514 @@
         </is>
       </c>
     </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>emp_version_rejected_client</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>参加できません：バージョン不一致
+Mod：自機 {0} ／ ホスト {1}
+ゲーム：自機 {2} ／ ホスト {3}
+古いバージョンのほうを更新してから、もう一度お試しください。</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>Could not join: Version mismatch
+Mod: Local {0} / Host {1}
+Game: Local {2} / Host {3}
+Whoever has the older version must update, then try again.</t>
+        </is>
+      </c>
+    </row>
     <row r="110" ht="45" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>emp_version_rejected_client</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>参加できません：バージョン不一致
-Mod：自機 {0} ／ ホスト {1}
-ゲーム：自機 {2} ／ ホスト {3}</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>Could not join: Version mismatch
-Mod: Local {0} / Host {1}
-Game: Local {2} / Host {3}</t>
+          <t>emp_ui_sleep_request</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>全員がベッドに入るのを待っています…</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Waiting for everyone to go to bed...</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_request</t>
+          <t>emp_ui_sleep_wish</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>全員がベッドに入るのを待っています…</t>
+          <t>{0}が眠りたがっています（{1}/{2}）</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Waiting for everyone to go to bed...</t>
+          <t>{0} wants to sleep ({1}/{2})</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_wish</t>
+          <t>emp_ui_sleep_cancel</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{0}が眠りたがっています（{1}/{2}）</t>
+          <t>{0}が目を覚ましました（{1}/{2}）</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{0} wants to sleep ({1}/{2})</t>
+          <t>{0} woke up ({1}/{2})</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_cancel</t>
+          <t>emp_travel_requesting</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{0}が目を覚ましました（{1}/{2}）</t>
+          <t>ホストに移動を申請中…</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{0} woke up ({1}/{2})</t>
+          <t>Asking the host to travel there alone…</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>emp_travel_requesting</t>
+          <t>emp_travel_returning</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ホストに移動を申請中…</t>
+          <t>ホストのいる場所へ戻っています…</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Asking the host to travel there alone…</t>
+          <t>Returning to the host…</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>emp_travel_returning</t>
+          <t>emp_travel_disabled</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ホストのいる場所へ戻っています…</t>
+          <t>ホストが単独行動を許可していません</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Returning to the host…</t>
+          <t>The host does not allow travelling alone</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>emp_travel_disabled</t>
+          <t>emp_travel_invalid</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ホストが単独行動を許可していません</t>
+          <t>この場所へは単独で行けません</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>The host does not allow travelling alone</t>
+          <t>You cannot travel there alone</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>emp_travel_invalid</t>
+          <t>emp_travel_host_zone</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>この場所へは単独で行けません</t>
+          <t>ホストはすでにそこにいます</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>You cannot travel there alone</t>
+          <t>The host is already there</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>emp_travel_host_zone</t>
+          <t>emp_travel_occupied</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ホストはすでにそこにいます</t>
+          <t>他のプレイヤーがその場所にいます</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>The host is already there</t>
+          <t>Another player is already there</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>emp_travel_occupied</t>
+          <t>emp_travel_recalling</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>他のプレイヤーがその場所にいます</t>
+          <t>{@Peer} がその場所を返すのを待っています…</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Another player is already there</t>
+          <t>Waiting for {@Peer} to hand the zone back…</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>emp_travel_recalling</t>
+          <t>emp_travel_recalled</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{@Peer} がその場所を返すのを待っています…</t>
+          <t>ホストが来ます。合流します…</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Waiting for {@Peer} to hand the zone back…</t>
+          <t>The host is coming, rejoining them…</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>emp_travel_recalled</t>
+          <t>emp_travel_zone_closed</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ホストが来ます。合流します…</t>
+          <t>この場所の主がいなくなりました。ホストに合流します</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>The host is coming, rejoining them…</t>
+          <t>The owner of this place is gone, rejoining the host</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>emp_travel_zone_closed</t>
+          <t>emp_travel_handoff</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>この場所の主がいなくなりました。ホストに合流します</t>
+          <t>この場所の主はあなたになりました</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>The owner of this place is gone, rejoining the host</t>
+          <t>You are now the owner of this place</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>emp_travel_handoff</t>
+          <t>emp_ui_sv_cfg_independent_travel</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>この場所の主はあなたになりました</t>
+          <t>単独行動を許可</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>You are now the owner of this place</t>
+          <t>Independent travel</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_independent_travel</t>
+          <t>emp_ui_sv_cfg_player_shipping</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>単独行動を許可</t>
+          <t>出荷はプレイヤーごと</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Independent travel</t>
+          <t>Shipping per player</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_shipping</t>
+          <t>emp_ui_sv_cfg_combat_time</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>出荷はプレイヤーごと</t>
+          <t>戦闘は各プレイヤーの時間で進行</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Shipping per player</t>
+          <t>Combat on each player's time</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_combat_time</t>
+          <t>emp_ui_bot_add</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>戦闘は各プレイヤーの時間で進行</t>
+          <t>Add a bot player</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Combat on each player's time</t>
+          <t>Add a bot player</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>emp_ui_bot_add</t>
+          <t>emp_ui_bot_stop</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Add a bot player</t>
+          <t>Stop the bots ({0})</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Add a bot player</t>
+          <t>Stop the bots ({0})</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>emp_ui_bot_stop</t>
+          <t>emp_ui_bot_all_actions</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Stop the bots ({0})</t>
+          <t>Bots do everything (quests, selling, digging, chests)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Stop the bots ({0})</t>
+          <t>Bots do everything (quests, selling, digging, chests)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>emp_ui_bot_all_actions</t>
+          <t>emp_ui_bot_need_local</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bots do everything (quests, selling, digging, chests)</t>
+          <t>Bots need a local server: disconnect, then add a bot to start one</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Bots do everything (quests, selling, digging, chests)</t>
+          <t>Bots need a local server: disconnect, then add a bot to start one</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>emp_ui_bot_need_local</t>
+          <t>emp_ui_bot_no_launcher</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bots need a local server: disconnect, then add a bot to start one</t>
+          <t>No second copy of the game found (see _tools/make_lab.py)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bots need a local server: disconnect, then add a bot to start one</t>
+          <t>No second copy of the game found (see _tools/make_lab.py)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>emp_ui_bot_no_launcher</t>
+          <t>emp_ui_bot_started</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No second copy of the game found (see _tools/make_lab.py)</t>
+          <t>Bot player starting, it joins in about a minute</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No second copy of the game found (see _tools/make_lab.py)</t>
+          <t>Bot player starting, it joins in about a minute</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>emp_ui_bot_started</t>
+          <t>emp_ui_sv_cfg_personal_quests</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bot player starting, it joins in about a minute</t>
+          <t>ランダムクエスト・名声・カルマはプレイヤーごと</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Bot player starting, it joins in about a minute</t>
+          <t>Random quests, fame and karma per player</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_personal_quests</t>
+          <t>emp_ui_sv_cfg_choose_chara</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ランダムクエスト・名声・カルマはプレイヤーごと</t>
+          <t>参加時にプレイヤーがキャラクターを選ぶ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Random quests, fame and karma per player</t>
+          <t>Players choose their character when joining</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_choose_chara</t>
+          <t>emp_ui_chara_pick</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Players choose their character when joining</t>
+          <t>どのキャラクターで遊びますか？</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Players choose their character when joining</t>
+          <t>Who do you want to play?</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>emp_ui_chara_pick</t>
+          <t>emp_ui_chara_new</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Who do you want to play?</t>
+          <t>新しいキャラクター</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Who do you want to play?</t>
+          <t>A new character</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>emp_ui_chara_new</t>
+          <t>emp_ui_sv_cfg_player_trade</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>A new character</t>
+          <t>プレイヤー間の取引ウィンドウ</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>A new character</t>
+          <t>Trade window between players</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_trade</t>
+          <t>emp_act_trade</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Trade window between players</t>
+          <t>取引</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Trade window between players</t>
+          <t>Trade</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>emp_act_trade</t>
+          <t>emp_ui_trade</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>取引</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -2796,1912 +2791,2031 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>emp_ui_trade</t>
+          <t>emp_trade_invite</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>{0} があなたと取引したがっています</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>{0} wants to trade with you</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>emp_trade_invite</t>
+          <t>emp_trade_you_offer</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{0} wants to trade with you</t>
+          <t>あなたの提示</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{0} wants to trade with you</t>
+          <t>You offer</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>emp_trade_you_offer</t>
+          <t>emp_trade_they_offer</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>You offer</t>
+          <t>{0} の提示</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>You offer</t>
+          <t>{0} offers</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>emp_trade_they_offer</t>
+          <t>emp_trade_nothing</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{0} offers</t>
+          <t>（まだなし）</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{0} offers</t>
+          <t>(nothing yet)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>emp_trade_nothing</t>
+          <t>emp_trade_add</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>(nothing yet)</t>
+          <t>アイテムを追加</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(nothing yet)</t>
+          <t>Add an item</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>emp_trade_add</t>
+          <t>emp_trade_gold</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Add an item</t>
+          <t>金貨: {0}</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Add an item</t>
+          <t>Gold: {0}</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>emp_trade_gold</t>
+          <t>emp_trade_clear</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Gold: {0}</t>
+          <t>すべて取り下げる</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Gold: {0}</t>
+          <t>Take everything back</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>emp_trade_clear</t>
+          <t>emp_trade_confirm</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Take everything back</t>
+          <t>確認</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Take everything back</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>emp_trade_confirm</t>
+          <t>emp_trade_cancel</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>emp_trade_cancel</t>
+          <t>emp_trade_you_ready</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>あなたは確認しました</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>You confirmed</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>emp_trade_you_ready</t>
+          <t>emp_trade_you_wait</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>You confirmed</t>
+          <t>あなたは未確認です</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>You confirmed</t>
+          <t>You have not confirmed</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>emp_trade_you_wait</t>
+          <t>emp_trade_they_ready</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>You have not confirmed</t>
+          <t>相手は確認しました</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>You have not confirmed</t>
+          <t>the other player confirmed</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>emp_trade_they_ready</t>
+          <t>emp_trade_they_wait</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>the other player confirmed</t>
+          <t>相手は未確認です</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>the other player confirmed</t>
+          <t>the other player has not confirmed</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>emp_trade_they_wait</t>
+          <t>emp_trade_pick</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>the other player has not confirmed</t>
+          <t>どのアイテム？</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>the other player has not confirmed</t>
+          <t>Which item?</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>emp_trade_pick</t>
+          <t>emp_trade_howmany</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Which item?</t>
+          <t>何個？</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Which item?</t>
+          <t>How many?</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>emp_trade_howmany</t>
+          <t>emp_trade_howmuch</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>How many?</t>
+          <t>金貨はいくら？</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>How many?</t>
+          <t>How much gold?</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>emp_trade_howmuch</t>
+          <t>emp_trade_done</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>How much gold?</t>
+          <t>取引が完了しました</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>How much gold?</t>
+          <t>Trade done</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>emp_trade_done</t>
+          <t>emp_trade_cancelled</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Trade done</t>
+          <t>取引は中止されました</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Trade done</t>
+          <t>Trade cancelled</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>emp_trade_cancelled</t>
+          <t>emp_trade_invalid</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Trade cancelled</t>
+          <t>取引中止：提示したものがもう存在しません</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Trade cancelled</t>
+          <t>Trade cancelled: something offered is not there anymore</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>emp_trade_invalid</t>
+          <t>emp_trade_far</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Trade cancelled: something offered is not there anymore</t>
+          <t>取引中止：お互いが離れすぎています</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Trade cancelled: something offered is not there anymore</t>
+          <t>Trade cancelled: too far from each other</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>emp_trade_far</t>
+          <t>emp_trade_busy</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Trade cancelled: too far from each other</t>
+          <t>そのプレイヤーはすでに取引中です</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Trade cancelled: too far from each other</t>
+          <t>That player is already trading</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>emp_trade_busy</t>
+          <t>emp_ui_sv_note_live</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>That player is already trading</t>
+          <t>ホストのルールです。変更はすぐに全員に適用されます。</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>That player is already trading</t>
+          <t>These rules are the host's. A change applies at once, for everyone.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>emp_ui_sv_note_live</t>
+          <t>emp_ui_sv_sec_players</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ホストのルールです。変更はすぐに全員に適用されます。</t>
+          <t>プレイヤーと移動</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>These rules are the host's. A change applies at once, for everyone.</t>
+          <t>Players and travel</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_players</t>
+          <t>emp_ui_sv_sec_own</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>プレイヤーと移動</t>
+          <t>プレイヤーごとのもの</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Players and travel</t>
+          <t>To each player its own</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_own</t>
+          <t>emp_ui_sv_sec_time</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>プレイヤーごとのもの</t>
+          <t>時間と戦闘</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>To each player its own</t>
+          <t>Time and combat</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_time</t>
+          <t>emp_ui_sv_sec_checks</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>時間と戦闘</t>
+          <t>参加時の検証（上級者向け）</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Time and combat</t>
+          <t>Joining checks (advanced)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_checks</t>
+          <t>emp_ui_sv_desc_choose_chara</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>参加時の検証（上級者向け）</t>
+          <t>参加時に、この世界の自分のキャラクターから選ぶか、新しく作る。</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Joining checks (advanced)</t>
+          <t>A joining player picks one of its characters in this world, or makes a new one.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_choose_chara</t>
+          <t>emp_ui_sv_desc_independent_travel</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>参加時に、この世界の自分のキャラクターから選ぶか、新しく作る。</t>
+          <t>誰でも好きな場所へ、一人でも一緒でも行ける。オフ：全員がホストについて行く。</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>A joining player picks one of its characters in this world, or makes a new one.</t>
+          <t>Everyone goes where they want, alone or together. Off: everyone follows the host.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_independent_travel</t>
+          <t>emp_ui_sv_desc_personal_quests</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>誰でも好きな場所へ、一人でも一緒でも行ける。オフ：全員がホストについて行く。</t>
+          <t>各自ランダムクエスト5件、報酬・名声・カルマも各自。メインクエストは共有。</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Everyone goes where they want, alone or together. Off: everyone follows the host.</t>
+          <t>5 random quests each, with their reward, fame and karma. Story quests stay shared.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_personal_quests</t>
+          <t>emp_ui_sv_desc_player_shipping</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>各自ランダムクエスト5件、報酬・名声・カルマも各自。メインクエストは共有。</t>
+          <t>出荷箱の売上はアイテムを入れたプレイヤーへ。オフ：すべてホストへ。</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>5 random quests each, with their reward, fame and karma. Story quests stay shared.</t>
+          <t>Shipping box money goes to the player who put the item in. Off: all to the host.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_shipping</t>
+          <t>emp_ui_sv_desc_player_trade</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>出荷箱の売上はアイテムを入れたプレイヤーへ。オフ：すべてホストへ。</t>
+          <t>他のプレイヤーをクリックしてアイテムと金貨を交換。双方が確認する。</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Shipping box money goes to the player who put the item in. Off: all to the host.</t>
+          <t>Click another player to trade items and gold. Both confirm.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_trade</t>
+          <t>emp_ui_sv_desc_combat_time</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>他のプレイヤーをクリックしてアイテムと金貨を交換。双方が確認する。</t>
+          <t>モンスターは戦っている相手が動いた時に動く。誰も待たない。ターン制より優先。</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Click another player to trade items and gold. Both confirm.</t>
+          <t>A monster acts when the player it fights acts: nobody waits. Takes over turn-based.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_combat_time</t>
+          <t>emp_ui_sv_desc_turn_combat</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>モンスターは戦っている相手が動いた時に動く。誰も待たない。ターン制より優先。</t>
+          <t>戦闘中、プレイヤーは順番に行動する。「戦闘は各プレイヤーの時間で進行」がオンの間は無効。</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>A monster acts when the player it fights acts: nobody waits. Takes over turn-based.</t>
+          <t>In a fight, players act in turn. No effect while "Combat on each player's time" is on.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_turn_combat</t>
+          <t>emp_ui_sv_desc_shared_speed</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>戦闘中、プレイヤーは順番に行動する。「戦闘は各プレイヤーの時間で進行」がオンの間は無効。</t>
+          <t>全プレイヤーが平均速度を共有。オフ：各自の速度。</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>In a fight, players act in turn. No effect while "Combat on each player's time" is on.</t>
+          <t>One speed for all players, the average. Off: each keeps its own.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_speed</t>
+          <t>emp_ui_sv_desc_validation</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>全プレイヤーが平均速度を共有。オフ：各自の速度。</t>
+          <t>参加するプレイヤーのゲームがホストと一致すべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>One speed for all players, the average. Off: each keeps its own.</t>
+          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_validation</t>
+          <t>emp_ui_sv_cfg_player_clock</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>参加するプレイヤーのゲームがホストと一致すべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
+          <t>各プレイヤーは自分の時計で動く</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
+          <t>Each player on its own clock</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_clock</t>
+          <t>emp_ui_sv_desc_player_clock</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>各プレイヤーは自分の時計で動く</t>
+          <t>ゲストもホストと同じように滑らかに動く（通信の速さに左右されない）。上のオプションが必要。</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Each player on its own clock</t>
+          <t>A guest walks and acts as smoothly as the host, not at the pace of the network. Needs the option above.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_clock</t>
+          <t>emp_ui_sv_cfg_step_pace</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ゲストもホストと同じように滑らかに動く（通信の速さに左右されない）。上のオプションが必要。</t>
+          <t>各プレイヤーはソロと同じ歩調で動く</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>A guest walks and acts as smoothly as the host, not at the pace of the network. Needs the option above.</t>
+          <t>Every player walks at the pace of a solo game</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_step_pace</t>
+          <t>emp_ui_sv_desc_step_pace</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>各プレイヤーはソロと同じ歩調で動く</t>
+          <t>歩く速さが他のプレイヤーの速度に左右されなくなります。戦闘では速度は今まで通り有効。「戦闘は各プレイヤーの時間で」が必要。</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Every player walks at the pace of a solo game</t>
+          <t>The length of a step no longer depends on the other players' speed. Speed still counts in a fight. Needs combat on each player's time.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_step_pace</t>
+          <t>emp_ui_sv_cfg_import_chara</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>歩く速さが他のプレイヤーの速度に左右されなくなります。戦闘では速度は今まで通り有効。「戦闘は各プレイヤーの時間で」が必要。</t>
+          <t>自分のセーブのキャラクターで参加できる</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>The length of a step no longer depends on the other players' speed. Speed still counts in a fight. Needs combat on each player's time.</t>
+          <t>Players can bring a character from their own saves</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_import_chara</t>
+          <t>emp_ui_sv_desc_import_chara</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラクターで参加できる</t>
+          <t>キャラクター本人、装備、持ち物、所持金、名声、カルマ。仲間、拠点、クエスト、銀行は含まれません。セーブは読むだけで変更しません。</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Players can bring a character from their own saves</t>
+          <t>The character, its equipment, bag and gold, its fame and karma. Not its companions, base, quests or bank. The save is only read, never changed.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_import_chara</t>
+          <t>emp_ui_chara_import</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>キャラクター本人、装備、持ち物、所持金、名声、カルマ。仲間、拠点、クエスト、銀行は含まれません。セーブは読むだけで変更しません。</t>
+          <t>自分のセーブのキャラクター…</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>The character, its equipment, bag and gold, its fame and karma. Not its companions, base, quests or bank. The save is only read, never changed.</t>
+          <t>A character from one of my saves…</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import</t>
+          <t>emp_ui_chara_import_pick</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラクター…</t>
+          <t>どのセーブのキャラクターで参加しますか？（セーブは変更されません）</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>A character from one of my saves…</t>
+          <t>Which save to bring the character of? (the save is not changed)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_pick</t>
+          <t>emp_ui_chara_import_back</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>どのセーブのキャラクターで参加しますか？（セーブは変更されません）</t>
+          <t>戻る</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Which save to bring the character of? (the save is not changed)</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_back</t>
+          <t>emp_ui_chara_import_none</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>戻る</t>
+          <t>読み込めるセーブがありません。</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>No save this game can read was found.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_none</t>
+          <t>emp_ui_chara_import_fail</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>読み込めるセーブがありません。</t>
+          <t>このキャラクターは読み込めませんでした。</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>No save this game can read was found.</t>
+          <t>That character could not be brought.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_fail</t>
+          <t>emp_ui_chara_import_twice</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>このキャラクターは読み込めませんでした。</t>
+          <t>このセーブのキャラクターはすでにこの世界にいます。</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>That character could not be brought.</t>
+          <t>The character of that save is already in this world.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_twice</t>
+          <t>emp_ui_sv_cfg_world_time</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>このセーブのキャラクターはすでにこの世界にいます。</t>
+          <t>世界の時間は全員で一つ</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>The character of that save is already in this world.</t>
+          <t>One date for the whole world</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_time</t>
+          <t>emp_ui_sv_desc_world_time</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>世界の時間は全員で一つ</t>
+          <t>一人で別のマップにいるプレイヤーの時間も世界の時間になります。一番進んだ日付が世界の日付。オフ：ホストの日付だけ。</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>One date for the whole world</t>
+          <t>Time passed by a player alone on another map counts for everyone: the most advanced date is the world's. Off: only the host's date counts.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_time</t>
+          <t>emp_ui_sv_cfg_world_keeper</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>一人で別のマップにいるプレイヤーの時間も世界の時間になります。一番進んだ日付が世界の日付。オフ：ホストの日付だけ。</t>
+          <t>世界の出来事は一度だけ起きる</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Time passed by a player alone on another map counts for everyone: the most advanced date is the world's. Off: only the host's date counts.</t>
+          <t>What time does to the world happens once</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_keeper</t>
+          <t>emp_ui_sv_desc_world_keeper</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>世界の出来事は一度だけ起きる</t>
+          <t>天気、依頼の期限切れ、税金、給料、手紙は一つのゲームだけが処理します。オフ：マップを持つ各プレイヤーのゲームでも起きます。</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>What time does to the world happens once</t>
+          <t>Weather, expired quests, taxes, salaries and letters are handled by one game only, the same for everyone. Off: every player holding a map runs them too.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_keeper</t>
+          <t>emp_ui_depot_take</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>天気、依頼の期限切れ、税金、給料、手紙は一つのゲームだけが処理します。オフ：マップを持つ各プレイヤーのゲームでも起きます。</t>
+          <t>サーバーから世界を取り出してホストする</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Weather, expired quests, taxes, salaries and letters are handled by one game only, the same for everyone. Off: every player holding a map runs them too.</t>
+          <t>Take the world from the server and host it</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>emp_ui_depot_take</t>
+          <t>emp_ui_depot_put</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>サーバーから世界を取り出してホストする</t>
+          <t>このセーブをサーバーに置く</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Take the world from the server and host it</t>
+          <t>Put this save on the server</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put</t>
+          <t>emp_ui_depot_held</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>このセーブをサーバーに置く</t>
+          <t>{0} が世界をホスト中です。Steam で参加してください（招待してもらうか、Steam のフレンド一覧で「ゲームに参加」）。相手が抜けた直後なら、最大3分待ってください。</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Put this save on the server</t>
+          <t>{0} is hosting the world. Join them through Steam: ask for an invite, or use "Join Game" on their name in your Steam friends list. If they have just left, wait up to 3 minutes.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>emp_ui_depot_held</t>
+          <t>emp_ui_depot_empty</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{0} が世界をホスト中です。Steam で参加してください（招待してもらうか、Steam のフレンド一覧で「ゲームに参加」）。相手が抜けた直後なら、最大3分待ってください。</t>
+          <t>サーバーにまだ世界がありません。ゲームを開始または読み込み、このパネルの「Lobby」で「このセーブをサーバーに置く」を押してください。</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>{0} is hosting the world. Join them through Steam: ask for an invite, or use "Join Game" on their name in your Steam friends list. If they have just left, wait up to 3 minutes.</t>
+          <t>The server holds no world yet. Start or load a game, then open this panel again: Lobby tab, "Put this save on the server".</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>emp_ui_depot_empty</t>
+          <t>emp_ui_depot_fail</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>サーバーにまだ世界がありません。ゲームを開始または読み込み、このパネルの「Lobby」で「このセーブをサーバーに置く」を押してください。</t>
+          <t>デポに接続できない、または読み書きできませんでした。</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>The server holds no world yet. Start or load a game, then open this panel again: Lobby tab, "Put this save on the server".</t>
+          <t>The depot could not be reached, read or written.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>emp_ui_depot_fail</t>
+          <t>emp_ui_depot_put_done</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>デポに接続できない、または読み書きできませんでした。</t>
+          <t>この世界はサーバーに置かれました。これからサーバーから読み込み直します。以後のセーブはすべてサーバーに送られます。</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>The depot could not be reached, read or written.</t>
+          <t>This world is now on the server. The game reloads it from there: from now on every save goes to the server.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put_done</t>
+          <t>emp_ui_depot_folder</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>この世界はサーバーに置かれました。これからサーバーから読み込み直します。以後のセーブはすべてサーバーに送られます。</t>
+          <t>デポ</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>This world is now on the server. The game reloads it from there: from now on every save goes to the server.</t>
+          <t>Depot</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder</t>
+          <t>emp_ui_depot_folder_ask</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>デポ（フォルダ、サーバーのアドレス、または GitHub）: {0}</t>
+          <t>セーブデポ：Elin Together Server のアドレス（ホスト:55557）、共有フォルダ、または非公開の GitHub リポジトリ（github:所有者/リポジトリ）。空欄でオフ</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Depot (folder, server address or GitHub): {0}</t>
+          <t>Save depot: the address of Elin Together Server (host:55557), a folder the whole group can reach, or a private GitHub repository (github:owner/repository). Empty for none</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder_ask</t>
+          <t>emp_ui_join_address</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>セーブデポ：Elin Together Server のアドレス（ホスト:55557）、共有フォルダ、または非公開の GitHub リポジトリ（github:所有者/リポジトリ）。空欄でオフ</t>
+          <t>アドレスで参加</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Save depot: the address of Elin Together Server (host:55557), a folder the whole group can reach, or a private GitHub repository (github:owner/repository). Empty for none</t>
+          <t>Join by address</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>emp_ui_join_address</t>
+          <t>emp_ui_join_address_ask</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>アドレスで参加</t>
+          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、Elin なしは 55557）</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Join by address</t>
+          <t>Address of the server (host:port; the port is 55556 with Elin, 55557 without)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>emp_ui_join_address_ask</t>
+          <t>emp_ui_depot_password</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、Elin なしは 55557）</t>
+          <t>デポのキー</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Address of the server (host:port; the port is 55556 with Elin, 55557 without)</t>
+          <t>Depot key</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password</t>
+          <t>emp_ui_depot_password_ask</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>デポのパスワード／GitHub のキー: {0}</t>
+          <t>デポのパスワード（サーバーで設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。空欄のままなら現在のキーを保持します</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Depot password or GitHub key: {0}</t>
+          <t>Password of the depot (when one was set in Elin Together Server), or the GitHub access key. A key is never shown again: leave empty to keep it</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_ask</t>
+          <t>emp_ui_timeout</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>デポのパスワード（サーバーで設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。空欄のままなら現在のキーを保持します</t>
+          <t>サーバーが応答しません。アドレス、ポート、サーバーのモードを確認してください。</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Password of the depot (when one was set in Elin Together Server), or the GitHub access key. A key is never shown again: leave empty to keep it</t>
+          <t>The server does not answer. Check the address, the port and the mode of the server.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>emp_ui_timeout</t>
+          <t>emp_ui_depot_password_wrong</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>サーバーが応答しません。アドレス、ポート、サーバーのモードを確認してください。</t>
+          <t>サーバーがパスワードを拒否しました。「Client Settings」の「デポのキー」で設定してください。</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The server does not answer. Check the address, the port and the mode of the server.</t>
+          <t>The server refused the password. Set it in Client Settings, "Depot key".</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_wrong</t>
+          <t>emp_ui_depot_lost</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>サーバーがパスワードを拒否しました。「Client Settings」の「デポのパスワード」で設定してください。</t>
+          <t>接続が切れている間に {0} がサーバーの世界を引き継ぎました。ここからのプレイはサーバーに届きません。タイトルに戻って相手に参加してください。</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>The server refused the password. Set it in Client Settings, "Depot password".</t>
+          <t>{0} took over the world on the server while this game was cut off. What you play from here no longer reaches the server: go back to the title screen and join them.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>emp_ui_depot_lost</t>
+          <t>emp_ui_depot_unsaved</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>接続が切れている間に {0} がサーバーの世界を引き継ぎました。ここからのプレイはサーバーに届きません。タイトルに戻って相手に参加してください。</t>
+          <t>このセーブはサーバーに届きませんでした。このPCには保存されています。次のセーブで再送します。</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>{0} took over the world on the server while this game was cut off. What you play from here no longer reaches the server: go back to the title screen and join them.</t>
+          <t>The server did not receive this save. It is kept on this PC; the next save tries again.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsaved</t>
+          <t>emp_ui_depot_unsent</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>このセーブはサーバーに届きませんでした。このPCには保存されています。次のセーブで再送します。</t>
+          <t>前回のプレイの最後のセーブがサーバーに届いていません。今送りますか？（はい：サーバーにある世界は別に保管されます。いいえ：このPCの分を破棄し、サーバーの世界を使います）</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The server did not receive this save. It is kept on this PC; the next save tries again.</t>
+          <t>The last save of your previous session never reached the server. Send it now? (Yes: the world the server holds now is kept aside. No: your save is dropped and the server's world is used.)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsent</t>
+          <t>emp_quest_follow_ask</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>前回のプレイの最後のセーブがサーバーに届いていません。今送りますか？（はい：サーバーにある世界は別に保管されます。いいえ：このPCの分を破棄し、サーバーの世界を使います）</t>
+          <t>{0}がクエストに出発します。同行しますか？報酬は{0}のものです。</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>The last save of your previous session never reached the server. Send it now? (Yes: the world the server holds now is kept aside. No: your save is dropped and the server's world is used.)</t>
+          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>emp_quest_follow_ask</t>
+          <t>emp_quest_follow_declined</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{0}がクエストに出発します。同行しますか？報酬は{0}のものです。</t>
+          <t>{0}は同行を断りました。</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
+          <t>{0} declined to come along.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>emp_quest_follow_declined</t>
+          <t>emp_quest_follow_no_answer</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{0}は同行を断りました。</t>
+          <t>{0}から返事がありません。</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>{0} declined to come along.</t>
+          <t>{0} did not answer.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>emp_quest_follow_no_answer</t>
+          <t>emp_quest_follow_asked</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{0}から返事がありません。</t>
+          <t>{0}に同行するか尋ねています…</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>{0} did not answer.</t>
+          <t>Asking {0} to come along...</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>emp_quest_follow_asked</t>
+          <t>emp_base_host_only</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>{0}に同行するか尋ねています…</t>
+          <t>今のところ、これはホストだけができます。</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Asking {0} to come along...</t>
+          <t>Only the host can do this for now.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>emp_base_host_only</t>
+          <t>emp_trade_equipped</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>今のところ、これはホストだけができます。</t>
+          <t>取引中止：提示したアイテムが装備されています</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Only the host can do this for now.</t>
+          <t>Trade cancelled: an offered item is now equipped</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>emp_trade_equipped</t>
+          <t>emp_trade_nodrop</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムが装備されています</t>
+          <t>取引中止：提示したアイテムは手放せません</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item is now equipped</t>
+          <t>Trade cancelled: an offered item cannot be dropped or given away</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>emp_trade_nodrop</t>
+          <t>emp_trade_npcprop</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムは手放せません</t>
+          <t>取引中止：提示したアイテムはNPCの所有物です</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item cannot be dropped or given away</t>
+          <t>Trade cancelled: an offered item belongs to an NPC</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>emp_trade_npcprop</t>
+          <t>emp_trade_gifted</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムはNPCの所有物です</t>
+          <t>取引中止：提示したアイテムは贈り物のため取引できません</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item belongs to an NPC</t>
+          <t>Trade cancelled: an offered item is a gift and cannot be traded</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>emp_trade_gifted</t>
+          <t>emp_trade_bound</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムは贈り物のため取引できません</t>
+          <t>取引中止：提示したアイテムはキャラクターに結び付いています</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item is a gift and cannot be traded</t>
+          <t>Trade cancelled: an offered item is bound to a character</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>emp_trade_bound</t>
+          <t>emp_trade_full</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムはキャラクターに結び付いています</t>
+          <t>取引中止：受け取るアイテムに対してバッグの空きが足りません</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item is bound to a character</t>
+          <t>Trade cancelled: a bag does not have enough free slots for what it would receive</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>emp_trade_full</t>
+          <t>emp_travel_recalled_by</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>取引中止：受け取るアイテムに対してバッグの空きが足りません</t>
+          <t>{@Peer} がこの場所に来ます。画面が再読み込みされ、合流します…</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Trade cancelled: a bag does not have enough free slots for what it would receive</t>
+          <t>{@Peer} is coming to this place: the screen will reload to rejoin them…</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>emp_travel_recalled_by</t>
+          <t>emp_ui_thing_gone</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{@Peer} がこの場所に来ます。画面が再読み込みされ、合流します…</t>
+          <t>遅かったようです。他のプレイヤーが先に取りました</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>{@Peer} is coming to this place: the screen will reload to rejoin them…</t>
+          <t>Too late: someone else already took it</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>emp_ui_thing_gone</t>
+          <t>emp_base_refused</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>遅かったようです。他のプレイヤーが先に取りました</t>
+          <t>ホストに断られました。拠点または所持金では、もう支払えません。</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Too late: someone else already took it</t>
+          <t>The host refused: the base or your purse can no longer pay for this.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>emp_base_refused</t>
+          <t>emp_base_pending</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ホストに断られました。拠点または所持金では、もう支払えません。</t>
+          <t>前回の依頼はまだホストの返事を待っています。</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>The host refused: the base or your purse can no longer pay for this.</t>
+          <t>Your last request is still waiting for the host's answer.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>emp_base_pending</t>
+          <t>emp_game_version_differs</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>前回の依頼はまだホストの返事を待っています。</t>
+          <t>{0} のElinのバージョンが異なります（{1} ／ こちら {2}）。接続は許可されます。問題が起きたら同じバージョンに揃えてください。</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Your last request is still waiting for the host's answer.</t>
+          <t>{0} runs another version of Elin ({1}, here {2}). The connection is allowed; if something goes wrong, use the same version.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>emp_game_version_differs</t>
+          <t>emp_ui_sv_cfg_same_game_version</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>{0} のElinのバージョンが異なります（{1} ／ こちら {2}）。接続は許可されます。問題が起きたら同じバージョンに揃えてください。</t>
+          <t>同じElinバージョンを必須にする</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>{0} runs another version of Elin ({1}, here {2}). The connection is allowed; if something goes wrong, use the same version.</t>
+          <t>Require the same Elin version</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_same_game_version</t>
+          <t>emp_ui_sv_desc_same_game_version</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>同じElinバージョンを必須にする</t>
+          <t>オン：Elinのバージョンが違うプレイヤーを拒否。オフ：警告のうえ参加を許可。Modのバージョンは常に同じである必要があります。</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Require the same Elin version</t>
+          <t>On: players on another version of Elin are refused. Off: they are let in with a warning. The same version of the mod is always required.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_same_game_version</t>
+          <t>emp_ui_sv_cfg_guest_build</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>オン：Elinのバージョンが違うプレイヤーを拒否。オフ：警告のうえ参加を許可。Modのバージョンは常に同じである必要があります。</t>
+          <t>他のプレイヤーも建築モードを使える</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>On: players on another version of Elin are refused. Off: they are let in with a warning. The same version of the mod is always required.</t>
+          <t>Other players can use build mode</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_guest_build</t>
+          <t>emp_ui_sv_desc_guest_build</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>他のプレイヤーも建築モードを使える</t>
+          <t>オン：他のプレイヤーも拠点の建築モード（床・壁・家具・採掘・伐採）を使えます。ホストのゲームが代わりに建て、費用と素材は本人が払います。オフ：ホストだけが建てられます。</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Other players can use build mode</t>
+          <t>On: the other players can use the build mode of the base (floors, walls, furniture, mining, cutting). The game of the host builds for them; they pay the gold and the materials. Off: only the host builds.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_guest_build</t>
+          <t>emp_ui_depot_gh_help</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
-        <is>
-          <t>オン：他のプレイヤーも拠点の建築モード（床・壁・家具・採掘・伐採）を使えます。ホストのゲームが代わりに建て、費用と素材は本人が払います。オフ：ホストだけが建てられます。</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>On: the other players can use the build mode of the base (floors, walls, furniture, mining, cutting). The game of the host builds for them; they pay the gold and the materials. Off: only the host builds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>emp_ui_depot_gh_help</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
         <is>
           <t>非公開の GitHub リポジトリをデポにできます（サーバーも共有フォルダも不要、フレンドは GitHub アカウント不要）：
 1. github.com で、この世界専用の空の非公開（Private）リポジトリを作成します。
 2. そのリポジトリ用のアクセスキーを1つ作成します：Settings → Developer settings → Fine-grained tokens、このリポジトリのみ、Contents: Read and write。
-3. キーを「デポのパスワード／GitHub のキー」に貼り付け、「デポ」に github:所有者/リポジトリ と入力します。
+3. キーを「デポのキー」に貼り付け、「デポ」に github:所有者/リポジトリ と入力します。
 4. 同じ2行をフレンドに送り、フレンドもここに入力します。このキーで開けるのはこのリポジトリだけです。</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>A private GitHub repository can be the depot (no server, no shared folder, your friends need no GitHub account):
 1. On github.com, create an empty private repository, only for this world.
 2. Create one access key for it: Settings, Developer settings, Fine-grained tokens; only this repository; Contents: Read and write.
-3. Paste the key in "Depot password or GitHub key" and write github:owner/repository in "Depot".
+3. Paste the key in "Depot key" and write github:owner/repository in "Depot".
 4. Send the same two lines to your friends: they type them here too. The key only opens this one repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_key</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>GitHub がアクセスキーを拒否しました。キーの有効期限、このリポジトリが対象になっているか、「Contents: Read and write」の権限があるかを確認し、「Client Settings」で貼り付け直してください。</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>GitHub refused the access key. Check that it has not expired, that it covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_key</t>
+          <t>emp_ui_depot_gh_missing</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>GitHub がアクセスキーを拒否しました。キーの有効期限、このリポジトリが対象になっているか、「Contents: Read and write」の権限があるかを確認し、「Client Settings」で貼り付け直してください。</t>
+          <t>GitHub でデポのリポジトリが見つかりません。「Client Settings」の名前（github:所有者/リポジトリ）と、アクセスキーがそのリポジトリを対象にしているかを確認してください。</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>GitHub refused the access key. Check that it has not expired, that it covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
+          <t>GitHub does not find the repository of the depot. Check its name (github:owner/repository) in Client Settings, and that your access key covers it.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_missing</t>
+          <t>emp_ui_depot_gh_public</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>GitHub でデポのリポジトリが見つかりません。「Client Settings」の名前（github:所有者/リポジトリ）と、アクセスキーがそのリポジトリを対象にしているかを確認してください。</t>
+          <t>この GitHub リポジトリは公開されています。世界とその履歴がすべて誰にでも見えてしまいます。非公開にしてから（Settings → Danger Zone → Change visibility）、もう一度お試しください。</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>GitHub does not find the repository of the depot. Check its name (github:owner/repository) in Client Settings, and that your access key covers it.</t>
+          <t>This GitHub repository is public: your world and all its history would be visible to everyone. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_public</t>
+          <t>emp_ui_depot_gh_big</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>この GitHub リポジトリは公開されています。世界とその履歴がすべて誰にでも見えてしまいます。非公開にしてから（Settings → Danger Zone → Change visibility）、もう一度お試しください。</t>
+          <t>この世界は 20 MB を超えており、GitHub のデポには大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに保存されています。</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>This GitHub repository is public: your world and all its history would be visible to everyone. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
+          <t>This world is over 20 MB: too big for a GitHub depot. Use Elin Together Server or a shared folder instead. The save is kept on this PC.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_big</t>
+          <t>emp_ui_depot_gh_changed</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>この世界は 20 MB を超えており、GitHub のデポには大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに保存されています。</t>
+          <t>接続が切れている間に、他のプレイヤーがデポの世界をホストしてセーブしました。あなたのセーブはこのPCに残り、デポには届きません。タイトルに戻って、もう一度世界を取り出してください。</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>This world is over 20 MB: too big for a GitHub depot. Use Elin Together Server or a shared folder instead. The save is kept on this PC.</t>
+          <t>The world in the depot changed while this game was cut off: someone else hosted it and saved. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_changed</t>
+          <t>emp_ui_depot_gh_down</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>接続が切れている間に、他のプレイヤーがデポの世界をホストしてセーブしました。あなたのセーブはこのPCに残り、デポには届きません。タイトルに戻って、もう一度世界を取り出してください。</t>
+          <t>GitHub から応答がありません。接続を確認して、しばらくしてからもう一度お試しください。</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>The world in the depot changed while this game was cut off: someone else hosted it and saved. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
+          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_down</t>
+          <t>emp_ui_sv_cfg_player_kill</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>GitHub から応答がありません。接続を確認して、しばらくしてからもう一度お試しください。</t>
+          <t>プレイヤー同士で殺せる</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
+          <t>Players can kill each other</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_kill</t>
+          <t>emp_ui_sv_desc_player_kill</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>プレイヤー同士で殺せる</t>
+          <t>オン：プレイヤー（とその仲間）の攻撃で他のプレイヤーのキャラクターが死にます。オフ：致命的な一撃でも相手のHPは0で止まり、死にません。</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Players can kill each other</t>
+          <t>On: a strike of a player (or of its companions) can kill another player's character. Off: a strike that would kill it leaves it at 0 hit points, alive.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_kill</t>
+          <t>emp_ui_sv_cfg_host_manages_base</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>オン：プレイヤー（とその仲間）の攻撃で他のプレイヤーのキャラクターが死にます。オフ：致命的な一撃でも相手のHPは0で止まり、死にません。</t>
+          <t>拠点の管理はホストだけ</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>On: a strike of a player (or of its companions) can kill another player's character. Off: a strike that would kill it leaves it at 0 hit points, alive.</t>
+          <t>Only the host manages the base</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_host_manages_base</t>
+          <t>emp_ui_sv_desc_host_manages_base</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>拠点の管理はホストだけ</t>
+          <t>オン：他のプレイヤーによる拠点の操作（研究、炉の技能、政策、名前、物の設定、住民、建築モード）は拒否されます。オフ：全員がホストと同じように拠点を管理できます。拠点の放棄は常にホストだけです。</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Only the host manages the base</t>
+          <t>On: what the other players ask of the base (research, hearth skills, policies, names, settings of an object, residents, build mode) is refused. Off: every player manages the base as the host does. Leaving the base for good always stays the host's.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_host_manages_base</t>
+          <t>emp_ui_sv_cfg_duels</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>オン：他のプレイヤーによる拠点の操作（研究、炉の技能、政策、名前、物の設定、住民、建築モード）は拒否されます。オフ：全員がホストと同じように拠点を管理できます。拠点の放棄は常にホストだけです。</t>
+          <t>プレイヤー同士の決闘</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>On: what the other players ask of the base (research, hearth skills, policies, names, settings of an object, residents, build mode) is refused. Off: every player manages the base as the host does. Leaving the base for good always stays the host's.</t>
+          <t>Duels between players</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_duels</t>
+          <t>emp_ui_sv_desc_duels</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>プレイヤー同士の決闘</t>
+          <t>オン：相手キャラクターのメニューから決闘を申し込めます。誰も死なず、終了時に両者が回復し、何も失いません。オフ：決闘なし。</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Duels between players</t>
+          <t>On: a player can challenge another from the menu on its character. Nobody dies, both are healed, nothing is lost. Off: no duels.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_duels</t>
+          <t>emp_act_duel</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>オン：相手キャラクターのメニューから決闘を申し込めます。誰も死なず、終了時に両者が回復し、何も失いません。オフ：決闘なし。</t>
+          <t>決闘を申し込む</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>On: a player can challenge another from the menu on its character. Nobody dies, both are healed, nothing is lost. Off: no duels.</t>
+          <t>Challenge to a duel</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>emp_act_duel</t>
+          <t>emp_duel_invite</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>決闘を申し込む</t>
+          <t>{0} が決闘を申し込んできました。誰も死なず何も失いませんが、決闘中に使ったポーション・矢・チャージは戻りません。受けますか？</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Challenge to a duel</t>
+          <t>{0} challenges you to a duel. Nobody dies and nothing is lost, but potions, arrows and charges used during the duel stay spent. Accept?</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>emp_duel_invite</t>
+          <t>emp_duel_asked</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>{0} が決闘を申し込んできました。誰も死なず何も失いませんが、決闘中に使ったポーション・矢・チャージは戻りません。受けますか？</t>
+          <t>{0} に決闘を申し込みました…</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>{0} challenges you to a duel. Nobody dies and nothing is lost, but potions, arrows and charges used during the duel stay spent. Accept?</t>
+          <t>You challenge {0} to a duel…</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>emp_duel_asked</t>
+          <t>emp_duel_countdown</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>{0} に決闘を申し込みました…</t>
+          <t>決闘：{0} 対 {1}。3秒後に開始！</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>You challenge {0} to a duel…</t>
+          <t>Duel: {0} against {1}. It starts in 3 seconds!</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>emp_duel_countdown</t>
+          <t>emp_duel_fight</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>決闘：{0} 対 {1}。3秒後に開始！</t>
+          <t>始め！</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Duel: {0} against {1}. It starts in 3 seconds!</t>
+          <t>Fight!</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>emp_duel_fight</t>
+          <t>emp_duel_won</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>始め！</t>
+          <t>{0} が {1} との決闘に勝ちました。</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Fight!</t>
+          <t>{0} won the duel against {1}.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>emp_duel_won</t>
+          <t>emp_duel_declined</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>{0} が {1} との決闘に勝ちました。</t>
+          <t>決闘は断られました。</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>{0} won the duel against {1}.</t>
+          <t>The duel was declined.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>emp_duel_declined</t>
+          <t>emp_duel_noanswer</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>決闘は断られました。</t>
+          <t>返事がなく、決闘は行われません。</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>The duel was declined.</t>
+          <t>No answer: no duel.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>emp_duel_noanswer</t>
+          <t>emp_duel_busy</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>返事がなく、決闘は行われません。</t>
+          <t>そのプレイヤーは決闘中か取引中です。</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>No answer: no duel.</t>
+          <t>That player is already in a duel or a trade.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>emp_duel_busy</t>
+          <t>emp_duel_over</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>そのプレイヤーは決闘中か取引中です。</t>
+          <t>決闘は勝者なしで終わりました。</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>That player is already in a duel or a trade.</t>
+          <t>The duel is over, without a winner.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>emp_duel_over</t>
+          <t>emp_handover_failed</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>決闘は勝者なしで終わりました。</t>
+          <t>あなたのキャラクター {0} はこの世界で交代できませんでした（死亡しています）。セーブデータのキャラクターで遊んでいます。</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>The duel is over, without a winner.</t>
+          <t>Your character {0} could not take its place in this world (it is dead). You are playing the character of the save.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_held_btn</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>{0} が世界をホスト中</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>{0} is hosting the world</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>emp_error_connection</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>接続できませんでした。ゲームが応答しません。まだ開いているか確認して、もう一度お試しください。</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Could not connect: the game does not answer. Check that it is still open, then try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>emp_not_allowed</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>このゲームは、Steam のロビーから参加したプレイヤーだけを受け入れます。</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>This game only accepts players who joined through its Steam lobby.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>emp_connection_no_server</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>そのゲームはまだ開かれていません。しばらくしてからもう一度お試しください。</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>That game is not open yet. Try again in a moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>emp_zone_session_empty</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ここには他のプレイヤーがいなくなりました</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>No other player is here anymore</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>emp_ui_timeout_steam</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>ゲームが応答しません。相手が退出したか、接続が切れた可能性があります。</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>The game does not answer: its player may have left or lost the connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>emp_trade_nothing_to_offer</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>提示できるアイテムがありません。</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>You have nothing you can offer.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D257"/>
+  <dimension ref="A1:D263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4819,6 +4820,108 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>emp_ui_reconnecting</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>接続が切れました。ゲームに戻っています…</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Connection lost. Getting you back into the game…</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>emp_ui_reconnect_cancel</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>emp_ui_reconnect_failed</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>ゲームに戻れませんでした。3分間応答がありません。終了した可能性があります。</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Could not get back into the game: it has not answered for 3 minutes. It may have ended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>emp_ui_save_kept</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>進行状況は参加中のゲームに保存されます。</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Your progress is kept by the game you joined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_auto_reconnect</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>接続が切れたプレイヤーは自動で戻る</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Players come back by themselves after a connection loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_auto_reconnect</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>オン：接続が切れたプレイヤーは3分間、自動で再参加を試みます。オフ：タイトル画面に戻ります。</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>On: a player who loses the connection joins the game again by itself, for 3 minutes. Off: it goes back to the title screen.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D263"/>
+  <dimension ref="A1:D270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4922,6 +4922,125 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_auto_host</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ワールドを読み込むと自動でフレンドに公開する</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>The game opens to friends by itself when a world is loaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_auto_host</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>オン：「サーバー起動」を押さなくても、ワールドを読み込むとフレンドが参加できます（土地の確保が必要）。オフ：ホストが自分でサーバーを起動します。</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>On: friends can join as soon as the world is loaded, without starting the server by hand (the world needs a claimed land). Off: the host starts the server itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_auto_save</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>他のプレイヤーがいる間、ワールドを自動で保存する</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>The world is saved by itself while others play</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_auto_save</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>オン：他のプレイヤーがいる間は2分ごと（保存が重い場合は5分ごと）、最後の一人が抜けた時にも保存します。オフ：ホストが保存した時だけ。</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>On: every 2 minutes while another player is in the game (5 when a save is slow), and when the last one leaves. Off: only when the host saves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>emp_ui_load_blocked</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>みんなで遊んでいる間は、セーブデータからロードできません。</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>A shared game cannot be loaded from a save while players are together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_join_btn</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>{0} に参加</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Join {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_join_fail</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>{0} が世界を持っていますが、ゲームがまだ開いていません。少し待ってもう一度お試しください。相手のゲームが止まった場合、世界は3分以内に空きます。</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>{0} has the world, but their game is not open yet. Try again in a moment. If their game stopped, the world is free again within 3 minutes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D270"/>
+  <dimension ref="A1:D271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5041,6 +5041,23 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>emp_ui_box_far</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>この箱は世界共通で、ホストが保管しています。ホストから離れて他のプレイヤーと一緒にいる間は、入れた物はホストに届きますが、ホストのマップに戻るまで表示されません。</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>This chest belongs to the whole world and is kept by the host. With other players away from the host, what you put in arrives there, but it only shows again once you are back on the host's map.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D271"/>
+  <dimension ref="A1:D277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5058,6 +5058,108 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_own_sleep</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>みんな自分のために眠る</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Everyone sleeps for themselves</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_own_sleep</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>オン：ベッドに入ったプレイヤーは誰も待たずにすぐ眠ります。全員が同時に眠ったときだけ、ワールドの夜が明けます。オフ：全員が互いを待ちます。</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>On: a player who goes to bed sleeps at once, without waiting for anyone. The night only passes for the world when every player is asleep at the same time. Off: everyone waits for everyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_time_jumps_together</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>時間は全員一緒のときだけ飛ぶ</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Time only jumps when everyone jumps</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_time_jumps_together</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>オン：ワールドマップの一歩は、全プレイヤーが一緒に旅しているときだけワールドの日付を進めます。それ以外は旅人が自分のターンだけを払います。オフ：誰の一歩でも全員に3時間が加わります。</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>On: a step on the world map only moves the date of the world when all the players travel on it together. Otherwise the traveller pays its own turns and the date stays. Off: every step of anyone adds 3 hours for all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_dump_spares_belt</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>自動収納は手とベルトに触れない</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Auto-dump spares hand and tool belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_dump_spares_belt</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>オン：自動収納は、手に持っている物とツールベルトの中身を収納しません（ホットバーと同じ）。オフ：ゲーム本来の動作。</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>On: auto-dump leaves what you hold and what is in your tool belt, as it leaves the hotbar. Off: as in the game.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D277"/>
+  <dimension ref="A1:D278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5160,6 +5160,23 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>emp_ui_travel_no_date</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>仲間は別の場所にいる。この旅では日付は進まない。</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Your friends are elsewhere: your trip does not move the date.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D278"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5177,6 +5177,40 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>emp_ui_bill_paid</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>{0}が請求書を支払いました：{1}（{2}）</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>{0} paid a bill: {1} ({2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>emp_ui_bill_already_paid</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>この請求書はすでに支払い済みです。所持金は減っていません。</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>This bill is already paid: nothing was taken from you.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5211,6 +5211,57 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>emp_ui_sleep_alone</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>眠った。世界の時間は進まなかった：{0} がまだ起きている。</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>You slept. The world did not move on: {0} still awake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>emp_ui_sleep_count</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>{0} は眠っている（{1}/{2}）</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>{0} is asleep ({1} of {2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>emp_ui_sleep_all</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>全員が眠った：夜が過ぎていく。</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Everyone is asleep: the night passes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5262,6 +5262,57 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>emp_ui_resync</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>マップを同期し直しています…</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Bringing the map up to date…</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_auto_resync</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>マップを自動で修復</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Repair the map by itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_auto_resync</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>オン：マップがホストと食い違ったプレイヤー（アイテムやキャラクターの欠落）は、自動でマップを読み込み直します（30秒に1回まで）。オフ：食い違いはログに書かれるだけです。</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>On: a player whose map no longer matches the host's (a missing item or character) loads it again by itself, at most once every 30 seconds. Off: the difference is only written to the log.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D286"/>
+  <dimension ref="A1:D292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5313,6 +5313,108 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>emp_ui_bank_deposit</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>{0}が銀行に{1}を預けました</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>{0} put {1} in the bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>emp_ui_bank_withdraw</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>{0}が銀行から{1}を引き出しました</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>{0} took {1} out of the bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_world_copy</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>他のプレイヤーがワールドのコピーを保持する</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>The other players keep a copy of the world</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_world_copy</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>オン：自動セーブのたびに、各プレイヤーのPCが自分のセーブとは別の場所にワールドのコピーを保存します。オフ：ワールドはホストのPCにしかありません。</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>On: after each automatic save, every player's PC keeps a copy of the world, outside its own saves. Off: the world is on the host's PC only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_shared_tax</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>税金は最も名声の高いプレイヤーで計算</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Tax on the most famous player</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_shared_tax</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>オン：毎月の税金は、接続中のプレイヤーの中で最も高い名声で計算されます。オフ：ホストの名声で計算されます（ゲーム本来の動作）。</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>On: the monthly tax is computed on the highest fame among the connected players. Off: on the host's fame, as the game does.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D292"/>
+  <dimension ref="A1:D294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5415,6 +5415,40 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_soft_recall</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ホストが来てもワールドを読み込み直さない（新機能）</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>No world reload when the host joins a player (new)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_soft_recall</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>オン：ホストが、プレイヤーが一人でいるマップに入っても、そのプレイヤーはその場に残り、ワールド全体を読み込み直しません。食い違いがあれば、これまでどおりワールドを読み込みます。オフ：そのたびにワールドを読み込み直します。</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>On: when the host walks onto the map a player is on alone, that player stays where it is and does not load the whole world again. Should anything not match, the world is loaded as before. Off: the world is loaded again each time.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -5423,12 +5423,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ホストが来てもワールドを読み込み直さない（新機能）</t>
+          <t>ホストと合流してもワールドを読み込み直さない（新機能）</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>No world reload when the host joins a player (new)</t>
+          <t>No world reload when the host and a player meet again (new)</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>オン：ホストが、プレイヤーが一人でいるマップに入っても、そのプレイヤーはその場に残り、ワールド全体を読み込み直しません。食い違いがあれば、これまでどおりワールドを読み込みます。オフ：そのたびにワールドを読み込み直します。</t>
+          <t>オン：ホストが、プレイヤーが一人でいるマップに入るとき、またはそのプレイヤーがホストのいるマップに入るとき、ワールド全体を読み込み直しません（その場に残るか、そのマップだけを読み込みます）。食い違いがあれば、これまでどおりワールドを読み込みます。オフ：そのたびにワールドを読み込み直します。</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>On: when the host walks onto the map a player is on alone, that player stays where it is and does not load the whole world again. Should anything not match, the world is loaded as before. Off: the world is loaded again each time.</t>
+          <t>On: when the host walks onto the map a player is on alone, or that player walks into the map the host is on, the player does not load the whole world again: it stays where it is, or loads that one map. Should anything not match, the world is loaded as before. Off: the world is loaded again each time.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5449,6 +5449,278 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_publish_mods</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>ゲームのMod一覧を公開する</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Show the mods of the game to the players</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_publish_mods</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>オン：参加前（ゲーム一覧）と参加時にMod一覧が伝えられ、拒否された場合はどのModが違うかが名前で表示されます。デポから取ったワールドではデポの一覧（modlist.txt）を使います。オフ：何も伝えません。</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>On: the list of mods is known before joining (list of games) and when joining, and a player who is refused is told which mods differ, by name. For a world taken from a depot it is the depot's list (modlist.txt). Off: nothing is said.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_fetch_mods</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ゲームのModを自動で取得する（新機能）</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Fetch the mods of the game by itself (new)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_desc_fetch_mods</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>オン：参加するゲームにあってここに無いワークショップModを、サブスクライブせずにダウンロードし、そのゲームのModだけでElinを1回再起動して自動で戻ります。次の起動で自分のMod一覧に戻ります。オフ：違うModの名前が表示されるだけです。</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>On: Workshop mods of the game you join that are missing here are downloaded without subscribing, Elin restarts once with exactly the mods of that game and comes back by itself. Your own mod list is back at the next start. Off: you are only told which mods differ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_lobby</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Mod {0} 個</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>{0} mods</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_lobby_missing</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Mod {0} 個、うち {1} 個がここにありません</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>{0} mods, {1} missing here</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_world</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>このワールドのModのうち {0} 個がここで読み込まれていません：{1}。一覧はログにあります。</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>{0} mods of this world are not loaded here: {1}. The list is in the log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_missing</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>ここに無いホストのMod（{0}）：{1}</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Mods of the host missing here ({0}): {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_hand</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>手動で入れる必要があるMod（{0}）：{1}</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Mods to install by hand ({0}): {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_extra</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>ホストに無いここのMod（{0}）：{1}</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Mods only here, not on the host ({0}): {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_fetching</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ゲームのModをダウンロード中 {0}/{1}：{2} {3}%（Escで中止）</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Downloading the mods of the game {0}/{1}: {2} {3}% (Esc to cancel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_fetch_failed</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>ゲームのModをダウンロードできませんでした。何も変更していません。</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>The mods of the game could not be downloaded. Nothing was changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_restart</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ElinはゲームのModで再起動し、自動でゲームに戻ります。再起動しない場合は、Elinをもう一度起動してください。</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Elin restarts with the mods of the game and comes back to it by itself. If it does not start, start Elin again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_restart_manual</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Elinを閉じます。もう一度起動してください：ゲームのModで自動的にゲームへ戻ります。</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Elin closes. Start it again: it comes back to the game by itself, with its mods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_session</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>今回のElinはマルチプレイのゲームのModで動いています。次の起動で自分のMod一覧に戻ります。</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Elin runs with the mods of the multiplayer game this time. Your own mod list is back at the next start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>emp_ui_mods_session_locked</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>このセッション中はMod一覧を保存しません。次の起動で自分の一覧に戻ります。</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>The mod list is not saved during this session: your own is back at the next start of Elin.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9510" yWindow="2685" windowWidth="31695" windowHeight="18195" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D310"/>
+  <dimension ref="A1:D312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5695,12 +5695,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>今回のElinはマルチプレイのゲームのModで動いています。次の起動で自分のMod一覧に戻ります。</t>
+          <t>今回のElinはマルチプレイのゲームのModで動いています。次の起動では自分のMod一覧に戻ります。この再起動を次回からなくすには、クライアント設定の「ゲームのModを残す」をオンにしてください。</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Elin runs with the mods of the multiplayer game this time. Your own mod list is back at the next start.</t>
+          <t>Elin runs with the mods of the multiplayer game this time. Your own mod list is back at the next start. To skip this restart next time, tick "Keep the mods of the game" in Client Settings.</t>
         </is>
       </c>
     </row>
@@ -5718,6 +5718,40 @@
       <c r="D310" t="inlineStr">
         <is>
           <t>The mod list is not saved during this session: your own is back at the next start of Elin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_keep_mods</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ゲームのModを残す（ワークショップでサブスクライブ）</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Keep the mods of the game (subscribe on the Workshop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_desc_keep_mods</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>オン：参加したゲームのModをSteamアカウントでサブスクライブし、自分のMod一覧でも有効のままにします。最初の一回だけElinが再起動し、その後はElinを閉じても同じゲームに再起動なしで参加できます。やめるには、ワークショップでサブスクライブを解除してください。オフ：サブスクライブせずに取得し、Elinを起動するたびに最初の参加で再起動します。</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>On: your Steam account subscribes to the mods of the game you join and they stay on in your own mod list. Elin still restarts once, the first time; after that you join the same game again with no restart, even after closing Elin. To undo, unsubscribe on the Workshop. Off: they are fetched without subscribing and Elin restarts at the first join of every start.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D312"/>
+  <dimension ref="A1:D315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5755,6 +5755,57 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_takeover</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>ホストが抜けたら他のプレイヤーが引き継ぐ</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Another player takes over when the host leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_takeover</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>オン：ホストが抜けると、プレイヤーの一人が自分のコピーからワールドを開き、ゲームはそこで続きます（上の「ワールドのコピー」が必要）。オフ：ホストが抜けるとゲームは終わります。</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>On: when the host leaves, a player opens the world from its copy and the game goes on there (needs the copy of the world, above). Off: the game ends with its host.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_takeover_begin</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>ホストが抜けました。あなたがワールドを引き継ぎます。まもなくここでゲームが続きます。</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>The host left. You are taking the world over: the game goes on here in a moment.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D315"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5806,6 +5806,23 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_takeover_leaving</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>退出中：他のプレイヤーに最後のセーブを渡しています…</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Leaving: the other players are getting the last save…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="9510" yWindow="2685" windowWidth="31695" windowHeight="18195" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="General" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D316"/>
+  <dimension ref="A1:D317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5823,6 +5823,23 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>emp_ui_limited_bought</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>それはもう買いました。</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>You already bought this one.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5840,6 +5840,57 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>emp_story_share</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>{0}の分け前</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>{0}'s share</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_once_per_player</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>一度きりのものを各プレイヤーに</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Once per world = once per player</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_once_per_player</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>オン：店の限定商品とストーリーの報酬を、各プレイヤーが一度ずつ得られます。オフ：最初のプレイヤーだけ（原作通り）。</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>On: what a shop sells only once and what the story gives (quest rewards, dialog gifts) go once to each player. Off: only the first player, as the game does.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D320"/>
+  <dimension ref="A1:D321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5891,6 +5891,23 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>emp_takeover_rejoin</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>別のプレイヤーがこの世界を引き継ぎました。そのゲームに参加します…</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Another player took this world over. Joining its game…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5908,6 +5908,40 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>emp_story_share_got</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>物語の報酬の分け前を受け取った：{0}</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>You receive your share of what the story gave: {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>emp_story_share_mail</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>物語の報酬の分け前（{0}）が拠点の郵便受けに届く。</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Your share of what the story gave ({0}) is sent to the mail of the base.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D323"/>
+  <dimension ref="A1:D327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5942,6 +5942,74 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>emp_ui_report</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>不具合レポートを作成</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Prepare a bug report</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>emp_ui_report_desc</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ゲームとModのログをまとめたzipをデスクトップに作成します（セーブデータや設定ファイルは含みません）。問題を報告するときに送ってください。</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Writes one zip on your desktop with the logs of the game and of the mod (no save, no settings file). Send it when you report a problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>emp_ui_report_done</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>レポートを作成しました：{0}</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Bug report written: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>emp_ui_report_failed</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>レポートを作成できませんでした。</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>The bug report could not be written.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D327"/>
+  <dimension ref="A1:D331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6010,6 +6010,74 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_bills</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>未払いの税金請求書：カウント {0}、実在 {1}（修復する）</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Unpaid tax bills: counted {0}, existing {1} (repair)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_bills_desc</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>カウントが実在する請求書より多い場合（以前の不具合）、実在する数まで下げます。増えることはありません。</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>When the count is above the bills that exist (an old defect), it is brought down to them. It is never raised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_bills_done</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>支払えない請求書 {0} 件をカウントから外しました。</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>{0} bill(s) that nothing could pay were taken off the count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_bills_none</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>カウントは実在する請求書と一致しています。</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>The count matches the bills that exist.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D331"/>
+  <dimension ref="A1:D336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6078,6 +6078,91 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_delete</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>キャラクターを削除する</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Delete a character</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_delete_confirm</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>#1 を削除しますか？持ち物も一緒に消えます。仲間はこの世界に残ります。</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Delete #1? What it carries goes with it. Its companions stay in this world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>emp_ui_chara_deleted</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>キャラクターを削除しました。</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>The character was deleted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_delete_chara</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>プレイヤーが自分のキャラクターを削除できる</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Players can delete their characters</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_delete_chara</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>キャラクター選択の一覧から（二度確認）。持ち物も消え、仲間は世界に残る。</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>From the list of characters (asked twice). What it carries goes too; its companions stay in the world.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D336"/>
+  <dimension ref="A1:D337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6163,6 +6163,23 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>emp_world_setting_host</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ワールド設定はホストが決めます。変更は保存されませんでした。</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>World settings are the host's: your changes were not kept.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D337"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6180,6 +6180,40 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_auto_combat_per_player</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>自動戦闘はそれぞれのプレイヤーが自分の仲間を守る</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Each player's auto combat protects its own</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_auto_combat_per_player</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>オン：致命的な一撃から守られるのは、自動戦闘をしているプレイヤーとその仲間です。戦術とスタミナもそのプレイヤーのもの。オフ：ホストの自動戦闘が全員を守り、ゲストの自動戦闘は誰も守りません。</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>On: auto combat saves from a deadly hit the player who runs it and its companions, with that player's tactics and stamina. Off: the host's auto combat protects everyone, a guest's protects no one.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D339"/>
+  <dimension ref="A1:D324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -527,12 +527,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>切断: ピアが無応答です</t>
+          <t>切断：相手の応答がありません</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Disconnected: inactive peer</t>
+          <t>Disconnected: no answer</t>
         </is>
       </c>
     </row>
@@ -544,12 +544,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>切断: 無効なソースデータ</t>
+          <t>切断：データが一致しません</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Disconnected: invalid source</t>
+          <t>Disconnected: the data does not match</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>切断: 無効なゾーン</t>
+          <t>切断：無効なマップです</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Disconnected: invalid zone</t>
+          <t>Disconnected: invalid map</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ネットワークセッションの初期化に失敗しました</t>
+          <t>接続を開始できませんでした</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Network session initialization failed</t>
+          <t>Could not start the connection</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>切断: 新しいホストが選出されました</t>
+          <t>切断：新しいホストが決まりました</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Disconnected: new host elected</t>
+          <t>Disconnected: there is a new host</t>
         </is>
       </c>
     </row>
@@ -617,5600 +617,5343 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cannot join while connected</t>
+          <t>You can't join while connected.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>emp_dc_rejoin_failed</t>
+          <t>emp_dc_remote_closed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>切断: 再接続に失敗しました</t>
+          <t>切断：相手が接続を閉じました</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Disconnected: rejoin failed</t>
+          <t>Disconnected: the other side closed the connection</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>emp_dc_remote_closed</t>
+          <t>emp_dc_timeout</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>切断: リモートが接続を閉じました</t>
+          <t>切断：応答がありません</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Disconnected: remote closed connection</t>
+          <t>Disconnected: no answer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>emp_dc_timeout</t>
+          <t>emp_tab_lobby</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>切断: 接続がタイムアウトしました</t>
+          <t>ロビー</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Disconnected: connection timed out</t>
+          <t>Lobby</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>emp_inactive</t>
+          <t>emp_tab_server</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>応答なしの接続</t>
+          <t>サーバー</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Unresponsive connection</t>
+          <t>Server</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emp_invalid_zone</t>
+          <t>emp_tab_session</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ゾーンデータが無効です</t>
+          <t>セッション</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zone data is invalid</t>
+          <t>Session</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emp_phase_auth</t>
+          <t>emp_ui_combat_decide</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>認証中…</t>
+          <t>次の行動を選択してください。</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Authenticating...</t>
+          <t>Decide your next action.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>emp_phase_connecting</t>
+          <t>emp_ui_combat_enter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>接続中…</t>
+          <t>戦闘モードに入りました。</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Connecting...</t>
+          <t>Enter combat mode.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emp_phase_disconnected</t>
+          <t>emp_ui_combat_exit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>切断済み</t>
+          <t>戦闘モードを終了しました。</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Disconnected</t>
+          <t>Exit combat mode.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emp_phase_disconnecting</t>
+          <t>emp_ui_combat_wait</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>切断中…</t>
+          <t>他のプレイヤーの行動選択を待っています。</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Disconnecting...</t>
+          <t>Wait for others to decide their next action.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>emp_phase_host_listening</t>
+          <t>emp_ui_config_changed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>待ち受け中…</t>
+          <t>Elin Together の設定が変更されました</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Listening...</t>
+          <t>Elin Together settings changed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>emp_phase_host_ready</t>
+          <t>emp_ui_config_reset</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ホスト準備完了</t>
+          <t>Elin Together の設定をバージョン {0} 用に初期化しました。</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Host Ready</t>
+          <t>Elin Together settings were reset for version {0}.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emp_phase_lobby_creating</t>
+          <t>emp_ui_connected_players</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ロビーを作成中…</t>
+          <t>接続中のプレイヤー</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Creating lobby...</t>
+          <t>Connected Players</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emp_phase_lobby_joining</t>
+          <t>emp_ui_invalid_chara</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ロビーに参加中…</t>
+          <t>無効なキャラ：プレイヤー {0}、UID {1}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Joining lobby...</t>
+          <t>Invalid character: player {0}, UID {1}.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emp_phase_none</t>
+          <t>emp_ui_lobby_desc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>待機中</t>
+          <t>{0}のゲーム {1}（{2}人）、{3}</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Idle</t>
+          <t>{0}'s game {1}, {2} player(s), at {3}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>emp_phase_player_prep</t>
+          <t>emp_ui_lobby_tally</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>プレイヤーを準備中…</t>
+          <t>オンラインのプレイヤー: {0}</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Preparing Player...</t>
+          <t>Players online: {0}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>emp_phase_receiving_world</t>
+          <t>emp_ui_ping_format</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ワールドを受信中…</t>
+          <t>遅延: {0}ms{1}</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Receiving World...</t>
+          <t>Ping: {0}ms{1}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>emp_phase_reconnecting</t>
+          <t>emp_ui_ping_host</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>再接続中…</t>
+          <t>遅延: N/A（ホスト）</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reconnecting...</t>
+          <t>Ping: N/A (Host)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>emp_phase_source_synced</t>
+          <t>emp_ui_quality_format</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ソース同期完了</t>
+          <t xml:space="preserve"> | 品質: {0}</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Source Synced</t>
+          <t xml:space="preserve"> | Quality: {0}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>emp_phase_source_validating</t>
+          <t>emp_ui_session</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ソースを検証中…</t>
+          <t>ゲーム情報</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Validating source...</t>
+          <t>Game Info</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>emp_phase_synchronized</t>
+          <t>emp_ui_sv_cfg_shared_speed</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>同期完了</t>
+          <t>平均速度を共有</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Synchronized</t>
+          <t>Shared Average Speed</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>emp_phase_unknown</t>
+          <t>emp_ui_sv_cfg_turn_combat</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>ターン制戦闘</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Turn-Based Combat</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>emp_phase_world_loading</t>
+          <t>emp_ui_sv_dc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ワールドを読み込み中…</t>
+          <t>切断</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Loading World...</t>
+          <t>Disconnect</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>emp_source_invalid</t>
+          <t>emp_ui_sv_invite</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ソースデータが一致しません</t>
+          <t>フレンドを招待</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Source data mismatch</t>
+          <t>Invite Friend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>emp_tab_lobby</t>
+          <t>emp_ui_sv_start</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ロビー</t>
+          <t>サーバー起動</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lobby</t>
+          <t>Start Server</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>emp_tab_server</t>
+          <t>emp_ui_tab_lobby</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>サーバー</t>
+          <t>ロビー</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Lobby</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>emp_tab_session</t>
+          <t>emp_ui_tab_server</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>セッション</t>
+          <t>サーバー設定</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Server Setting</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>emp_ui_combat_decide</t>
+          <t>emp_ui_title</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>次の行動を選択してください。</t>
+          <t>Elin Together</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Decide your next action.</t>
+          <t>Elin Together</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>emp_ui_combat_enter</t>
+          <t>emp_ui_unclaimed_zone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>戦闘モードに入りました。</t>
+          <t>サーバーを開始するには、先に土地を所有する必要があります。</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enter combat mode.</t>
+          <t>You need to claim a land before you start a server.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>emp_ui_combat_exit</t>
+          <t>emp_version_mismatch</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>戦闘モードを終了しました。</t>
+          <t>Elin Together のバージョンが違います</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Exit combat mode.</t>
+          <t>Elin Together versions differ.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>emp_ui_combat_wait</t>
+          <t>emp_ui_ping</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>他のプレイヤーの行動選択を待っています。</t>
+          <t>{0} が地点をマークしました。</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wait for others to decide their next action.</t>
+          <t>{0} pinged a location.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>emp_ui_config_changed</t>
+          <t>emp_ui_ping_keymap</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Elin Together の設定が変更されました</t>
+          <t>ピンキー設定: {0}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Elin Together configuration changed</t>
+          <t>Bind Ping Key: {0}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>emp_ui_config_open</t>
+          <t>emp_connecting_host</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>設定を編集</t>
+          <t>ホスト {@Peer} に接続中…</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Edit Configuration</t>
+          <t>Connecting to host {@Peer}…</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>emp_ui_config_reset</t>
+          <t>emp_player_connected</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Elin Together の設定が {0} にリセットされました</t>
+          <t>プレイヤー {@Peer} が接続しました</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Elin Together configuration has been resetted to {0}</t>
+          <t>Player {@Peer} connected</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>emp_ui_connected_players</t>
+          <t>emp_player_disconnected</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>接続中のプレイヤー</t>
+          <t>プレイヤー {@Peer} が切断しました
+{DisconnectInfo}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Connected Players</t>
+          <t>Player {@Peer} disconnected
+{DisconnectInfo}</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>emp_ui_invalid_chara</t>
+          <t>emp_lobby_join_request</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>無効なキャラクター: プレイヤー {0}, UID {1}</t>
+          <t>ロビー参加リクエストを受信しました {LobbyId}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Invalid character: Player {0}, UID {1}</t>
+          <t>Received lobby join request {LobbyId}</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>emp_ui_lobby_desc</t>
+          <t>emp_lobby_joined</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{0} のゲーム  {1}、{2} 人プレイ、場所: {3}</t>
+          <t>ロビーに参加しました、バージョン: {EmpVersion}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{0}'s Game {1} with {2} Player, at {3}</t>
+          <t>Joined lobby, version: {EmpVersion}</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>emp_ui_lobby_tally</t>
+          <t>emp_lobby_state_changed</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>オンラインプレイヤー総数: {0}</t>
+          <t>プレイヤーのロビー状態が変更されました
+{@LobbyState}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Total Online Players : {0}</t>
+          <t>Player lobby state changed
+{@LobbyState}</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>emp_ui_ping_format</t>
+          <t>emp_temp_folder_path</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>遅延: {0}ms{1}</t>
+          <t>一時フォルダのパスを更新しました
+{Path}</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ping: {0}ms{1}</t>
+          <t>Temp folder path updated
+{Path}</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>emp_ui_ping_host</t>
+          <t>emp_server_started</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>遅延: N/A（ホスト）</t>
+          <t>サーバーが起動しました</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ping: N/A (Host)</t>
+          <t>Server started</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>emp_ui_quality_format</t>
+          <t>emp_lobby_created</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | 品質: {0}</t>
+          <t>Steamロビーを作成しました</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | Quality: {0}</t>
+          <t>Steam lobby created</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>emp_ui_session</t>
+          <t>emp_wait_zone</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>セッション情報</t>
+          <t>マップを待っています…</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Session Info</t>
+          <t>Waiting for the map…</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_shared_speed</t>
+          <t>emp_zone_change</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>平均速度を共有</t>
+          <t>ゾーンを切り替え中…</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Shared Average Speed</t>
+          <t>Switching zone…</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_turn_combat</t>
+          <t>emp_party_gather</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ターン制戦闘</t>
+          <t>旅立つ前に、仲間を集めなければなりません。</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Turn-Based Combat</t>
+          <t>You must gather your party before you set out.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>emp_ui_sv_dc</t>
+          <t>emp_accept_failed</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>切断</t>
+          <t>接続を受け付けられませんでした</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Disconnect</t>
+          <t>Could not accept the connection.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>emp_ui_sv_invite</t>
+          <t>emp_disconnected_host</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>フレンドを招待</t>
+          <t>ホストから切断されました
+{0}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Invite Friend</t>
+          <t>Disconnected from host
+{0}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>emp_ui_sv_start</t>
+          <t>emp_dc_host_kick</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>サーバー起動</t>
+          <t>切断: ホストによりキックされました</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Start Server</t>
+          <t>Disconnected: Kicked by host</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>emp_ui_tab_lobby</t>
+          <t>emp_ui_tab_client</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ロビー</t>
+          <t>クライアント設定</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lobby</t>
+          <t>Client Settings</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>emp_ui_tab_server</t>
+          <t>emp_tab_client</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>サーバー設定</t>
+          <t>クライアント</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Server Setting</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>emp_ui_title</t>
+          <t>emp_ui_kick</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Elin Together</t>
+          <t>キック</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Elin Together</t>
+          <t>Kick</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>emp_ui_unclaimed_zone</t>
+          <t>emp_ui_ping_action</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ゾーンを確保してからサーバーを起動してください！</t>
+          <t>ピン</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Server can only be started after claiming a zone!</t>
+          <t>Ping</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>emp_version_mismatch</t>
+          <t>emp_ui_unknown_player</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Elin Together のビルドバージョンが一致しません</t>
+          <t>プレイヤー {0}</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Elin Together build version mismatch</t>
+          <t>Player {0}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>emp_ui_ping</t>
+          <t>emp_ui_source_mismatch_header</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{0} が地点をマークしました。</t>
+          <t>データが一致しません — {0} 件</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{0} pinged a location.</t>
+          <t>The data does not match: {0} differences</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>emp_ui_ping_keymap</t>
+          <t>emp_ui_source_mismatch_sources</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ピンキー設定: {0}</t>
+          <t>データの違い：</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bind Ping Key: {0}</t>
+          <t>Different data:</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>emp_connecting_host</t>
+          <t>emp_ui_source_mismatch_plugins</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ホスト {@Peer} に接続中…</t>
+          <t>プラグインの違い：</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Connecting to host {@Peer}…</t>
+          <t>Different plugins:</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>emp_player_connected</t>
+          <t>emp_ui_source_mismatch_files</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>プレイヤー {@Peer} が接続しました</t>
+          <t>ファイルの違い：</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Player {@Peer} connected</t>
+          <t>Different files:</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>emp_player_disconnected</t>
+          <t>emp_ui_source_mismatch_more</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>プレイヤー {@Peer} が切断しました
-{DisconnectInfo}</t>
+          <t>…ほか {0} 件</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Player {@Peer} disconnected
-{DisconnectInfo}</t>
+          <t>...and {0} more</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>emp_lobby_join_request</t>
+          <t>emp_ui_source_mismatch_continue</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ロビー参加リクエストを受信しました {LobbyId}</t>
+          <t>それでも続けますか？</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Received lobby join request {LobbyId}</t>
+          <t>Join anyway?</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>emp_lobby_joined</t>
+          <t>emp_validation_none</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ロビーに参加しました、バージョン: {EmpVersion}</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Joined lobby, version: {EmpVersion}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>emp_lobby_state_changed</t>
+          <t>emp_validation_sources</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>プレイヤーのロビー状態が変更されました
-{@LobbyState}</t>
+          <t>ソース</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Player lobby state changed
-{@LobbyState}</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>emp_temp_folder_path</t>
+          <t>emp_validation_plugins</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>一時フォルダのパスを更新しました
-{Path}</t>
+          <t>プラグイン</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Temp folder path updated
-{Path}</t>
+          <t>Plugin</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>emp_server_started</t>
+          <t>emp_validation_all</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>サーバーが起動しました</t>
+          <t>すべて</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Server started</t>
+          <t>All</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>emp_lobby_created</t>
+          <t>emp_ui_reconnect</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Steamロビーを作成しました</t>
+          <t>再接続</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Steam lobby created</t>
+          <t>Reconnect</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>emp_wait_zone</t>
+          <t>emp_dc_reconnect_request</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ゾーン状態の同期待機中…</t>
+          <t>再接続</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Waiting on zone state sync…</t>
+          <t>Reconnect</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>emp_zone_change</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ゾーンを切り替え中…</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Switching zone…</t>
+          <t>emp_lobby_create_failed</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>Steam ロビーを作れませんでした：{Result}
+あとでもう一度試してください。</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>Could not create the Steam lobby: {Result}
+Try again later.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>emp_party_gather</t>
+          <t>emp_lobby_enter_failed</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>仲間を集めてから出発してください</t>
+          <t>Steam ロビーに入れませんでした：{Response}</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>You must gather your party before venturing forth</t>
+          <t>Could not enter the Steam lobby: {Response}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>emp_accept_failed</t>
+          <t>emp_lobby_already_joined</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>接続の受け入れに失敗しました</t>
+          <t>すでにそのロビーにいます</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Failed to accept connection</t>
+          <t>You are already in that lobby.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>emp_disconnected_host</t>
+          <t>emp_ui_quest_client</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ホストから切断されました
-{0}</t>
+          <t>このクエストはホストしか開始できない。</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Disconnected from host
-{0}</t>
+          <t>Only the host can start this quest.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="60" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>emp_dc_host_kick</t>
+          <t>emp_dc_version_mismatch</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>切断: ホストによりキックされました</t>
+          <t>切断: 無効なVersion</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Disconnected: Kicked by host</t>
+          <t>Disconnected: invalid version</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>emp_ui_tab_client</t>
+          <t>emp_dc_act_mismatch</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>クライアント設定</t>
+          <t>切断：MODが一致しません</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Client Settings</t>
+          <t>Disconnected: the mods differ</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>emp_tab_client</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>クライアント</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Client</t>
+          <t>emp_ui_reject_acts</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>参加できません：MODが一致しません（{0}）
+ホストと同じMODを入れてください。</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>Could not join: the mods differ ({0}).
+Install the same mods as the host.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>emp_ui_kick</t>
+          <t>emp_ui_reject_integrity</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>キック</t>
+          <t>参加できません：ホストが厳密なチェックをオンにしていて、データが一致しません（{0}）</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Kick</t>
+          <t>Could not join: the host checks everything and your data does not match ({0}).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>emp_ui_ping_keymap</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>ピンキー設定: {0}</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Bind Ping Key: {0}</t>
+          <t>emp_version_rejected_host</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>{0} の参加を断りました
+バージョンが違います
+ホストのMOD：{1}
+ホストのゲーム：{2}</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>{0} was refused.
+Versions differ.
+Host mod: {1}
+Host game: {2}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>emp_ui_ping_action</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>ピン</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Ping</t>
+          <t>emp_version_rejected_client</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>参加できません：バージョンが違います
+MOD：自分 {0} / ホスト {1}
+ゲーム：自分 {2} / ホスト {3}
+古いほうを更新してから、もう一度試してください。</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>Could not join: versions differ.
+Mod: yours {0}, host {1}
+Game: yours {2}, host {3}
+Whoever is older must update, then try again.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>emp_ui_unknown_player</t>
+          <t>emp_ui_sleep_request</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>プレイヤー {0}</t>
+          <t>全員が寝るのを待っています…</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Player {0}</t>
+          <t>Waiting for everyone to go to bed...</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_header</t>
+          <t>emp_ui_sleep_wish</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ソース検証失敗 — {0} 件の不一致</t>
+          <t>{0}が眠りたがっています（{1}/{2}）</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Source validation failed — {0} mismatches</t>
+          <t>{0} wants to sleep ({1}/{2})</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_sources</t>
+          <t>emp_ui_sleep_cancel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ソース不一致:</t>
+          <t>{0}が目を覚ましました（{1}/{2}）</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Source mismatches:</t>
+          <t>{0} woke up ({1}/{2})</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_plugins</t>
+          <t>emp_travel_requesting</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>プラグイン不一致:</t>
+          <t>ホストに単独行動を頼んでいます…</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Plugin mismatches:</t>
+          <t>Asking the host to let you go alone…</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_files</t>
+          <t>emp_travel_returning</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ファイル不一致:</t>
+          <t>ホストのもとへ戻っています…</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>File mismatches:</t>
+          <t>Going back to the host…</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_more</t>
+          <t>emp_travel_disabled</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>… 他 {0} 件</t>
+          <t>ホストが単独行動を許可していません</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>… and {0} more</t>
+          <t>The host doesn't allow going alone.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>emp_ui_source_mismatch_continue</t>
+          <t>emp_travel_invalid</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>それでも続行しますか？</t>
+          <t>そこへ単独では行けません</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Continue anyway?</t>
+          <t>You can't go there alone.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_validation_sets</t>
+          <t>emp_travel_host_zone</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>検証セット</t>
+          <t>ホストはもうそこにいます</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Validation Sets</t>
+          <t>The host is already there.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>emp_validation_none</t>
+          <t>emp_travel_occupied</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>別のプレイヤーがもうそこにいます</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Another player is already there.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>emp_validation_sources</t>
+          <t>emp_travel_recalling</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ソース</t>
+          <t>{@Peer} がマップを返すのを待っています…</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Waiting for {@Peer} to give the map back…</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>emp_validation_plugins</t>
+          <t>emp_travel_recalled</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>プラグイン</t>
+          <t>ホストが来ます。合流します…</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Plugin</t>
+          <t>The host is coming. Joining them…</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>emp_validation_all</t>
+          <t>emp_travel_zone_closed</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>すべて</t>
+          <t>ここの持ち主がいなくなりました。ホストと合流します</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>The one who held this place is gone. Joining the host.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect</t>
+          <t>emp_travel_handoff</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>再接続</t>
+          <t>この場所はあなたが引き継ぎました</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Reconnect</t>
+          <t>You now hold this place.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>emp_dc_reconnect_request</t>
+          <t>emp_ui_sv_cfg_independent_travel</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>再接続</t>
+          <t>単独行動を許可</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Reconnect Request</t>
+          <t>Allow travelling alone</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>emp_lobby_create_failed</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>Steamロビーの作成に失敗しました: {Result}
-後でもう一度試してください</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>Failed to create Steam lobby: {Result}
-Try again later</t>
+          <t>emp_ui_sv_cfg_player_shipping</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>出荷はプレイヤーごと</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Shipping per player</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>emp_lobby_enter_failed</t>
+          <t>emp_ui_sv_cfg_combat_time</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Steamロビーへの参加に失敗しました: {Response}</t>
+          <t>戦闘はプレイヤーごとの時間で</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Failed to enter Steam lobby: {Response}</t>
+          <t>Combat at each player's pace</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>emp_lobby_already_joined</t>
+          <t>emp_ui_bot_add</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>すでに同じロビーに参加しています</t>
+          <t>Add a bot player</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Already in the same lobby</t>
+          <t>Add a bot player</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>emp_ui_quest_client</t>
+          <t>emp_ui_bot_stop</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>（暫定）このクエストはクライアントプレイヤーからは開始できません。</t>
+          <t>Stop the bots ({0})</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(Temp) This quest cannot be started by client players.</t>
+          <t>Stop the bots ({0})</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>emp_dc_version_mismatch</t>
+          <t>emp_ui_bot_all_actions</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>切断: 無効なVersion</t>
+          <t>Bots do everything (quests, selling, digging, chests)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Disconnected: invalid version</t>
+          <t>Bots do everything (quests, selling, digging, chests)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>emp_dc_act_mismatch</t>
+          <t>emp_ui_bot_need_local</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>切断: Act 不一致</t>
+          <t>Bots need a local server: disconnect, then add a bot to start one</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Act mapping mismatch</t>
+          <t>Bots need a local server: disconnect, then add a bot to start one</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>emp_ui_reject_acts</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>参加できません：Actマッピングが一致しません（{0}件）
-Act ID同期エラー：不一致は動作不良の原因になります。
-双方とも同じModを導入しているか確認してください。</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>Could not join: Act mapping mismatch ({0})
-Act ID is used for action sync. Game cannot run with mismatch acts.
-Please ensure both players have the exact same mods installed.</t>
+          <t>emp_ui_bot_no_launcher</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>No second copy of the game found (see _tools/make_lab.py)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>No second copy of the game found (see _tools/make_lab.py)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="60" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>emp_ui_reject_integrity</t>
+          <t>emp_ui_bot_started</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>参加できません：ホストの厳密チェックにより、データ整合性が不一致です（{0}件）</t>
+          <t>Bot player starting, it joins in about a minute</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Could not join: Host has strict verification enabled. Data integrity mismatch ({0})</t>
+          <t>Bot player starting, it joins in about a minute</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>emp_version_rejected_host</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>{0}の接続を拒否しました
-バージョンがホストと一致しません
-ホストMod：{1}
-ホストゲーム：{2}</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>Connection request from {0} rejected
-Version mismatch with host
-Host Mod: {1}
-Host Game: {2}</t>
+          <t>emp_ui_sv_cfg_personal_quests</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>依頼・名声・カルマはプレイヤーごと</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Quests, fame and karma per player</t>
         </is>
       </c>
     </row>
     <row r="109" ht="60" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>emp_version_rejected_client</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>参加できません：バージョン不一致
-Mod：自機 {0} ／ ホスト {1}
-ゲーム：自機 {2} ／ ホスト {3}
-古いバージョンのほうを更新してから、もう一度お試しください。</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>Could not join: Version mismatch
-Mod: Local {0} / Host {1}
-Game: Local {2} / Host {3}
-Whoever has the older version must update, then try again.</t>
+          <t>emp_ui_sv_cfg_choose_chara</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>参加時にキャラを選ぶ</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Choose a character when joining</t>
         </is>
       </c>
     </row>
     <row r="110" ht="45" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_request</t>
+          <t>emp_ui_chara_pick</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>全員がベッドに入るのを待っています…</t>
+          <t>どのキャラクターで遊びますか？</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Waiting for everyone to go to bed...</t>
+          <t>Who do you want to play?</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_wish</t>
+          <t>emp_ui_chara_new</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{0}が眠りたがっています（{1}/{2}）</t>
+          <t>新しいキャラクター</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{0} wants to sleep ({1}/{2})</t>
+          <t>A new character</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_cancel</t>
+          <t>emp_ui_sv_cfg_player_trade</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{0}が目を覚ましました（{1}/{2}）</t>
+          <t>プレイヤー同士の取引</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{0} woke up ({1}/{2})</t>
+          <t>Trade between players</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>emp_travel_requesting</t>
+          <t>emp_act_trade</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ホストに移動を申請中…</t>
+          <t>取引</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Asking the host to travel there alone…</t>
+          <t>Trade</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>emp_travel_returning</t>
+          <t>emp_ui_trade</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ホストのいる場所へ戻っています…</t>
+          <t>取引</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Returning to the host…</t>
+          <t>Trade</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>emp_travel_disabled</t>
+          <t>emp_trade_invite</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ホストが単独行動を許可していません</t>
+          <t>{0} があなたと取引したがっています</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>The host does not allow travelling alone</t>
+          <t>{0} wants to trade with you</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>emp_travel_invalid</t>
+          <t>emp_trade_you_offer</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>この場所へは単独で行けません</t>
+          <t>あなたの提示</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>You cannot travel there alone</t>
+          <t>You offer</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>emp_travel_host_zone</t>
+          <t>emp_trade_they_offer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ホストはすでにそこにいます</t>
+          <t>{0} の提示</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>The host is already there</t>
+          <t>{0} offers</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>emp_travel_occupied</t>
+          <t>emp_trade_nothing</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>他のプレイヤーがその場所にいます</t>
+          <t>（まだなし）</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Another player is already there</t>
+          <t>(nothing yet)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>emp_travel_recalling</t>
+          <t>emp_trade_add</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{@Peer} がその場所を返すのを待っています…</t>
+          <t>アイテムを追加</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Waiting for {@Peer} to hand the zone back…</t>
+          <t>Add an item</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>emp_travel_recalled</t>
+          <t>emp_trade_gold</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ホストが来ます。合流します…</t>
+          <t>金貨: {0}</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>The host is coming, rejoining them…</t>
+          <t>Gold: {0}</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>emp_travel_zone_closed</t>
+          <t>emp_trade_clear</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>この場所の主がいなくなりました。ホストに合流します</t>
+          <t>すべて取り下げる</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>The owner of this place is gone, rejoining the host</t>
+          <t>Take everything back</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>emp_travel_handoff</t>
+          <t>emp_trade_confirm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>この場所の主はあなたになりました</t>
+          <t>確定する</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>You are now the owner of this place</t>
+          <t>Validate</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_independent_travel</t>
+          <t>emp_trade_cancel</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>単独行動を許可</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Independent travel</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_shipping</t>
+          <t>emp_trade_you_ready</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>出荷はプレイヤーごと</t>
+          <t>確定済み</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Shipping per player</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_combat_time</t>
+          <t>emp_trade_you_wait</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>戦闘は各プレイヤーの時間で進行</t>
+          <t>あなたは未確認です</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Combat on each player's time</t>
+          <t>You have not confirmed</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>emp_ui_bot_add</t>
+          <t>emp_trade_they_ready</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Add a bot player</t>
+          <t>確定済み</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Add a bot player</t>
+          <t>validated</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>emp_ui_bot_stop</t>
+          <t>emp_trade_they_wait</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Stop the bots ({0})</t>
+          <t>まだ確定していない</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Stop the bots ({0})</t>
+          <t>not validated yet</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>emp_ui_bot_all_actions</t>
+          <t>emp_trade_pick</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bots do everything (quests, selling, digging, chests)</t>
+          <t>どのアイテム？</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bots do everything (quests, selling, digging, chests)</t>
+          <t>Which item?</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>emp_ui_bot_need_local</t>
+          <t>emp_trade_howmany</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bots need a local server: disconnect, then add a bot to start one</t>
+          <t>何個？</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Bots need a local server: disconnect, then add a bot to start one</t>
+          <t>How many?</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>emp_ui_bot_no_launcher</t>
+          <t>emp_trade_howmuch</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>No second copy of the game found (see _tools/make_lab.py)</t>
+          <t>金貨はいくら？</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>No second copy of the game found (see _tools/make_lab.py)</t>
+          <t>How much gold?</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>emp_ui_bot_started</t>
+          <t>emp_trade_done</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bot player starting, it joins in about a minute</t>
+          <t>取引が完了しました</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Bot player starting, it joins in about a minute</t>
+          <t>Trade done</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_personal_quests</t>
+          <t>emp_trade_cancelled</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ランダムクエスト・名声・カルマはプレイヤーごと</t>
+          <t>取引は中止されました</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Random quests, fame and karma per player</t>
+          <t>Trade cancelled</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_choose_chara</t>
+          <t>emp_trade_invalid</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>参加時にプレイヤーがキャラクターを選ぶ</t>
+          <t>取引は中止されました：渡すはずの物がもうありません</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Players choose their character when joining</t>
+          <t>Trade cancelled: an item is gone.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>emp_ui_chara_pick</t>
+          <t>emp_trade_far</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>どのキャラクターで遊びますか？</t>
+          <t>取引は中止されました：離れすぎです</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Who do you want to play?</t>
+          <t>Trade cancelled: you are too far apart.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>emp_ui_chara_new</t>
+          <t>emp_trade_busy</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>新しいキャラクター</t>
+          <t>そのプレイヤーは取引中です</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>A new character</t>
+          <t>That player is already trading.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_trade</t>
+          <t>emp_ui_sv_note_live</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>プレイヤー間の取引ウィンドウ</t>
+          <t>これはホストのルールです。変更はすぐ全員に反映されます。</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Trade window between players</t>
+          <t>These are the host's rules. Changes apply to everyone at once.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>emp_act_trade</t>
+          <t>emp_ui_sv_sec_players</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>取引</t>
+          <t>プレイヤーと移動</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Players and travel</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>emp_ui_trade</t>
+          <t>emp_ui_sv_sec_own</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>取引</t>
+          <t>プレイヤーごとのもの</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>One for each player</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>emp_trade_invite</t>
+          <t>emp_ui_sv_sec_time</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{0} があなたと取引したがっています</t>
+          <t>時間と戦闘</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{0} wants to trade with you</t>
+          <t>Time and combat</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>emp_trade_you_offer</t>
+          <t>emp_ui_sv_sec_checks</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>あなたの提示</t>
+          <t>参加チェック</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>You offer</t>
+          <t>Joining checks</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>emp_trade_they_offer</t>
+          <t>emp_ui_sv_desc_choose_chara</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{0} の提示</t>
+          <t>参加するとき、この世界での自分のキャラを選ぶか、新しく作ります。</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{0} offers</t>
+          <t>Joining players pick one of their characters in this world, or make a new one.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>emp_trade_nothing</t>
+          <t>emp_ui_sv_desc_independent_travel</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>（まだなし）</t>
+          <t>好きな場所へ、ひとりでも仲間とでも行けます。オフ：全員がホストについていきます。</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(nothing yet)</t>
+          <t>Players can go anywhere, alone or together. Unticked, everyone follows the host.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>emp_trade_add</t>
+          <t>emp_ui_sv_desc_personal_quests</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>アイテムを追加</t>
+          <t>依頼は1人5件ずつ。報酬・名声・カルマも別々です。ストーリーは共通です。</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Add an item</t>
+          <t>Each player gets 5 quests, with their own reward, fame and karma. Story quests stay shared.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>emp_trade_gold</t>
+          <t>emp_ui_sv_desc_player_shipping</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>金貨: {0}</t>
+          <t>出荷箱のお金は、入れたプレイヤーのものに。オフ：すべてホストへ。</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Gold: {0}</t>
+          <t>Shipping money goes to the player who put the item in. Unticked, the host gets it all.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>emp_trade_clear</t>
+          <t>emp_ui_sv_desc_player_trade</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>すべて取り下げる</t>
+          <t>ほかのプレイヤーをクリックすると、アイテムやお金を取引できます。双方の確認が必要です。</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Take everything back</t>
+          <t>Click another player to trade items and gold. Both must confirm.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>emp_trade_confirm</t>
+          <t>emp_ui_sv_desc_combat_time</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>モンスターは、戦っているプレイヤーが動くときに動きます。誰も待ちません。ターン制より優先されます。</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>A monster acts when the player it fights acts. Nobody waits. This comes before turn-based combat.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>emp_trade_cancel</t>
+          <t>emp_ui_sv_desc_turn_combat</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>戦闘中、プレイヤーは順番に動きます。「戦闘はプレイヤーごとの時間で」がオンのときは無効です。</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>In a fight, players take turns. Does nothing while "Combat at each player's pace" is ticked.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>emp_trade_you_ready</t>
+          <t>emp_ui_sv_desc_shared_speed</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>あなたは確認しました</t>
+          <t>全員が平均の速さで動きます。オフ：それぞれの速さのまま。</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>You confirmed</t>
+          <t>Everyone moves at the average speed. Unticked, each keeps their own.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>emp_trade_you_wait</t>
+          <t>emp_ui_sv_desc_validation</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>あなたは未確認です</t>
+          <t>参加するプレイヤーのゲームが、ホストと同じであるべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>You have not confirmed</t>
+          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>emp_trade_they_ready</t>
+          <t>emp_ui_sv_cfg_player_clock</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>相手は確認しました</t>
+          <t>プレイヤーごとの時間で動く</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>the other player confirmed</t>
+          <t>Each player moves at their own pace</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>emp_trade_they_wait</t>
+          <t>emp_ui_sv_desc_player_clock</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>相手は未確認です</t>
+          <t>ゲストも、ホストと同じなめらかさで動けます。上の項目がオンのときに使えます。</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>the other player has not confirmed</t>
+          <t>Guests move as smoothly as the host. Needs the option above.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>emp_trade_pick</t>
+          <t>emp_ui_sv_cfg_step_pace</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>どのアイテム？</t>
+          <t>全員がひとり用の速さで歩く</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Which item?</t>
+          <t>Everyone walks as in a solo game</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>emp_trade_howmany</t>
+          <t>emp_ui_sv_desc_step_pace</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>何個？</t>
+          <t>歩く速さが、ほかのプレイヤーの速さに左右されません。戦闘では速さが効きます。「戦闘はプレイヤーごとの時間で」が必要です。</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>How many?</t>
+          <t>A step no longer depends on the others' speed. Speed still counts in a fight. Needs "Combat at each player's pace".</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>emp_trade_howmuch</t>
+          <t>emp_ui_sv_cfg_import_chara</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>金貨はいくら？</t>
+          <t>自分のセーブのキャラを連れてこられる</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>How much gold?</t>
+          <t>Players can bring a character from their saves</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>emp_trade_done</t>
+          <t>emp_ui_sv_desc_import_chara</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>取引が完了しました</t>
+          <t>キャラ本人、装備、バッグ、お金、名声とカルマ。仲間、拠点、依頼、銀行は含みません。セーブは読むだけで、変更されません。</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Trade done</t>
+          <t>The character, gear, bag, gold, fame and karma. Not companions, base, quests or bank. The save is never changed.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>emp_trade_cancelled</t>
+          <t>emp_ui_chara_import</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>取引は中止されました</t>
+          <t>自分のセーブのキャラ…</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Trade cancelled</t>
+          <t>A character from my saves…</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>emp_trade_invalid</t>
+          <t>emp_ui_chara_import_pick</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>取引中止：提示したものがもう存在しません</t>
+          <t>どのセーブのキャラを連れてきますか？（セーブは変更されません）</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Trade cancelled: something offered is not there anymore</t>
+          <t>Which save? It will not be changed.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>emp_trade_far</t>
+          <t>emp_ui_chara_import_back</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>取引中止：お互いが離れすぎています</t>
+          <t>戻る</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Trade cancelled: too far from each other</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>emp_trade_busy</t>
+          <t>emp_ui_chara_import_none</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>そのプレイヤーはすでに取引中です</t>
+          <t>読み込めるセーブが見つかりません。</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>That player is already trading</t>
+          <t>No save was found.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>emp_ui_sv_note_live</t>
+          <t>emp_ui_chara_import_fail</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ホストのルールです。変更はすぐに全員に適用されます。</t>
+          <t>そのキャラを連れてこられませんでした。</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>These rules are the host's. A change applies at once, for everyone.</t>
+          <t>That character can't be brought.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_players</t>
+          <t>emp_ui_chara_import_twice</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>プレイヤーと移動</t>
+          <t>そのセーブのキャラは、すでにこの世界にいます。</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Players and travel</t>
+          <t>That character is already in this world.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_own</t>
+          <t>emp_ui_sv_cfg_world_time</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>プレイヤーごとのもの</t>
+          <t>世界で日付をひとつにする</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>To each player its own</t>
+          <t>One date for the whole world</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_time</t>
+          <t>emp_ui_sv_desc_world_time</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>時間と戦闘</t>
+          <t>別のマップにひとりでいるプレイヤーの時間も、全員に反映されます。いちばん進んだ日付が世界の日付です。オフ：ホストの日付のみ。</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Time and combat</t>
+          <t>Time spent alone on another map counts for everyone. The latest date is the world's. Unticked, only the host's date counts.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_checks</t>
+          <t>emp_ui_sv_cfg_world_keeper</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>参加時の検証（上級者向け）</t>
+          <t>時間の影響を一度だけ起こす</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Joining checks (advanced)</t>
+          <t>Time affects the world only once</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_choose_chara</t>
+          <t>emp_ui_sv_desc_world_keeper</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>参加時に、この世界の自分のキャラクターから選ぶか、新しく作る。</t>
+          <t>天気、依頼の期限切れ、税金、給料、手紙は、ひとりのゲームだけが処理します。オフ：マップを持つ全員が処理します。</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>A joining player picks one of its characters in this world, or makes a new one.</t>
+          <t>Weather, expired quests, taxes, salaries and letters are handled by one player only. Unticked, every player holding a map handles them.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_independent_travel</t>
+          <t>emp_ui_depot_take</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>誰でも好きな場所へ、一人でも一緒でも行ける。オフ：全員がホストについて行く。</t>
+          <t>デポから世界を取り出してホストする</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Everyone goes where they want, alone or together. Off: everyone follows the host.</t>
+          <t>Take the world from the depot and host it</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_personal_quests</t>
+          <t>emp_ui_depot_put</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>各自ランダムクエスト5件、報酬・名声・カルマも各自。メインクエストは共有。</t>
+          <t>このセーブをデポに置く</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>5 random quests each, with their reward, fame and karma. Story quests stay shared.</t>
+          <t>Put this save in the depot</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_shipping</t>
+          <t>emp_ui_depot_held</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>出荷箱の売上はアイテムを入れたプレイヤーへ。オフ：すべてホストへ。</t>
+          <t>{0} が世界をホスト中です。Steam で参加してください。招待してもらうか、Steam のフレンド一覧で「ゲームに参加」を選びます。抜けた直後なら、3分ほど待ってください。</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Shipping box money goes to the player who put the item in. Off: all to the host.</t>
+          <t>{0} is hosting the world. Join through Steam: ask for an invite, or use "Join Game" on their name in your friends list. If they just left, wait up to 3 minutes.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_trade</t>
+          <t>emp_ui_depot_empty</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>他のプレイヤーをクリックしてアイテムと金貨を交換。双方が確認する。</t>
+          <t>デポにはまだ世界がありません。ゲームを始めるかロードして、このパネルをもう一度開き、ロビーのタブで「このセーブをデポに置く」を選んでください。</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Click another player to trade items and gold. Both confirm.</t>
+          <t>The depot has no world yet. Start or load a game, then open this panel again and use "Put this save in the depot" in the Lobby tab.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_combat_time</t>
+          <t>emp_ui_depot_fail</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>モンスターは戦っている相手が動いた時に動く。誰も待たない。ターン制より優先。</t>
+          <t>デポに接続できませんでした。</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>A monster acts when the player it fights acts: nobody waits. Takes over turn-based.</t>
+          <t>Could not reach the depot.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_turn_combat</t>
+          <t>emp_ui_depot_put_done</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>戦闘中、プレイヤーは順番に行動する。「戦闘は各プレイヤーの時間で進行」がオンの間は無効。</t>
+          <t>この世界をデポに置きました。ゲームはそこから読み込み直します。これからのセーブはすべてデポに送られます。</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>In a fight, players act in turn. No effect while "Combat on each player's time" is on.</t>
+          <t>The world is now in the depot. The game loads it again from there. From now on, every save goes to the depot.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_speed</t>
+          <t>emp_ui_depot_folder</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>全プレイヤーが平均速度を共有。オフ：各自の速度。</t>
+          <t>デポ</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>One speed for all players, the average. Off: each keeps its own.</t>
+          <t>Depot</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_validation</t>
+          <t>emp_ui_depot_folder_ask</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>参加するプレイヤーのゲームがホストと一致すべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
+          <t>セーブの置き場所：Elin Together Server のアドレス（ホスト:55557）、全員が使えるフォルダ、または非公開の GitHub リポジトリ（github:ユーザー/リポジトリ）。空欄なら使いません</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
+          <t>Where the world is kept: the address of Elin Together Server (host:55557), a folder everyone can reach, or a private GitHub repository (github:owner/repository). Leave empty for none.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_clock</t>
+          <t>emp_ui_join_address</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>各プレイヤーは自分の時計で動く</t>
+          <t>アドレスで参加</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Each player on its own clock</t>
+          <t>Join by address</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_clock</t>
+          <t>emp_ui_join_address_ask</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ゲストもホストと同じように滑らかに動く（通信の速さに左右されない）。上のオプションが必要。</t>
+          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、なしは 55557）</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>A guest walks and acts as smoothly as the host, not at the pace of the network. Needs the option above.</t>
+          <t>Server address (host:port). The port is 55556 with Elin, 55557 without.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_step_pace</t>
+          <t>emp_ui_depot_password</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>各プレイヤーはソロと同じ歩調で動く</t>
+          <t>デポのキー</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Every player walks at the pace of a solo game</t>
+          <t>Depot key</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_step_pace</t>
+          <t>emp_ui_depot_password_ask</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>歩く速さが他のプレイヤーの速度に左右されなくなります。戦闘では速度は今まで通り有効。「戦闘は各プレイヤーの時間で」が必要。</t>
+          <t>デポのパスワード（設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。変えないなら空欄のままにしてください</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>The length of a step no longer depends on the other players' speed. Speed still counts in a fight. Needs combat on each player's time.</t>
+          <t>The depot password (if one was set), or the GitHub key. A key is never shown again. Leave empty to keep it.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_import_chara</t>
+          <t>emp_ui_timeout</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラクターで参加できる</t>
+          <t>サーバーが応答しません。アドレスとポートを確認してください。</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Players can bring a character from their own saves</t>
+          <t>The server does not answer. Check the address and the port.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_import_chara</t>
+          <t>emp_ui_depot_password_wrong</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>キャラクター本人、装備、持ち物、所持金、名声、カルマ。仲間、拠点、クエスト、銀行は含まれません。セーブは読むだけで変更しません。</t>
+          <t>サーバーにパスワードを断られました。クライアント設定の「デポのキー」で設定してください。</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>The character, its equipment, bag and gold, its fame and karma. Not its companions, base, quests or bank. The save is only read, never changed.</t>
+          <t>The server refused the password. Set it in Client Settings, under "Depot key".</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import</t>
+          <t>emp_ui_depot_lost</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラクター…</t>
+          <t>接続が切れている間に、{0} がデポの世界を引き継ぎました。これ以降のプレイはデポに届きません。タイトルに戻って、その人のゲームに参加してください。</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>A character from one of my saves…</t>
+          <t>{0} took over the world while you were cut off. What you play now won't reach the depot. Go back to the title screen and join them.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_pick</t>
+          <t>emp_ui_depot_unsaved</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>どのセーブのキャラクターで参加しますか？（セーブは変更されません）</t>
+          <t>デポにセーブが届きませんでした。このPCに残してあり、次のセーブでもう一度送ります。</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Which save to bring the character of? (the save is not changed)</t>
+          <t>The save didn't reach the depot. It is kept on this PC and sent again at the next save.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_back</t>
+          <t>emp_ui_depot_unsent</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>戻る</t>
+          <t>前回の最後のセーブが、デポに届いていません。今送りますか？（はい：デポにある世界は別に取っておきます。いいえ：このセーブは捨てて、デポの世界を使います。）</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Your last save never reached the depot. Send it now? Yes keeps the depot's world aside. No drops your save and uses the depot's world.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_none</t>
+          <t>emp_quest_follow_ask</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>読み込めるセーブがありません。</t>
+          <t>{0} が依頼に出かけます。ついていきますか？報酬は {0} のものになります。</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>No save this game can read was found.</t>
+          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_fail</t>
+          <t>emp_quest_follow_declined</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>このキャラクターは読み込めませんでした。</t>
+          <t>{0} は同行を断りました。</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>That character could not be brought.</t>
+          <t>{0} won't come along.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_twice</t>
+          <t>emp_quest_follow_no_answer</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>このセーブのキャラクターはすでにこの世界にいます。</t>
+          <t>{0} から返事がありません。</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>The character of that save is already in this world.</t>
+          <t>{0} didn't answer.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_time</t>
+          <t>emp_quest_follow_asked</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>世界の時間は全員で一つ</t>
+          <t>{0} に同行を頼んでいます…</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>One date for the whole world</t>
+          <t>Asking {0} to come along...</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_time</t>
+          <t>emp_base_host_only</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>一人で別のマップにいるプレイヤーの時間も世界の時間になります。一番進んだ日付が世界の日付。オフ：ホストの日付だけ。</t>
+          <t>今はホストだけができます。</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Time passed by a player alone on another map counts for everyone: the most advanced date is the world's. Off: only the host's date counts.</t>
+          <t>Only the host can do this for now.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_keeper</t>
+          <t>emp_trade_equipped</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>世界の出来事は一度だけ起きる</t>
+          <t>取引は中止されました：渡す物が装備中です</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>What time does to the world happens once</t>
+          <t>Trade cancelled: an item is equipped.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_keeper</t>
+          <t>emp_trade_nodrop</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>天気、依頼の期限切れ、税金、給料、手紙は一つのゲームだけが処理します。オフ：マップを持つ各プレイヤーのゲームでも起きます。</t>
+          <t>取引は中止されました：捨てられない物、渡せない物があります</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Weather, expired quests, taxes, salaries and letters are handled by one game only, the same for everyone. Off: every player holding a map runs them too.</t>
+          <t>Trade cancelled: an item can't be given away.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>emp_ui_depot_take</t>
+          <t>emp_trade_npcprop</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>サーバーから世界を取り出してホストする</t>
+          <t>取引は中止されました：NPCの持ち物が含まれています</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Take the world from the server and host it</t>
+          <t>Trade cancelled: an item belongs to an NPC.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put</t>
+          <t>emp_trade_gifted</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>このセーブをサーバーに置く</t>
+          <t>取引は中止されました：贈り物は取引できません</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Put this save on the server</t>
+          <t>Trade cancelled: a gift can't be traded.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>emp_ui_depot_held</t>
+          <t>emp_trade_bound</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{0} が世界をホスト中です。Steam で参加してください（招待してもらうか、Steam のフレンド一覧で「ゲームに参加」）。相手が抜けた直後なら、最大3分待ってください。</t>
+          <t>取引は中止されました：キャラに結びついた物があります</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>{0} is hosting the world. Join them through Steam: ask for an invite, or use "Join Game" on their name in your Steam friends list. If they have just left, wait up to 3 minutes.</t>
+          <t>Trade cancelled: an item is bound to a character.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>emp_ui_depot_empty</t>
+          <t>emp_trade_full</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>サーバーにまだ世界がありません。ゲームを開始または読み込み、このパネルの「Lobby」で「このセーブをサーバーに置く」を押してください。</t>
+          <t>取引は中止されました：バッグの空きが足りません</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>The server holds no world yet. Start or load a game, then open this panel again: Lobby tab, "Put this save on the server".</t>
+          <t>Trade cancelled: a bag is full.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>emp_ui_depot_fail</t>
+          <t>emp_travel_recalled_by</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>デポに接続できない、または読み書きできませんでした。</t>
+          <t>{@Peer} がここに来ます。合流のため画面を読み込み直します…</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>The depot could not be reached, read or written.</t>
+          <t>{@Peer} is coming here. The screen reloads to join them…</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put_done</t>
+          <t>emp_ui_thing_gone</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>この世界はサーバーに置かれました。これからサーバーから読み込み直します。以後のセーブはすべてサーバーに送られます。</t>
+          <t>遅かった：ほかの人が先に取りました</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>This world is now on the server. The game reloads it from there: from now on every save goes to the server.</t>
+          <t>Too late. Someone else took it.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder</t>
+          <t>emp_base_refused</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>デポ</t>
+          <t>ホストに断られました：拠点か所持金では払えません。</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Depot</t>
+          <t>The host refused. The base or your purse can't pay for this.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder_ask</t>
+          <t>emp_base_pending</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>セーブデポ：Elin Together Server のアドレス（ホスト:55557）、共有フォルダ、または非公開の GitHub リポジトリ（github:所有者/リポジトリ）。空欄でオフ</t>
+          <t>前の頼みが、まだホストの返事待ちです。</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Save depot: the address of Elin Together Server (host:55557), a folder the whole group can reach, or a private GitHub repository (github:owner/repository). Empty for none</t>
+          <t>Your last request is still waiting for the host.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>emp_ui_join_address</t>
+          <t>emp_game_version_differs</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>アドレスで参加</t>
+          <t>{0} の Elin はバージョンが違います（{1}、自分は {2}）。接続はできます。問題が起きたら同じバージョンにしてください。</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Join by address</t>
+          <t>{0} has another version of Elin ({1}, yours is {2}). You can still join. If something goes wrong, use the same version.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>emp_ui_join_address_ask</t>
+          <t>emp_ui_sv_cfg_same_game_version</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、Elin なしは 55557）</t>
+          <t>同じ Elin のバージョンを必須にする</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Address of the server (host:port; the port is 55556 with Elin, 55557 without)</t>
+          <t>Require the same Elin version</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password</t>
+          <t>emp_ui_sv_desc_same_game_version</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>デポのキー</t>
+          <t>Elin のバージョンが違うプレイヤーは入れません。オフ：警告つきで入れます。MODのバージョンは常に同じである必要があります。</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Depot key</t>
+          <t>Players with another Elin version can't join. Unticked, they join with a warning. The mod version must always match.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_ask</t>
+          <t>emp_ui_sv_cfg_guest_build</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>デポのパスワード（サーバーで設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。空欄のままなら現在のキーを保持します</t>
+          <t>ほかのプレイヤーも建築できる</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Password of the depot (when one was set in Elin Together Server), or the GitHub access key. A key is never shown again: leave empty to keep it</t>
+          <t>Other players can build</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>emp_ui_timeout</t>
+          <t>emp_ui_sv_desc_guest_build</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>サーバーが応答しません。アドレス、ポート、サーバーのモードを確認してください。</t>
+          <t>拠点の建築モード（床、壁、家具、採掘、伐採）を使えます。お金と素材は本人が払います。オフ：建築できるのはホストだけ。</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>The server does not answer. Check the address, the port and the mode of the server.</t>
+          <t>Others can use build mode in the base: floors, walls, furniture, mining, cutting. They pay the gold and materials. Unticked, only the host builds.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_wrong</t>
+          <t>emp_ui_depot_gh_help</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>サーバーがパスワードを拒否しました。「Client Settings」の「デポのキー」で設定してください。</t>
+          <t>非公開の GitHub リポジトリを、デポにできます。サーバーも共有フォルダも要らず、友達に GitHub アカウントも要りません。
+1. github.com で、この世界専用の空の非公開リポジトリを作ります。
+2. そのアクセスキーを作ります：Settings、Developer settings、Fine-grained tokens。このリポジトリだけ、Contents は Read and write。
+3. 「デポのキー」にキーを貼り、「デポ」に github:ユーザー/リポジトリ と入力します。
+4. 同じ2行を友達に送ります。友達もここに入力します。キーで開けるのはこのリポジトリだけです。</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The server refused the password. Set it in Client Settings, "Depot key".</t>
+          <t>A private GitHub repository can be the depot. No server, no shared folder, and your friends need no GitHub account.
+1. On github.com, create an empty private repository just for this world.
+2. Create an access key for it: Settings, Developer settings, Fine-grained tokens. Only this repository. Contents: Read and write.
+3. Paste the key in "Depot key" and write github:owner/repository in "Depot".
+4. Send the same two lines to your friends. They type them here too. The key opens only this repository.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>emp_ui_depot_lost</t>
+          <t>emp_ui_depot_gh_key</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>接続が切れている間に {0} がサーバーの世界を引き継ぎました。ここからのプレイはサーバーに届きません。タイトルに戻って相手に参加してください。</t>
+          <t>GitHub にアクセスキーを断られました。期限切れでないか、このリポジトリを含み「Contents: Read and write」であるかを確認して、クライアント設定でもう一度貼ってください。</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>{0} took over the world on the server while this game was cut off. What you play from here no longer reaches the server: go back to the title screen and join them.</t>
+          <t>GitHub refused the key. Check that it hasn't expired and covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsaved</t>
+          <t>emp_ui_depot_gh_missing</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>このセーブはサーバーに届きませんでした。このPCには保存されています。次のセーブで再送します。</t>
+          <t>GitHub でこのリポジトリが見つかりません。クライアント設定で名前（github:ユーザー/リポジトリ）を確認し、アクセスキーがそれを含んでいるか確認してください。</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>The server did not receive this save. It is kept on this PC; the next save tries again.</t>
+          <t>GitHub can't find the repository. Check its name (github:owner/repository) in Client Settings, and that your key covers it.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsent</t>
+          <t>emp_ui_depot_gh_public</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>前回のプレイの最後のセーブがサーバーに届いていません。今送りますか？（はい：サーバーにある世界は別に保管されます。いいえ：このPCの分を破棄し、サーバーの世界を使います）</t>
+          <t>この GitHub リポジトリは公開です。世界とその履歴が誰にでも見えてしまいます。非公開に変えて（Settings、Danger Zone、Change visibility）、もう一度試してください。</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>The last save of your previous session never reached the server. Send it now? (Yes: the world the server holds now is kept aside. No: your save is dropped and the server's world is used.)</t>
+          <t>This GitHub repository is public. Everyone could see your world and its history. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>emp_quest_follow_ask</t>
+          <t>emp_ui_depot_gh_big</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{0}がクエストに出発します。同行しますか？報酬は{0}のものです。</t>
+          <t>この世界は20MBを超えていて、GitHub には大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに残っています。</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
+          <t>This world is over 20 MB, too big for GitHub. Use Elin Together Server or a shared folder. The save stays on this PC.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>emp_quest_follow_declined</t>
+          <t>emp_ui_depot_gh_changed</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{0}は同行を断りました。</t>
+          <t>接続が切れている間に、別の人が世界をホストしてセーブしました。あなたのセーブはこのPCに残り、これ以上デポに送られません。タイトルに戻って、世界を取り直してください。</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>{0} declined to come along.</t>
+          <t>Someone else hosted the world and saved while you were cut off. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>emp_quest_follow_no_answer</t>
+          <t>emp_ui_depot_gh_down</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{0}から返事がありません。</t>
+          <t>GitHub が応答しません。接続を確認して、少し待ってからもう一度試してください。</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>{0} did not answer.</t>
+          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>emp_quest_follow_asked</t>
+          <t>emp_ui_sv_cfg_player_kill</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{0}に同行するか尋ねています…</t>
+          <t>プレイヤー同士で倒せる</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Asking {0} to come along...</t>
+          <t>Players can kill each other</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>emp_base_host_only</t>
+          <t>emp_ui_sv_desc_player_kill</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>今のところ、これはホストだけができます。</t>
+          <t>プレイヤーや仲間の攻撃で、ほかのプレイヤーを倒せます。オフ：致命傷でもHP0で生き残ります。</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Only the host can do this for now.</t>
+          <t>Players and their companions can kill other players. Unticked, a deadly blow leaves them alive at 0 HP.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>emp_trade_equipped</t>
+          <t>emp_ui_sv_cfg_host_manages_base</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムが装備されています</t>
+          <t>拠点を管理できるのはホストだけ</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item is now equipped</t>
+          <t>Only the host manages the base</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>emp_trade_nodrop</t>
+          <t>emp_ui_sv_desc_host_manages_base</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムは手放せません</t>
+          <t>ほかのプレイヤーの拠点操作（研究、炉の技能、方針、名前、設定、住人、建築）は断られます。オフ：全員がホストと同じように管理できます。拠点を完全に手放せるのは常にホストだけです。</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item cannot be dropped or given away</t>
+          <t>Others can't change the base: research, hearth skills, policies, names, settings, residents, build mode. Unticked, all can. Only the host can give up the base for good.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>emp_trade_npcprop</t>
+          <t>emp_ui_sv_cfg_duels</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムはNPCの所有物です</t>
+          <t>プレイヤー同士の決闘</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item belongs to an NPC</t>
+          <t>Duels between players</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>emp_trade_gifted</t>
+          <t>emp_ui_sv_desc_duels</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムは贈り物のため取引できません</t>
+          <t>相手のキャラのメニューから決闘を申し込めます。誰も死なず、終わると全員回復し、何も失いません。</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item is a gift and cannot be traded</t>
+          <t>Challenge another player from the menu on their character. Nobody dies, both are healed and nothing is lost.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>emp_trade_bound</t>
+          <t>emp_act_duel</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>取引中止：提示したアイテムはキャラクターに結び付いています</t>
+          <t>決闘を申し込む</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Trade cancelled: an offered item is bound to a character</t>
+          <t>Challenge to a duel</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>emp_trade_full</t>
+          <t>emp_duel_invite</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>取引中止：受け取るアイテムに対してバッグの空きが足りません</t>
+          <t>{0}が決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Trade cancelled: a bag does not have enough free slots for what it would receive</t>
+          <t>{0} challenges you to a duel. Nobody dies, but what you use up stays used. Accept?</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>emp_travel_recalled_by</t>
+          <t>emp_duel_asked</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{@Peer} がこの場所に来ます。画面が再読み込みされ、合流します…</t>
+          <t>{0} に決闘を申し込みました…</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>{@Peer} is coming to this place: the screen will reload to rejoin them…</t>
+          <t>You challenge {0} to a duel…</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>emp_ui_thing_gone</t>
+          <t>emp_duel_countdown</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>遅かったようです。他のプレイヤーが先に取りました</t>
+          <t>{0} と {1} が向かい合います。3秒後に決闘開始。</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Too late: someone else already took it</t>
+          <t>{0} and {1} face each other. The duel starts in 3 seconds.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>emp_base_refused</t>
+          <t>emp_duel_fight</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>ホストに断られました。拠点または所持金では、もう支払えません。</t>
+          <t>始め！</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>The host refused: the base or your purse can no longer pay for this.</t>
+          <t>Fight!</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>emp_base_pending</t>
+          <t>emp_duel_declined</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>前回の依頼はまだホストの返事を待っています。</t>
+          <t>決闘を断られました。</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Your last request is still waiting for the host's answer.</t>
+          <t>Your challenge was declined.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>emp_game_version_differs</t>
+          <t>emp_duel_noanswer</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>{0} のElinのバージョンが異なります（{1} ／ こちら {2}）。接続は許可されます。問題が起きたら同じバージョンに揃えてください。</t>
+          <t>決闘の返事がありません。</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>{0} runs another version of Elin ({1}, here {2}). The connection is allowed; if something goes wrong, use the same version.</t>
+          <t>Nobody answered your challenge.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_same_game_version</t>
+          <t>emp_duel_busy</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>同じElinバージョンを必須にする</t>
+          <t>そのプレイヤーは決闘中か取引中です。</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Require the same Elin version</t>
+          <t>That player is busy in a duel or a trade.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_same_game_version</t>
+          <t>emp_duel_over</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>オン：Elinのバージョンが違うプレイヤーを拒否。オフ：警告のうえ参加を許可。Modのバージョンは常に同じである必要があります。</t>
+          <t>決闘は引き分けです。</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>On: players on another version of Elin are refused. Off: they are let in with a warning. The same version of the mod is always required.</t>
+          <t>The duel ends in a draw.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_guest_build</t>
+          <t>emp_handover_failed</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>他のプレイヤーも建築モードを使える</t>
+          <t>キャラ {0} はこの世界に入れませんでした（死亡しています）。セーブのキャラで遊びます。</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Other players can use build mode</t>
+          <t>Your character {0} can't join this world because it is dead. You play the character of the save.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_guest_build</t>
+          <t>emp_ui_depot_held_btn</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>オン：他のプレイヤーも拠点の建築モード（床・壁・家具・採掘・伐採）を使えます。ホストのゲームが代わりに建て、費用と素材は本人が払います。オフ：ホストだけが建てられます。</t>
+          <t>{0} が世界をホスト中</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>On: the other players can use the build mode of the base (floors, walls, furniture, mining, cutting). The game of the host builds for them; they pay the gold and the materials. Off: only the host builds.</t>
+          <t>{0} is hosting the world</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_help</t>
+          <t>emp_error_connection</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>非公開の GitHub リポジトリをデポにできます（サーバーも共有フォルダも不要、フレンドは GitHub アカウント不要）：
-1. github.com で、この世界専用の空の非公開（Private）リポジトリを作成します。
-2. そのリポジトリ用のアクセスキーを1つ作成します：Settings → Developer settings → Fine-grained tokens、このリポジトリのみ、Contents: Read and write。
-3. キーを「デポのキー」に貼り付け、「デポ」に github:所有者/リポジトリ と入力します。
-4. 同じ2行をフレンドに送り、フレンドもここに入力します。このキーで開けるのはこのリポジトリだけです。</t>
+          <t>接続できません：ゲームが応答しません。ゲームが開いているか確認して、もう一度試してください。</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>A private GitHub repository can be the depot (no server, no shared folder, your friends need no GitHub account):
-1. On github.com, create an empty private repository, only for this world.
-2. Create one access key for it: Settings, Developer settings, Fine-grained tokens; only this repository; Contents: Read and write.
-3. Paste the key in "Depot key" and write github:owner/repository in "Depot".
-4. Send the same two lines to your friends: they type them here too. The key only opens this one repository.</t>
+          <t>Could not connect. The game does not answer. Check that it is open, then try again.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_key</t>
+          <t>emp_not_allowed</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>GitHub がアクセスキーを拒否しました。キーの有効期限、このリポジトリが対象になっているか、「Contents: Read and write」の権限があるかを確認し、「Client Settings」で貼り付け直してください。</t>
+          <t>このゲームには、Steam ロビーから参加したプレイヤーしか入れません。</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>GitHub refused the access key. Check that it has not expired, that it covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
+          <t>Only players who join through its Steam lobby can enter this game.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_missing</t>
+          <t>emp_connection_no_server</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>GitHub でデポのリポジトリが見つかりません。「Client Settings」の名前（github:所有者/リポジトリ）と、アクセスキーがそのリポジトリを対象にしているかを確認してください。</t>
+          <t>そのゲームはまだ開いていません。少し待ってからもう一度試してください。</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>GitHub does not find the repository of the depot. Check its name (github:owner/repository) in Client Settings, and that your access key covers it.</t>
+          <t>That game is not open yet. Try again in a moment.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_public</t>
+          <t>emp_zone_session_empty</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>この GitHub リポジトリは公開されています。世界とその履歴がすべて誰にでも見えてしまいます。非公開にしてから（Settings → Danger Zone → Change visibility）、もう一度お試しください。</t>
+          <t>ここにはもう誰もいません</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>This GitHub repository is public: your world and all its history would be visible to everyone. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
+          <t>Nobody else is here anymore.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_big</t>
+          <t>emp_ui_timeout_steam</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>この世界は 20 MB を超えており、GitHub のデポには大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに保存されています。</t>
+          <t>ゲームが応答しません。相手が抜けたか、接続が切れたのかもしれません。</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>This world is over 20 MB: too big for a GitHub depot. Use Elin Together Server or a shared folder instead. The save is kept on this PC.</t>
+          <t>The game does not answer. The player may have left or lost the connection.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_changed</t>
+          <t>emp_trade_nothing_to_offer</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>接続が切れている間に、他のプレイヤーがデポの世界をホストしてセーブしました。あなたのセーブはこのPCに残り、デポには届きません。タイトルに戻って、もう一度世界を取り出してください。</t>
+          <t>渡せる物がありません。</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>The world in the depot changed while this game was cut off: someone else hosted it and saved. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
+          <t>You have nothing to offer.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_down</t>
+          <t>emp_ui_reconnecting</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>GitHub から応答がありません。接続を確認して、しばらくしてからもう一度お試しください。</t>
+          <t>接続が切れました。ゲームに戻っています…</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
+          <t>Connection lost. Going back into the game…</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_kill</t>
+          <t>emp_ui_reconnect_cancel</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>プレイヤー同士で殺せる</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Players can kill each other</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_kill</t>
+          <t>emp_ui_reconnect_failed</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>オン：プレイヤー（とその仲間）の攻撃で他のプレイヤーのキャラクターが死にます。オフ：致命的な一撃でも相手のHPは0で止まり、死にません。</t>
+          <t>ゲームに戻れませんでした。3分間応答がなく、終わった可能性があります。</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>On: a strike of a player (or of its companions) can kill another player's character. Off: a strike that would kill it leaves it at 0 hit points, alive.</t>
+          <t>Could not get back into the game. It didn't answer for 3 minutes and may be over.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_host_manages_base</t>
+          <t>emp_ui_save_kept</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>拠点の管理はホストだけ</t>
+          <t>進行状況は、参加したゲームが保存します。</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Only the host manages the base</t>
+          <t>The game you joined keeps your progress.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_host_manages_base</t>
+          <t>emp_ui_sv_cfg_auto_reconnect</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>オン：他のプレイヤーによる拠点の操作（研究、炉の技能、政策、名前、物の設定、住民、建築モード）は拒否されます。オフ：全員がホストと同じように拠点を管理できます。拠点の放棄は常にホストだけです。</t>
+          <t>切れたプレイヤーは自動で戻る</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>On: what the other players ask of the base (research, hearth skills, policies, names, settings of an object, residents, build mode) is refused. Off: every player manages the base as the host does. Leaving the base for good always stays the host's.</t>
+          <t>Players rejoin by themselves after a drop</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_duels</t>
+          <t>emp_ui_sv_desc_auto_reconnect</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>プレイヤー同士の決闘</t>
+          <t>接続が切れたプレイヤーは、3分間自動で再参加を試みます。オフ：タイトルに戻ります。</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Duels between players</t>
+          <t>A player who drops tries to rejoin for 3 minutes. Unticked, they go back to the title screen.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_duels</t>
+          <t>emp_ui_sv_cfg_auto_host</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>オン：相手キャラクターのメニューから決闘を申し込めます。誰も死なず、終了時に両者が回復し、何も失いません。オフ：決闘なし。</t>
+          <t>世界を読み込むと自動でフレンドに公開</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>On: a player can challenge another from the menu on its character. Nobody dies, both are healed, nothing is lost. Off: no duels.</t>
+          <t>Open the game to friends when a world loads</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>emp_act_duel</t>
+          <t>emp_ui_sv_desc_auto_host</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>決闘を申し込む</t>
+          <t>世界を読み込むとすぐ、サーバーを手で始めなくてもフレンドが参加できます（所有した土地が必要）。オフ：ホストが自分でサーバーを始めます。</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Challenge to a duel</t>
+          <t>Friends can join as soon as the world loads, with no need to start the server. The world needs a claimed land. Unticked, the host starts the server.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>emp_duel_invite</t>
+          <t>emp_ui_sv_cfg_auto_save</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>{0} が決闘を申し込んできました。誰も死なず何も失いませんが、決闘中に使ったポーション・矢・チャージは戻りません。受けますか？</t>
+          <t>他のプレイヤーがいる間は自動でセーブ</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>{0} challenges you to a duel. Nobody dies and nothing is lost, but potions, arrows and charges used during the duel stay spent. Accept?</t>
+          <t>Save automatically while others play</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>emp_duel_asked</t>
+          <t>emp_ui_sv_desc_auto_save</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>{0} に決闘を申し込みました…</t>
+          <t>他のプレイヤーがいる間は2分ごと（遅いときは5分ごと）と、最後の人が抜けたときにセーブします。オフ：ホストがセーブしたときだけ。</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>You challenge {0} to a duel…</t>
+          <t>Saves every 2 minutes while others are in the game (5 if saving is slow), and when the last one leaves. Unticked, only when the host saves.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>emp_duel_countdown</t>
+          <t>emp_ui_load_blocked</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>決闘：{0} 対 {1}。3秒後に開始！</t>
+          <t>みんなで遊んでいる間は、セーブをロードできません。</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Duel: {0} against {1}. It starts in 3 seconds!</t>
+          <t>You can't load a save while players are together.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>emp_duel_fight</t>
+          <t>emp_ui_depot_join_btn</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>始め！</t>
+          <t>{0} に参加</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Fight!</t>
+          <t>Join {0}</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>emp_duel_won</t>
+          <t>emp_ui_depot_join_fail</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>{0} が {1} との決闘に勝ちました。</t>
+          <t>{0} が世界を持っていますが、そのゲームはまだ開いていません。少し待ってからもう一度試してください。ゲームが止まっていたら、3分以内に世界は空きます。</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>{0} won the duel against {1}.</t>
+          <t>{0} has the world, but their game is not open yet. Try again in a moment. If their game stopped, the world is free again within 3 minutes.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>emp_duel_declined</t>
+          <t>emp_ui_box_far</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>決闘は断られました。</t>
+          <t>この箱は世界全体のもので、ホストが預かっています。ホストから離れていても入れた物はホストに届きますが、ホストのマップに戻るまで表示されません。</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>The duel was declined.</t>
+          <t>This chest belongs to the whole world and the host keeps it. If you are away from the host, what you put in still arrives, but you only see it again back on the host's map.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>emp_duel_noanswer</t>
+          <t>emp_ui_sv_cfg_own_sleep</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>返事がなく、決闘は行われません。</t>
+          <t>各自で眠る</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>No answer: no duel.</t>
+          <t>Everyone sleeps on their own</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>emp_duel_busy</t>
+          <t>emp_ui_sv_desc_own_sleep</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>そのプレイヤーは決闘中か取引中です。</t>
+          <t>ベッドに入ったプレイヤーはすぐ眠れます。夜が明けるのは、全員が同時に眠っているときだけです。オフ：全員が揃うまで待ちます。</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>That player is already in a duel or a trade.</t>
+          <t>A player in bed sleeps at once. The night passes only when everyone sleeps at the same time. Unticked, everyone waits for everyone.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>emp_duel_over</t>
+          <t>emp_ui_sv_cfg_time_jumps_together</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>決闘は勝者なしで終わりました。</t>
+          <t>全員一緒のときだけ時間が進む</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>The duel is over, without a winner.</t>
+          <t>Time moves only when all travel together</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>emp_handover_failed</t>
+          <t>emp_ui_sv_desc_time_jumps_together</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>あなたのキャラクター {0} はこの世界で交代できませんでした（死亡しています）。セーブデータのキャラクターで遊んでいます。</t>
+          <t>ワールドマップの一歩で日付が進むのは、全員が一緒に旅しているときだけです。そうでなければ旅人だけがターンを消費します。オフ：誰かの一歩ごとに全員が3時間進みます。</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Your character {0} could not take its place in this world (it is dead). You are playing the character of the save.</t>
+          <t>On the world map, the date moves only when all players travel together. Otherwise only the traveller's turns pass. Unticked, every step by anyone adds 3 hours for all.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>emp_ui_depot_held_btn</t>
+          <t>emp_ui_sv_cfg_dump_spares_belt</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>{0} が世界をホスト中</t>
+          <t>自動整理で手持ちとツールベルトを残す</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>{0} is hosting the world</t>
+          <t>Auto-dump leaves your hands and tool belt alone</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>emp_error_connection</t>
+          <t>emp_ui_sv_desc_dump_spares_belt</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>接続できませんでした。ゲームが応答しません。まだ開いているか確認して、もう一度お試しください。</t>
+          <t>手に持っている物とツールベルトの中身は、ホットバーと同じように、まとめて入れても残ります。オフ：元のゲームと同じ。</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Could not connect: the game does not answer. Check that it is still open, then try again.</t>
+          <t>Dump spares keeps what you hold and what is in your tool belt, like the hotbar. Unticked, it works as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>emp_not_allowed</t>
+          <t>emp_ui_travel_no_date</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>このゲームは、Steam のロビーから参加したプレイヤーだけを受け入れます。</t>
+          <t>仲間は別の場所にいます。あなたの旅では日付は進みません。</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>This game only accepts players who joined through its Steam lobby.</t>
+          <t>Your friends are elsewhere. Your trip doesn't move the date.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>emp_connection_no_server</t>
+          <t>emp_ui_bill_paid</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>そのゲームはまだ開かれていません。しばらくしてからもう一度お試しください。</t>
+          <t>{0}が請求書を支払いました：{1}（{2}）</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>That game is not open yet. Try again in a moment.</t>
+          <t>{0} paid a bill: {1} ({2})</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>emp_zone_session_empty</t>
+          <t>emp_ui_bill_already_paid</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>ここには他のプレイヤーがいなくなりました</t>
+          <t>この請求書はもう払われています。お金は引かれていません。</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>No other player is here anymore</t>
+          <t>This bill is already paid. Nothing was taken from you.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>emp_ui_timeout_steam</t>
+          <t>emp_ui_sleep_alone</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>ゲームが応答しません。相手が退出したか、接続が切れた可能性があります。</t>
+          <t>あなたは眠りました。世界は進みません：{0} がまだ起きています。</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>The game does not answer: its player may have left or lost the connection.</t>
+          <t>You slept. The world did not move on, as {0} is still awake.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>emp_trade_nothing_to_offer</t>
+          <t>emp_ui_sleep_count</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>提示できるアイテムがありません。</t>
+          <t>{0} は眠っている（{1}/{2}）</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>You have nothing you can offer.</t>
+          <t>{0} is asleep ({1} of {2})</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>emp_ui_reconnecting</t>
+          <t>emp_ui_sleep_all</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>接続が切れました。ゲームに戻っています…</t>
+          <t>全員が眠りました。夜が明けます。</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Connection lost. Getting you back into the game…</t>
+          <t>Everyone is asleep. The night passes.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect_cancel</t>
+          <t>emp_ui_resync</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>マップを整えています…</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Fixing the map…</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect_failed</t>
+          <t>emp_ui_sv_cfg_auto_resync</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ゲームに戻れませんでした。3分間応答がありません。終了した可能性があります。</t>
+          <t>マップを自動で直す</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Could not get back into the game: it has not answered for 3 minutes. It may have ended.</t>
+          <t>Fix the map automatically</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>emp_ui_save_kept</t>
+          <t>emp_ui_sv_desc_auto_resync</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>進行状況は参加中のゲームに保存されます。</t>
+          <t>マップがホストと食い違う（物やキャラが足りない）と、自動で読み込み直します。30秒に1回まで。オフ：違いはログに書くだけ。</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Your progress is kept by the game you joined.</t>
+          <t>If a player's map differs from the host's, with an item or character missing, it loads again by itself, at most every 30 seconds. Unticked, the difference is only logged.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_reconnect</t>
+          <t>emp_ui_bank_deposit</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>接続が切れたプレイヤーは自動で戻る</t>
+          <t>{0}が銀行に{1}を預けました</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Players come back by themselves after a connection loss</t>
+          <t>{0} put {1} in the bank</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_reconnect</t>
+          <t>emp_ui_bank_withdraw</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>オン：接続が切れたプレイヤーは3分間、自動で再参加を試みます。オフ：タイトル画面に戻ります。</t>
+          <t>{0}が銀行から{1}を引き出しました</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>On: a player who loses the connection joins the game again by itself, for 3 minutes. Off: it goes back to the title screen.</t>
+          <t>{0} took {1} out of the bank</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_host</t>
+          <t>emp_ui_sv_cfg_world_copy</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ワールドを読み込むと自動でフレンドに公開する</t>
+          <t>ほかのプレイヤーも世界のコピーを持つ</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>The game opens to friends by itself when a world is loaded</t>
+          <t>Other players keep a copy of the world</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_host</t>
+          <t>emp_ui_sv_desc_world_copy</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>オン：「サーバー起動」を押さなくても、ワールドを読み込むとフレンドが参加できます（土地の確保が必要）。オフ：ホストが自分でサーバーを起動します。</t>
+          <t>自動セーブのたびに、全員のPCが自分のセーブとは別に世界のコピーを保管します。オフ：世界はホストのPCにしかありません。</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>On: friends can join as soon as the world is loaded, without starting the server by hand (the world needs a claimed land). Off: the host starts the server itself.</t>
+          <t>After each automatic save, every player's PC keeps a copy of the world, apart from their own saves. Unticked, only the host's PC has it.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_save</t>
+          <t>emp_ui_sv_cfg_shared_tax</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>他のプレイヤーがいる間、ワールドを自動で保存する</t>
+          <t>税金は最も有名なプレイヤーで計算</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>The world is saved by itself while others play</t>
+          <t>Tax follows the most famous player</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_save</t>
+          <t>emp_ui_sv_desc_shared_tax</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>オン：他のプレイヤーがいる間は2分ごと（保存が重い場合は5分ごと）、最後の一人が抜けた時にも保存します。オフ：ホストが保存した時だけ。</t>
+          <t>毎月の税金は、接続中のプレイヤーでいちばん高い名声で計算します。オフ：ホストの名声で計算（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>On: every 2 minutes while another player is in the game (5 when a save is slow), and when the last one leaves. Off: only when the host saves.</t>
+          <t>Monthly tax uses the highest fame among the players. Unticked, it uses the host's fame, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>emp_ui_load_blocked</t>
+          <t>emp_ui_sv_cfg_soft_recall</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>みんなで遊んでいる間は、セーブデータからロードできません。</t>
+          <t>合流のとき世界を読み込み直さない</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>A shared game cannot be loaded from a save while players are together.</t>
+          <t>Rejoin without reloading the world</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>emp_ui_depot_join_btn</t>
+          <t>emp_ui_sv_desc_soft_recall</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>{0} に参加</t>
+          <t>ホストとプレイヤーが同じマップになるとき、世界全体は読み込み直さず、そのまま、またはそのマップだけを読み込みます。合わないときは従来どおり読み込み直します。オフ：毎回読み込み直します。</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Join {0}</t>
+          <t>When the host and a player meet on one map, the whole world does not reload. Only that map loads, or nothing. If something doesn't match, the world reloads as before. Unticked, it always reloads.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>emp_ui_depot_join_fail</t>
+          <t>emp_ui_sv_cfg_publish_mods</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>{0} が世界を持っていますが、ゲームがまだ開いていません。少し待ってもう一度お試しください。相手のゲームが止まった場合、世界は3分以内に空きます。</t>
+          <t>ゲームのMOD一覧をプレイヤーに見せる</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>{0} has the world, but their game is not open yet. Try again in a moment. If their game stopped, the world is free again within 3 minutes.</t>
+          <t>Show the game's mods to players</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>emp_ui_box_far</t>
+          <t>emp_ui_sv_desc_publish_mods</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>この箱は世界共通で、ホストが保管しています。ホストから離れて他のプレイヤーと一緒にいる間は、入れた物はホストに届きますが、ホストのマップに戻るまで表示されません。</t>
+          <t>参加前（ゲーム一覧）と参加時にMOD一覧が分かり、断られたときは違うMODが名前で表示されます。デポから取った世界では、デポの一覧（modlist.txt）を使います。オフ：何も伝えません。</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>This chest belongs to the whole world and is kept by the host. With other players away from the host, what you put in arrives there, but it only shows again once you are back on the host's map.</t>
+          <t>Players see the mod list before joining and when joining. If refused, they are told which mods differ. For a world from a depot, the depot's list (modlist.txt) is used. Unticked, nothing is shown.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_own_sleep</t>
+          <t>emp_ui_cl_fetch_mods</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>みんな自分のために眠る</t>
+          <t>ゲームのMODをダウンロードする</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Everyone sleeps for themselves</t>
+          <t>Download the game's mods</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_own_sleep</t>
+          <t>emp_ui_cl_desc_fetch_mods</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>オン：ベッドに入ったプレイヤーは誰も待たずにすぐ眠ります。全員が同時に眠ったときだけ、ワールドの夜が明けます。オフ：全員が互いを待ちます。</t>
+          <t>参加するゲームのMODで足りない Workshop のものを、購読せずにダウンロードします。Elin は一度再起動し、自動でゲームに戻ります。MOD一覧は次の起動で元に戻ります。オフ：違うMODを知らせるだけ。</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>On: a player who goes to bed sleeps at once, without waiting for anyone. The night only passes for the world when every player is asleep at the same time. Off: everyone waits for everyone.</t>
+          <t>Missing Workshop mods of the game you join are downloaded without subscribing. Elin restarts once with those mods and comes back by itself. Your own list returns at the next start. Unticked, you are only told which mods differ.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_time_jumps_together</t>
+          <t>emp_ui_mods_lobby</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>時間は全員一緒のときだけ飛ぶ</t>
+          <t>Mod {0} 個</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Time only jumps when everyone jumps</t>
+          <t>{0} mods</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_time_jumps_together</t>
+          <t>emp_ui_mods_lobby_missing</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>オン：ワールドマップの一歩は、全プレイヤーが一緒に旅しているときだけワールドの日付を進めます。それ以外は旅人が自分のターンだけを払います。オフ：誰の一歩でも全員に3時間が加わります。</t>
+          <t>{0} 個のMOD（{1} 個が足りません）</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>On: a step on the world map only moves the date of the world when all the players travel on it together. Otherwise the traveller pays its own turns and the date stays. Off: every step of anyone adds 3 hours for all.</t>
+          <t>{0} mods, {1} missing</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_dump_spares_belt</t>
+          <t>emp_ui_mods_world</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>自動収納は手とベルトに触れない</t>
+          <t>この世界のMODのうち {0} 個が読み込まれていません：{1}。一覧はログにあります。</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Auto-dump spares hand and tool belt</t>
+          <t>{0} mods of this world are not loaded: {1}. The full list is in the log.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_dump_spares_belt</t>
+          <t>emp_ui_mods_missing</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>オン：自動収納は、手に持っている物とツールベルトの中身を収納しません（ホットバーと同じ）。オフ：ゲーム本来の動作。</t>
+          <t>ホストのMODで足りないもの（{0}）：{1}</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>On: auto-dump leaves what you hold and what is in your tool belt, as it leaves the hotbar. Off: as in the game.</t>
+          <t>Host mods you don't have ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>emp_ui_travel_no_date</t>
+          <t>emp_ui_mods_hand</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>仲間は別の場所にいる。この旅では日付は進まない。</t>
+          <t>手動で入れるMOD（{0}）：{1}</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Your friends are elsewhere: your trip does not move the date.</t>
+          <t>Mods to install yourself ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>emp_ui_bill_paid</t>
+          <t>emp_ui_mods_extra</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>{0}が請求書を支払いました：{1}（{2}）</t>
+          <t>ホストにないMOD（{0}）：{1}</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>{0} paid a bill: {1} ({2})</t>
+          <t>Mods the host doesn't have ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>emp_ui_bill_already_paid</t>
+          <t>emp_ui_mods_fetching</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>この請求書はすでに支払い済みです。所持金は減っていません。</t>
+          <t>ゲームのMODをダウンロード中 {0}/{1}：{2} {3}%（Escで中止）</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>This bill is already paid: nothing was taken from you.</t>
+          <t>Downloading the game's mods {0}/{1}: {2} {3}% (Esc to cancel)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_alone</t>
+          <t>emp_ui_mods_fetch_failed</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>眠った。世界の時間は進まなかった：{0} がまだ起きている。</t>
+          <t>ゲームのMODをダウンロードできませんでした。何も変更していません。</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>You slept. The world did not move on: {0} still awake.</t>
+          <t>Could not download the mods. Nothing was changed.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_count</t>
+          <t>emp_ui_mods_restart</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>{0} は眠っている（{1}/{2}）</t>
+          <t>Elin はゲームのMODで再起動し、自動でゲームに戻ります。起動しないときは、Elin をもう一度起動してください。</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>{0} is asleep ({1} of {2})</t>
+          <t>Elin restarts with the game's mods and comes back by itself. If it doesn't start, start Elin again.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_all</t>
+          <t>emp_ui_mods_restart_manual</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>全員が眠った：夜が過ぎていく。</t>
+          <t>Elin を閉じます。もう一度起動すると、ゲームのMODで自動でゲームに戻ります。</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Everyone is asleep: the night passes.</t>
+          <t>Elin closes. Start it again and it comes back to the game by itself, with its mods.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>emp_ui_resync</t>
+          <t>emp_ui_mods_session</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>マップを同期し直しています…</t>
+          <t>今回の Elin は、マルチプレイのMODで動いています。MOD一覧は次の起動で元に戻ります。次回の再起動を省くには、クライアント設定の「ゲームのMODを残す」にチェックしてください。</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Bringing the map up to date…</t>
+          <t>This time Elin runs with the game's mods. Your own list returns at the next start. To skip this restart next time, tick "Keep the game's mods" in Client Settings.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_resync</t>
+          <t>emp_ui_mods_session_locked</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>マップを自動で修復</t>
+          <t>今回はMOD一覧を保存しません。次の起動で元の一覧に戻ります。</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Repair the map by itself</t>
+          <t>The mod list is not saved this time. Yours returns at the next start of Elin.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_resync</t>
+          <t>emp_ui_cl_keep_mods</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>オン：マップがホストと食い違ったプレイヤー（アイテムやキャラクターの欠落）は、自動でマップを読み込み直します（30秒に1回まで）。オフ：食い違いはログに書かれるだけです。</t>
+          <t>ゲームのMODを残す（Workshop で購読）</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>On: a player whose map no longer matches the host's (a missing item or character) loads it again by itself, at most once every 30 seconds. Off: the difference is only written to the log.</t>
+          <t>Keep the game's mods (subscribe on the Workshop)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>emp_ui_bank_deposit</t>
+          <t>emp_ui_cl_desc_keep_mods</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>{0}が銀行に{1}を預けました</t>
+          <t>参加するゲームのMODを Steam アカウントで購読し、自分のMOD一覧に残します。最初の一度だけ再起動し、以降は Elin を閉じても再起動なしで同じゲームに入れます。取り消すには Workshop で購読を解除します。オフ：購読せず取得し、起動後の最初の参加で毎回再起動します。</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>{0} put {1} in the bank</t>
+          <t>Your Steam account subscribes to the mods of the game you join and keeps them on. Elin restarts once, the first time. After that you rejoin the same game with no restart. To undo, unsubscribe on the Workshop. Unticked, Elin restarts at the first join of every start.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>emp_ui_bank_withdraw</t>
+          <t>emp_ui_sv_cfg_takeover</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>{0}が銀行から{1}を引き出しました</t>
+          <t>ホストが抜けたら別のプレイヤーが引き継ぐ</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>{0} took {1} out of the bank</t>
+          <t>Another player takes over when the host leaves</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_copy</t>
+          <t>emp_ui_sv_desc_takeover</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>他のプレイヤーがワールドのコピーを保持する</t>
+          <t>ホストが抜けると、プレイヤーのひとりが自分のコピーから世界を開き、そこでゲームが続きます（「世界のコピー」が必要）。オフ：ホストが抜けるとゲームは終わります。</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>The other players keep a copy of the world</t>
+          <t>When the host leaves, a player opens the world from their copy and the game goes on. Needs the world copy option. Unticked, the game ends with the host.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_copy</t>
+          <t>emp_takeover_begin</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>オン：自動セーブのたびに、各プレイヤーのPCが自分のセーブとは別の場所にワールドのコピーを保存します。オフ：ワールドはホストのPCにしかありません。</t>
+          <t>ホストが抜けました。あなたが世界を引き継ぎます。まもなくここでゲームが続きます。</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>On: after each automatic save, every player's PC keeps a copy of the world, outside its own saves. Off: the world is on the host's PC only.</t>
+          <t>The host left. You take over the world. The game goes on here in a moment.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_shared_tax</t>
+          <t>emp_takeover_leaving</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>税金は最も名声の高いプレイヤーで計算</t>
+          <t>退出中：ほかのプレイヤーに最後のセーブを渡しています…</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Tax on the most famous player</t>
+          <t>Leaving. Giving the last save to the others…</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_tax</t>
+          <t>emp_ui_limited_bought</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>オン：毎月の税金は、接続中のプレイヤーの中で最も高い名声で計算されます。オフ：ホストの名声で計算されます（ゲーム本来の動作）。</t>
+          <t>それはもう買いました。</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>On: the monthly tax is computed on the highest fame among the connected players. Off: on the host's fame, as the game does.</t>
+          <t>You already bought this one.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_soft_recall</t>
+          <t>emp_story_share</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ホストと合流してもワールドを読み込み直さない（新機能）</t>
+          <t>{0}の分け前</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>No world reload when the host and a player meet again (new)</t>
+          <t>{0}'s share</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_soft_recall</t>
+          <t>emp_ui_sv_cfg_once_per_player</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>オン：ホストが、プレイヤーが一人でいるマップに入るとき、またはそのプレイヤーがホストのいるマップに入るとき、ワールド全体を読み込み直しません（その場に残るか、そのマップだけを読み込みます）。食い違いがあれば、これまでどおりワールドを読み込みます。オフ：そのたびにワールドを読み込み直します。</t>
+          <t>一度きりの報酬をプレイヤーごとに</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>On: when the host walks onto the map a player is on alone, or that player walks into the map the host is on, the player does not load the whole world again: it stays where it is, or loads that one map. Should anything not match, the world is loaded as before. Off: the world is loaded again each time.</t>
+          <t>One-time rewards for every player</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_publish_mods</t>
+          <t>emp_ui_sv_desc_once_per_player</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>ゲームのMod一覧を公開する</t>
+          <t>店の限定品と、ストーリーでもらえる物（依頼の報酬、会話の贈り物）が、プレイヤーごとに1回ずつ手に入ります。オフ：最初のひとりだけ（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Show the mods of the game to the players</t>
+          <t>One-time shop goods and story gifts, like quest rewards, go once to each player. Unticked, only the first player gets them, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_publish_mods</t>
+          <t>emp_takeover_rejoin</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>オン：参加前（ゲーム一覧）と参加時にMod一覧が伝えられ、拒否された場合はどのModが違うかが名前で表示されます。デポから取ったワールドではデポの一覧（modlist.txt）を使います。オフ：何も伝えません。</t>
+          <t>別のプレイヤーがこの世界を引き継ぎました。そのゲームに参加します…</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>On: the list of mods is known before joining (list of games) and when joining, and a player who is refused is told which mods differ, by name. For a world taken from a depot it is the depot's list (modlist.txt). Off: nothing is said.</t>
+          <t>Another player took over this world. Joining them…</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>emp_ui_cl_fetch_mods</t>
+          <t>emp_story_share_got</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ゲームのModを自動で取得する（新機能）</t>
+          <t>ストーリーでもらえた物のうち、あなたの分を受け取りました：{0}。</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Fetch the mods of the game by itself (new)</t>
+          <t>You get your share of what the story gave: {0}.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_fetch_mods</t>
+          <t>emp_story_share_mail</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>オン：参加するゲームにあってここに無いワークショップModを、サブスクライブせずにダウンロードし、そのゲームのModだけでElinを1回再起動して自動で戻ります。次の起動で自分のMod一覧に戻ります。オフ：違うModの名前が表示されるだけです。</t>
+          <t>ストーリーでもらえた物のうち、あなたの分（{0}）を拠点の郵便に送りました。</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>On: Workshop mods of the game you join that are missing here are downloaded without subscribing, Elin restarts once with exactly the mods of that game and comes back by itself. Your own mod list is back at the next start. Off: you are only told which mods differ.</t>
+          <t>Your share of what the story gave ({0}) was sent to the base's mail.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>emp_ui_mods_lobby</t>
+          <t>emp_ui_report</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Mod {0} 個</t>
+          <t>不具合レポートを作成</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>{0} mods</t>
+          <t>Prepare a bug report</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>emp_ui_mods_lobby_missing</t>
+          <t>emp_ui_report_desc</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mod {0} 個、うち {1} 個がここにありません</t>
+          <t>ゲームとMODのログをまとめた zip をデスクトップに作ります。セーブと設定ファイルは含みません。不具合を報告するときに送ってください。</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>{0} mods, {1} missing here</t>
+          <t>Writes a zip with the game and mod logs on your desktop. No save, no settings. Send it when you report a problem.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>emp_ui_mods_world</t>
+          <t>emp_ui_report_done</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>このワールドのModのうち {0} 個がここで読み込まれていません：{1}。一覧はログにあります。</t>
+          <t>レポートを作成しました：{0}</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>{0} mods of this world are not loaded here: {1}. The list is in the log.</t>
+          <t>Bug report written: {0}</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>emp_ui_mods_missing</t>
+          <t>emp_ui_report_failed</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>ここに無いホストのMod（{0}）：{1}</t>
+          <t>レポートを作成できませんでした。</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Mods of the host missing here ({0}): {1}</t>
+          <t>The bug report could not be written.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>emp_ui_mods_hand</t>
+          <t>emp_ui_sv_bills</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>手動で入れる必要があるMod（{0}）：{1}</t>
+          <t>未払いの税金請求書：カウント {0}、実在 {1}（修復する）</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Mods to install by hand ({0}): {1}</t>
+          <t>Unpaid tax bills: counted {0}, existing {1} (repair)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>emp_ui_mods_extra</t>
+          <t>emp_ui_sv_bills_desc</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ホストに無いここのMod（{0}）：{1}</t>
+          <t>カウントが実際の請求書より多いとき（古い不具合）、実際の数に合わせます。増やすことはありません。</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Mods only here, not on the host ({0}): {1}</t>
+          <t>If the count is above the bills that exist (an old bug), it is set to the real number. It is never raised.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>emp_ui_mods_fetching</t>
+          <t>emp_ui_sv_bills_done</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>ゲームのModをダウンロード中 {0}/{1}：{2} {3}%（Escで中止）</t>
+          <t>支払えない請求書 {0} 件をカウントから外しました。</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Downloading the mods of the game {0}/{1}: {2} {3}% (Esc to cancel)</t>
+          <t>{0} bill(s) that nothing could pay were taken off the count.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>emp_ui_mods_fetch_failed</t>
+          <t>emp_ui_sv_bills_none</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>ゲームのModをダウンロードできませんでした。何も変更していません。</t>
+          <t>カウントは実在する請求書と一致しています。</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>The mods of the game could not be downloaded. Nothing was changed.</t>
+          <t>The count matches the bills that exist.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>emp_ui_mods_restart</t>
+          <t>emp_ui_chara_delete</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>ElinはゲームのModで再起動し、自動でゲームに戻ります。再起動しない場合は、Elinをもう一度起動してください。</t>
+          <t>キャラクターを削除する</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Elin restarts with the mods of the game and comes back to it by itself. If it does not start, start Elin again.</t>
+          <t>Delete a character</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>emp_ui_mods_restart_manual</t>
+          <t>emp_ui_chara_delete_confirm</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Elinを閉じます。もう一度起動してください：ゲームのModで自動的にゲームへ戻ります。</t>
+          <t>#1 を削除しますか？持ち物も一緒に消えます。仲間はこの世界に残ります。</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Elin closes. Start it again: it comes back to the game by itself, with its mods.</t>
+          <t>Delete #1? Its belongings go with it. Its companions stay in this world.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>emp_ui_mods_session</t>
+          <t>emp_ui_chara_deleted</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>今回のElinはマルチプレイのゲームのModで動いています。次の起動では自分のMod一覧に戻ります。この再起動を次回からなくすには、クライアント設定の「ゲームのModを残す」をオンにしてください。</t>
+          <t>キャラクターを削除しました。</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Elin runs with the mods of the multiplayer game this time. Your own mod list is back at the next start. To skip this restart next time, tick "Keep the mods of the game" in Client Settings.</t>
+          <t>The character was deleted.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>emp_ui_mods_session_locked</t>
+          <t>emp_ui_sv_cfg_delete_chara</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>このセッション中はMod一覧を保存しません。次の起動で自分の一覧に戻ります。</t>
+          <t>プレイヤーが自分のキャラを削除できる</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>The mod list is not saved during this session: your own is back at the next start of Elin.</t>
+          <t>Players can delete their characters</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>emp_ui_cl_keep_mods</t>
+          <t>emp_ui_sv_desc_delete_chara</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>ゲームのModを残す（ワークショップでサブスクライブ）</t>
+          <t>キャラの一覧から削除します（確認は2回）。持ち物も消え、仲間は世界に残ります。</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Keep the mods of the game (subscribe on the Workshop)</t>
+          <t>Done from the character list, with two confirmations. Belongings go too. Companions stay in the world.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_keep_mods</t>
+          <t>emp_world_setting_host</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>オン：参加したゲームのModをSteamアカウントでサブスクライブし、自分のMod一覧でも有効のままにします。最初の一回だけElinが再起動し、その後はElinを閉じても同じゲームに再起動なしで参加できます。やめるには、ワークショップでサブスクライブを解除してください。オフ：サブスクライブせずに取得し、Elinを起動するたびに最初の参加で再起動します。</t>
+          <t>世界の設定はホストのものです。変更は保存されませんでした。</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>On: your Steam account subscribes to the mods of the game you join and they stay on in your own mod list. Elin still restarts once, the first time; after that you join the same game again with no restart, even after closing Elin. To undo, unsubscribe on the Workshop. Off: they are fetched without subscribing and Elin restarts at the first join of every start.</t>
+          <t>World settings belong to the host. Your changes were not kept.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_takeover</t>
+          <t>emp_ui_sv_cfg_auto_combat_per_player</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>ホストが抜けたら他のプレイヤーが引き継ぐ</t>
+          <t>自動戦闘はそれぞれ自分の仲間を守る</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Another player takes over when the host leaves</t>
+          <t>Each player's auto combat protects their own</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_takeover</t>
+          <t>emp_ui_sv_desc_auto_combat_per_player</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>オン：ホストが抜けると、プレイヤーの一人が自分のコピーからワールドを開き、ゲームはそこで続きます（上の「ワールドのコピー」が必要）。オフ：ホストが抜けるとゲームは終わります。</t>
+          <t>自動戦闘を使うプレイヤーと仲間を、そのプレイヤー自身の戦術とスタミナで致命傷から守ります。オフ：ホストの自動戦闘が全員を守り、ゲストのは誰も守りません。</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>On: when the host leaves, a player opens the world from its copy and the game goes on there (needs the copy of the world, above). Off: the game ends with its host.</t>
+          <t>Auto combat saves the player using it, and their companions, from a deadly hit, with their own tactics and stamina. Unticked, the host's auto combat protects everyone and a guest's protects no one.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>emp_takeover_begin</t>
+          <t>emp_duel_win</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ホストが抜けました。あなたがワールドを引き継ぎます。まもなくここでゲームが続きます。</t>
+          <t>{0}との決闘に勝った！</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>The host left. You are taking the world over: the game goes on here in a moment.</t>
+          <t>You win the duel against {0}!</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>emp_takeover_leaving</t>
+          <t>emp_duel_lose</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>退出中：他のプレイヤーに最後のセーブを渡しています…</t>
+          <t>{0}との決闘に負けた。</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Leaving: the other players are getting the last save…</t>
+          <t>You lose the duel against {0}.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>emp_ui_limited_bought</t>
+          <t>emp_duel_wait</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>それはもう買いました。</t>
+          <t>まだ {0} に決闘を申し込めません。</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>You already bought this one.</t>
+          <t>You can't challenge {0} again so soon.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>emp_story_share</t>
+          <t>emp_trade_gold_button</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>{0}の分け前</t>
+          <t>お金</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>{0}'s share</t>
+          <t>Gold</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_once_per_player</t>
+          <t>emp_trade_locked</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>一度きりのものを各プレイヤーに</t>
+          <t>変更があったばかりだ。少し待ってから確定しよう。</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Once per world = once per player</t>
+          <t>The offer just changed. Wait a moment before validating.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_once_per_player</t>
+          <t>emp_trade_log_add</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>オン：店の限定商品とストーリーの報酬を、各プレイヤーが一度ずつ得られます。オフ：最初のプレイヤーだけ（原作通り）。</t>
+          <t>{0}が{1}を差し出した。</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>On: what a shop sells only once and what the story gives (quest rewards, dialog gifts) go once to each player. Off: only the first player, as the game does.</t>
+          <t>{0} offers {1}.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>emp_takeover_rejoin</t>
+          <t>emp_trade_log_remove</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>別のプレイヤーがこの世界を引き継ぎました。そのゲームに参加します…</t>
+          <t>{0}が{1}を引っ込めた。</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Another player took this world over. Joining its game…</t>
+          <t>{0} takes back {1}.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>emp_story_share_got</t>
+          <t>emp_trade_log_gold</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>物語の報酬の分け前を受け取った：{0}</t>
+          <t>{0}の提示額は{1}オレンになった。</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>You receive your share of what the story gave: {0}.</t>
+          <t>{0} now offers {1} gold.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>emp_story_share_mail</t>
+          <t>emp_trade_cant_offer</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>物語の報酬の分け前（{0}）が拠点の郵便受けに届く。</t>
+          <t>{0}は差し出せない。</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Your share of what the story gave ({0}) is sent to the mail of the base.</t>
+          <t>You can't offer {0}.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>emp_ui_report</t>
+          <t>emp_trade_status</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>不具合レポートを作成</t>
+          <t>{0}: {1}オレン、{2}</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Prepare a bug report</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>emp_ui_report_desc</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>ゲームとModのログをまとめたzipをデスクトップに作成します（セーブデータや設定ファイルは含みません）。問題を報告するときに送ってください。</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Writes one zip on your desktop with the logs of the game and of the mod (no save, no settings file). Send it when you report a problem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>emp_ui_report_done</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>レポートを作成しました：{0}</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Bug report written: {0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>emp_ui_report_failed</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>レポートを作成できませんでした。</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>The bug report could not be written.</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_bills</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>未払いの税金請求書：カウント {0}、実在 {1}（修復する）</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Unpaid tax bills: counted {0}, existing {1} (repair)</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_bills_desc</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>カウントが実在する請求書より多い場合（以前の不具合）、実在する数まで下げます。増えることはありません。</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>When the count is above the bills that exist (an old defect), it is brought down to them. It is never raised.</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_bills_done</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>支払えない請求書 {0} 件をカウントから外しました。</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>{0} bill(s) that nothing could pay were taken off the count.</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_bills_none</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>カウントは実在する請求書と一致しています。</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>The count matches the bills that exist.</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>emp_ui_chara_delete</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>キャラクターを削除する</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Delete a character</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>emp_ui_chara_delete_confirm</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>#1 を削除しますか？持ち物も一緒に消えます。仲間はこの世界に残ります。</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Delete #1? What it carries goes with it. Its companions stay in this world.</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>emp_ui_chara_deleted</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>キャラクターを削除しました。</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>The character was deleted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_cfg_delete_chara</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>プレイヤーが自分のキャラクターを削除できる</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Players can delete their characters</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_desc_delete_chara</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>キャラクター選択の一覧から（二度確認）。持ち物も消え、仲間は世界に残る。</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>From the list of characters (asked twice). What it carries goes too; its companions stay in the world.</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>emp_world_setting_host</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>ワールド設定はホストが決めます。変更は保存されませんでした。</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>World settings are the host's: your changes were not kept.</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_cfg_auto_combat_per_player</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>自動戦闘はそれぞれのプレイヤーが自分の仲間を守る</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Each player's auto combat protects its own</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_desc_auto_combat_per_player</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>オン：致命的な一撃から守られるのは、自動戦闘をしているプレイヤーとその仲間です。戦術とスタミナもそのプレイヤーのもの。オフ：ホストの自動戦闘が全員を守り、ゲストの自動戦闘は誰も守りません。</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>On: auto combat saves from a deadly hit the player who runs it and its companions, with that player's tactics and stamina. Off: the host's auto combat protects everyone, a guest's protects no one.</t>
+          <t>{0}: {1} gold, {2}</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D324"/>
+  <dimension ref="A1:D314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Disconnected: client cancelled</t>
+          <t>Disconnected: you cancelled the connection.</t>
         </is>
       </c>
     </row>
@@ -2365,1523 +2365,1370 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>emp_ui_trade</t>
+          <t>emp_trade_invite</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>取引</t>
+          <t>{0} があなたと取引したがっています</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>{0} wants to trade with you</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>emp_trade_invite</t>
+          <t>emp_trade_gold</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{0} があなたと取引したがっています</t>
+          <t>金貨: {0}</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{0} wants to trade with you</t>
+          <t>Gold: {0}</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>emp_trade_you_offer</t>
+          <t>emp_trade_confirm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>あなたの提示</t>
+          <t>確定する</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>You offer</t>
+          <t>Validate</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>emp_trade_they_offer</t>
+          <t>emp_trade_cancel</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{0} の提示</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{0} offers</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>emp_trade_nothing</t>
+          <t>emp_trade_you_ready</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>（まだなし）</t>
+          <t>確定済み</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(nothing yet)</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>emp_trade_add</t>
+          <t>emp_trade_they_ready</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>アイテムを追加</t>
+          <t>確定済み</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Add an item</t>
+          <t>validated</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>emp_trade_gold</t>
+          <t>emp_trade_they_wait</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>金貨: {0}</t>
+          <t>まだ確定していない</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Gold: {0}</t>
+          <t>not validated yet</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>emp_trade_clear</t>
+          <t>emp_trade_howmuch</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>すべて取り下げる</t>
+          <t>金貨はいくら？</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Take everything back</t>
+          <t>How much gold?</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>emp_trade_confirm</t>
+          <t>emp_trade_done</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>確定する</t>
+          <t>取引が完了しました</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Validate</t>
+          <t>Trade done</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>emp_trade_cancel</t>
+          <t>emp_trade_cancelled</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>取引は中止されました</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Trade cancelled</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>emp_trade_you_ready</t>
+          <t>emp_trade_invalid</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>確定済み</t>
+          <t>取引は中止されました：渡すはずの物がもうありません</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Trade cancelled: an item is gone.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>emp_trade_you_wait</t>
+          <t>emp_trade_far</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>あなたは未確認です</t>
+          <t>取引は中止されました：離れすぎです</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>You have not confirmed</t>
+          <t>Trade cancelled: you are too far apart.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>emp_trade_they_ready</t>
+          <t>emp_trade_busy</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>確定済み</t>
+          <t>そのプレイヤーは取引中です</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>validated</t>
+          <t>That player is already trading.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>emp_trade_they_wait</t>
+          <t>emp_ui_sv_note_live</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>まだ確定していない</t>
+          <t>これはホストのルールです。変更はすぐ全員に反映されます。</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>not validated yet</t>
+          <t>These are the host's rules. Changes apply to everyone at once.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>emp_trade_pick</t>
+          <t>emp_ui_sv_sec_players</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>どのアイテム？</t>
+          <t>プレイヤーと移動</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Which item?</t>
+          <t>Players and travel</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>emp_trade_howmany</t>
+          <t>emp_ui_sv_sec_own</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>何個？</t>
+          <t>プレイヤーごとのもの</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>How many?</t>
+          <t>One for each player</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>emp_trade_howmuch</t>
+          <t>emp_ui_sv_sec_time</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>金貨はいくら？</t>
+          <t>時間と戦闘</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>How much gold?</t>
+          <t>Time and combat</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>emp_trade_done</t>
+          <t>emp_ui_sv_sec_checks</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>取引が完了しました</t>
+          <t>参加チェック</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Trade done</t>
+          <t>Joining checks</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>emp_trade_cancelled</t>
+          <t>emp_ui_sv_desc_choose_chara</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>取引は中止されました</t>
+          <t>参加するとき、この世界での自分のキャラを選ぶか、新しく作ります。</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Trade cancelled</t>
+          <t>Joining players pick one of their characters in this world, or make a new one.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>emp_trade_invalid</t>
+          <t>emp_ui_sv_desc_independent_travel</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>取引は中止されました：渡すはずの物がもうありません</t>
+          <t>好きな場所へ、ひとりでも仲間とでも行けます。オフ：全員がホストについていきます。</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item is gone.</t>
+          <t>Players can go anywhere, alone or together. Unticked, everyone follows the host.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>emp_trade_far</t>
+          <t>emp_ui_sv_desc_personal_quests</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>取引は中止されました：離れすぎです</t>
+          <t>依頼は1人5件ずつ。報酬・名声・カルマも別々です。ストーリーは共通です。</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Trade cancelled: you are too far apart.</t>
+          <t>Each player gets 5 quests, with their own reward, fame and karma. Story quests stay shared.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>emp_trade_busy</t>
+          <t>emp_ui_sv_desc_player_shipping</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>そのプレイヤーは取引中です</t>
+          <t>出荷箱のお金は、入れたプレイヤーのものに。オフ：すべてホストへ。</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>That player is already trading.</t>
+          <t>Shipping money goes to the player who put the item in. Unticked, the host gets it all.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>emp_ui_sv_note_live</t>
+          <t>emp_ui_sv_desc_player_trade</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>これはホストのルールです。変更はすぐ全員に反映されます。</t>
+          <t>ほかのプレイヤーをクリックすると、アイテムやお金を取引できます。双方の確認が必要です。</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>These are the host's rules. Changes apply to everyone at once.</t>
+          <t>Click another player to trade items and gold. Both must confirm.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_players</t>
+          <t>emp_ui_sv_desc_combat_time</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>プレイヤーと移動</t>
+          <t>モンスターは、戦っているプレイヤーが動くときに動きます。誰も待ちません。ターン制より優先されます。</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Players and travel</t>
+          <t>A monster acts when the player it fights acts. Nobody waits. This comes before turn-based combat.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_own</t>
+          <t>emp_ui_sv_desc_turn_combat</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>プレイヤーごとのもの</t>
+          <t>戦闘中、プレイヤーは順番に動きます。「戦闘はプレイヤーごとの時間で」がオンのときは無効です。</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>One for each player</t>
+          <t>In a fight, players take turns. Does nothing while "Combat at each player's pace" is ticked.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_time</t>
+          <t>emp_ui_sv_desc_shared_speed</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>時間と戦闘</t>
+          <t>全員が平均の速さで動きます。オフ：それぞれの速さのまま。</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Time and combat</t>
+          <t>Everyone moves at the average speed. Unticked, each keeps their own.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>emp_ui_sv_sec_checks</t>
+          <t>emp_ui_sv_desc_validation</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>参加チェック</t>
+          <t>参加するプレイヤーのゲームが、ホストと同じであるべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Joining checks</t>
+          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_choose_chara</t>
+          <t>emp_ui_sv_cfg_player_clock</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>参加するとき、この世界での自分のキャラを選ぶか、新しく作ります。</t>
+          <t>プレイヤーごとの時間で動く</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Joining players pick one of their characters in this world, or make a new one.</t>
+          <t>Each player moves at their own pace</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_independent_travel</t>
+          <t>emp_ui_sv_desc_player_clock</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>好きな場所へ、ひとりでも仲間とでも行けます。オフ：全員がホストについていきます。</t>
+          <t>ゲストも、ホストと同じなめらかさで動けます。上の項目がオンのときに使えます。</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Players can go anywhere, alone or together. Unticked, everyone follows the host.</t>
+          <t>Guests move as smoothly as the host. Needs the option above.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_personal_quests</t>
+          <t>emp_ui_sv_cfg_step_pace</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>依頼は1人5件ずつ。報酬・名声・カルマも別々です。ストーリーは共通です。</t>
+          <t>全員がひとり用の速さで歩く</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Each player gets 5 quests, with their own reward, fame and karma. Story quests stay shared.</t>
+          <t>Everyone walks as in a solo game</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_shipping</t>
+          <t>emp_ui_sv_desc_step_pace</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>出荷箱のお金は、入れたプレイヤーのものに。オフ：すべてホストへ。</t>
+          <t>歩く速さが、ほかのプレイヤーの速さに左右されません。戦闘では速さが効きます。「戦闘はプレイヤーごとの時間で」が必要です。</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Shipping money goes to the player who put the item in. Unticked, the host gets it all.</t>
+          <t>A step no longer depends on the others' speed. Speed still counts in a fight. Needs "Combat at each player's pace".</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_trade</t>
+          <t>emp_ui_sv_cfg_import_chara</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーをクリックすると、アイテムやお金を取引できます。双方の確認が必要です。</t>
+          <t>自分のセーブのキャラを連れてこられる</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Click another player to trade items and gold. Both must confirm.</t>
+          <t>Players can bring a character from their saves</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_combat_time</t>
+          <t>emp_ui_sv_desc_import_chara</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>モンスターは、戦っているプレイヤーが動くときに動きます。誰も待ちません。ターン制より優先されます。</t>
+          <t>キャラ本人、装備、バッグ、お金、名声とカルマ。仲間、拠点、依頼、銀行は含みません。セーブは読むだけで、変更されません。</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>A monster acts when the player it fights acts. Nobody waits. This comes before turn-based combat.</t>
+          <t>The character, gear, bag, gold, fame and karma. Not companions, base, quests or bank. The save is never changed.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_turn_combat</t>
+          <t>emp_ui_chara_import</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>戦闘中、プレイヤーは順番に動きます。「戦闘はプレイヤーごとの時間で」がオンのときは無効です。</t>
+          <t>自分のセーブのキャラ…</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>In a fight, players take turns. Does nothing while "Combat at each player's pace" is ticked.</t>
+          <t>A character from my saves…</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_speed</t>
+          <t>emp_ui_chara_import_pick</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>全員が平均の速さで動きます。オフ：それぞれの速さのまま。</t>
+          <t>どのセーブのキャラを連れてきますか？（セーブは変更されません）</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Everyone moves at the average speed. Unticked, each keeps their own.</t>
+          <t>Which save? It will not be changed.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_validation</t>
+          <t>emp_ui_chara_import_back</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>参加するプレイヤーのゲームが、ホストと同じであるべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
+          <t>戻る</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_clock</t>
+          <t>emp_ui_chara_import_none</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>プレイヤーごとの時間で動く</t>
+          <t>読み込めるセーブが見つかりません。</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Each player moves at their own pace</t>
+          <t>No save was found.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_clock</t>
+          <t>emp_ui_chara_import_fail</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ゲストも、ホストと同じなめらかさで動けます。上の項目がオンのときに使えます。</t>
+          <t>そのキャラを連れてこられませんでした。</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Guests move as smoothly as the host. Needs the option above.</t>
+          <t>That character can't be brought.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_step_pace</t>
+          <t>emp_ui_chara_import_twice</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>全員がひとり用の速さで歩く</t>
+          <t>そのセーブのキャラは、すでにこの世界にいます。</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Everyone walks as in a solo game</t>
+          <t>That character is already in this world.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_step_pace</t>
+          <t>emp_ui_sv_cfg_world_time</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>歩く速さが、ほかのプレイヤーの速さに左右されません。戦闘では速さが効きます。「戦闘はプレイヤーごとの時間で」が必要です。</t>
+          <t>世界で日付をひとつにする</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>A step no longer depends on the others' speed. Speed still counts in a fight. Needs "Combat at each player's pace".</t>
+          <t>One date for the whole world</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_import_chara</t>
+          <t>emp_ui_sv_desc_world_time</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラを連れてこられる</t>
+          <t>別のマップにひとりでいるプレイヤーの時間も、全員に反映されます。いちばん進んだ日付が世界の日付です。オフ：ホストの日付のみ。</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Players can bring a character from their saves</t>
+          <t>Time spent alone on another map counts for everyone. The latest date is the world's. Unticked, only the host's date counts.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_import_chara</t>
+          <t>emp_ui_sv_cfg_world_keeper</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>キャラ本人、装備、バッグ、お金、名声とカルマ。仲間、拠点、依頼、銀行は含みません。セーブは読むだけで、変更されません。</t>
+          <t>時間の影響を一度だけ起こす</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>The character, gear, bag, gold, fame and karma. Not companions, base, quests or bank. The save is never changed.</t>
+          <t>Time affects the world only once</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import</t>
+          <t>emp_ui_sv_desc_world_keeper</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラ…</t>
+          <t>天気、依頼の期限切れ、税金、給料、手紙は、ひとりのゲームだけが処理します。オフ：マップを持つ全員が処理します。</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>A character from my saves…</t>
+          <t>Weather, expired quests, taxes, salaries and letters are handled by one player only. Unticked, every player holding a map handles them.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_pick</t>
+          <t>emp_ui_depot_take</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>どのセーブのキャラを連れてきますか？（セーブは変更されません）</t>
+          <t>デポから世界を取り出してホストする</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Which save? It will not be changed.</t>
+          <t>Take the world from the depot and host it</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_back</t>
+          <t>emp_ui_depot_put</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>戻る</t>
+          <t>このセーブをデポに置く</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Put this save in the depot</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_none</t>
+          <t>emp_ui_depot_held</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>読み込めるセーブが見つかりません。</t>
+          <t>{0} が世界をホスト中です。Steam で参加してください。招待してもらうか、Steam のフレンド一覧で「ゲームに参加」を選びます。抜けた直後なら、3分ほど待ってください。</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>No save was found.</t>
+          <t>{0} is hosting the world. Join through Steam: ask for an invite, or use "Join Game" on their name in your friends list. If they just left, wait up to 3 minutes.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_fail</t>
+          <t>emp_ui_depot_empty</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>そのキャラを連れてこられませんでした。</t>
+          <t>デポにはまだ世界がありません。ゲームを始めるかロードして、このパネルをもう一度開き、ロビーのタブで「このセーブをデポに置く」を選んでください。</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>That character can't be brought.</t>
+          <t>The depot has no world yet. Start or load a game, then open this panel again and use "Put this save in the depot" in the Lobby tab.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>emp_ui_chara_import_twice</t>
+          <t>emp_ui_depot_fail</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>そのセーブのキャラは、すでにこの世界にいます。</t>
+          <t>デポに接続できませんでした。</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>That character is already in this world.</t>
+          <t>Could not reach the depot.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_time</t>
+          <t>emp_ui_depot_put_done</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>世界で日付をひとつにする</t>
+          <t>この世界をデポに置きました。ゲームはそこから読み込み直します。これからのセーブはすべてデポに送られます。</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>One date for the whole world</t>
+          <t>The world is now in the depot. The game loads it again from there. From now on, every save goes to the depot.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_time</t>
+          <t>emp_ui_depot_folder</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>別のマップにひとりでいるプレイヤーの時間も、全員に反映されます。いちばん進んだ日付が世界の日付です。オフ：ホストの日付のみ。</t>
+          <t>デポ</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Time spent alone on another map counts for everyone. The latest date is the world's. Unticked, only the host's date counts.</t>
+          <t>Depot</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_keeper</t>
+          <t>emp_ui_depot_folder_ask</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>時間の影響を一度だけ起こす</t>
+          <t>セーブの置き場所：Elin Together Server のアドレス（ホスト:55557）、全員が使えるフォルダ、または非公開の GitHub リポジトリ（github:ユーザー/リポジトリ）。空欄なら使いません</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Time affects the world only once</t>
+          <t>Where the world is kept: the address of Elin Together Server (host:55557), a folder everyone can reach, or a private GitHub repository (github:owner/repository). Leave empty for none.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_keeper</t>
+          <t>emp_ui_join_address</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>天気、依頼の期限切れ、税金、給料、手紙は、ひとりのゲームだけが処理します。オフ：マップを持つ全員が処理します。</t>
+          <t>アドレスで参加</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Weather, expired quests, taxes, salaries and letters are handled by one player only. Unticked, every player holding a map handles them.</t>
+          <t>Join by address</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>emp_ui_depot_take</t>
+          <t>emp_ui_join_address_ask</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>デポから世界を取り出してホストする</t>
+          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、なしは 55557）</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Take the world from the depot and host it</t>
+          <t>Server address (host:port). The port is 55556 with Elin, 55557 without.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put</t>
+          <t>emp_ui_depot_password</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>このセーブをデポに置く</t>
+          <t>デポのキー</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Put this save in the depot</t>
+          <t>Depot key</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>emp_ui_depot_held</t>
+          <t>emp_ui_depot_password_ask</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{0} が世界をホスト中です。Steam で参加してください。招待してもらうか、Steam のフレンド一覧で「ゲームに参加」を選びます。抜けた直後なら、3分ほど待ってください。</t>
+          <t>デポのパスワード（設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。変えないなら空欄のままにしてください</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{0} is hosting the world. Join through Steam: ask for an invite, or use "Join Game" on their name in your friends list. If they just left, wait up to 3 minutes.</t>
+          <t>The depot password (if one was set), or the GitHub key. A key is never shown again. Leave empty to keep it.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>emp_ui_depot_empty</t>
+          <t>emp_ui_timeout</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>デポにはまだ世界がありません。ゲームを始めるかロードして、このパネルをもう一度開き、ロビーのタブで「このセーブをデポに置く」を選んでください。</t>
+          <t>サーバーが応答しません。アドレスとポートを確認してください。</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>The depot has no world yet. Start or load a game, then open this panel again and use "Put this save in the depot" in the Lobby tab.</t>
+          <t>The server does not answer. Check the address and the port.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>emp_ui_depot_fail</t>
+          <t>emp_ui_depot_password_wrong</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>デポに接続できませんでした。</t>
+          <t>サーバーにパスワードを断られました。クライアント設定の「デポのキー」で設定してください。</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Could not reach the depot.</t>
+          <t>The server refused the password. Set it in Client Settings, under "Depot key".</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>emp_ui_depot_put_done</t>
+          <t>emp_ui_depot_lost</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>この世界をデポに置きました。ゲームはそこから読み込み直します。これからのセーブはすべてデポに送られます。</t>
+          <t>接続が切れている間に、{0} がデポの世界を引き継ぎました。これ以降のプレイはデポに届きません。タイトルに戻って、その人のゲームに参加してください。</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>The world is now in the depot. The game loads it again from there. From now on, every save goes to the depot.</t>
+          <t>{0} took over the world while you were cut off. What you play now won't reach the depot. Go back to the title screen and join them.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder</t>
+          <t>emp_ui_depot_unsaved</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>デポ</t>
+          <t>デポにセーブが届きませんでした。このPCに残してあり、次のセーブでもう一度送ります。</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Depot</t>
+          <t>The save didn't reach the depot. It is kept on this PC and sent again at the next save.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>emp_ui_depot_folder_ask</t>
+          <t>emp_ui_depot_unsent</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>セーブの置き場所：Elin Together Server のアドレス（ホスト:55557）、全員が使えるフォルダ、または非公開の GitHub リポジトリ（github:ユーザー/リポジトリ）。空欄なら使いません</t>
+          <t>前回の最後のセーブが、デポに届いていません。今送りますか？（はい：デポにある世界は別に取っておきます。いいえ：このセーブは捨てて、デポの世界を使います。）</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Where the world is kept: the address of Elin Together Server (host:55557), a folder everyone can reach, or a private GitHub repository (github:owner/repository). Leave empty for none.</t>
+          <t>Your last save never reached the depot. Send it now? Yes keeps the depot's world aside. No drops your save and uses the depot's world.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>emp_ui_join_address</t>
+          <t>emp_quest_follow_ask</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>アドレスで参加</t>
+          <t>{0} が依頼に出かけます。ついていきますか？報酬は {0} のものになります。</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Join by address</t>
+          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>emp_ui_join_address_ask</t>
+          <t>emp_quest_follow_declined</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>サーバーのアドレス（ホスト:ポート。Elin ありは 55556、なしは 55557）</t>
+          <t>{0} は同行を断りました。</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Server address (host:port). The port is 55556 with Elin, 55557 without.</t>
+          <t>{0} won't come along.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password</t>
+          <t>emp_quest_follow_no_answer</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>デポのキー</t>
+          <t>{0} から返事がありません。</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Depot key</t>
+          <t>{0} didn't answer.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_ask</t>
+          <t>emp_quest_follow_asked</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>デポのパスワード（設定した場合）、または GitHub のアクセスキー。キーは二度と表示されません。変えないなら空欄のままにしてください</t>
+          <t>{0} に同行を頼んでいます…</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>The depot password (if one was set), or the GitHub key. A key is never shown again. Leave empty to keep it.</t>
+          <t>Asking {0} to come along...</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>emp_ui_timeout</t>
+          <t>emp_base_host_only</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>サーバーが応答しません。アドレスとポートを確認してください。</t>
+          <t>今はホストだけができます。</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>The server does not answer. Check the address and the port.</t>
+          <t>Only the host can do this for now.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>emp_ui_depot_password_wrong</t>
+          <t>emp_trade_equipped</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>サーバーにパスワードを断られました。クライアント設定の「デポのキー」で設定してください。</t>
+          <t>取引は中止されました：渡す物が装備中です</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>The server refused the password. Set it in Client Settings, under "Depot key".</t>
+          <t>Trade cancelled: an item is equipped.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>emp_ui_depot_lost</t>
+          <t>emp_trade_nodrop</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>接続が切れている間に、{0} がデポの世界を引き継ぎました。これ以降のプレイはデポに届きません。タイトルに戻って、その人のゲームに参加してください。</t>
+          <t>取引は中止されました：捨てられない物、渡せない物があります</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>{0} took over the world while you were cut off. What you play now won't reach the depot. Go back to the title screen and join them.</t>
+          <t>Trade cancelled: an item can't be given away.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsaved</t>
+          <t>emp_trade_npcprop</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>デポにセーブが届きませんでした。このPCに残してあり、次のセーブでもう一度送ります。</t>
+          <t>取引は中止されました：NPCの持ち物が含まれています</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>The save didn't reach the depot. It is kept on this PC and sent again at the next save.</t>
+          <t>Trade cancelled: an item belongs to an NPC.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>emp_ui_depot_unsent</t>
+          <t>emp_trade_gifted</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>前回の最後のセーブが、デポに届いていません。今送りますか？（はい：デポにある世界は別に取っておきます。いいえ：このセーブは捨てて、デポの世界を使います。）</t>
+          <t>取引は中止されました：贈り物は取引できません</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Your last save never reached the depot. Send it now? Yes keeps the depot's world aside. No drops your save and uses the depot's world.</t>
+          <t>Trade cancelled: a gift can't be traded.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>emp_quest_follow_ask</t>
+          <t>emp_trade_bound</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{0} が依頼に出かけます。ついていきますか？報酬は {0} のものになります。</t>
+          <t>取引は中止されました：キャラに結びついた物があります</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>{0} is leaving on a quest. Go along? The reward goes to {0}.</t>
+          <t>Trade cancelled: an item is bound to a character.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>emp_quest_follow_declined</t>
+          <t>emp_trade_full</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{0} は同行を断りました。</t>
+          <t>取引は中止されました：バッグの空きが足りません</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>{0} won't come along.</t>
+          <t>Trade cancelled: a bag is full.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>emp_quest_follow_no_answer</t>
+          <t>emp_travel_recalled_by</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{0} から返事がありません。</t>
+          <t>{@Peer} がここに来ます。合流のため画面を読み込み直します…</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>{0} didn't answer.</t>
+          <t>{@Peer} is coming here. The screen reloads to join them…</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>emp_quest_follow_asked</t>
+          <t>emp_ui_thing_gone</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{0} に同行を頼んでいます…</t>
+          <t>遅かった：ほかの人が先に取りました</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Asking {0} to come along...</t>
+          <t>Too late. Someone else took it.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>emp_base_host_only</t>
+          <t>emp_base_refused</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>今はホストだけができます。</t>
+          <t>ホストに断られました：拠点か所持金では払えません。</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Only the host can do this for now.</t>
+          <t>The host refused. The base or your purse can't pay for this.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>emp_trade_equipped</t>
+          <t>emp_base_pending</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>取引は中止されました：渡す物が装備中です</t>
+          <t>前の頼みが、まだホストの返事待ちです。</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item is equipped.</t>
+          <t>Your last request is still waiting for the host.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>emp_trade_nodrop</t>
+          <t>emp_game_version_differs</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>取引は中止されました：捨てられない物、渡せない物があります</t>
+          <t>{0} の Elin はバージョンが違います（{1}、自分は {2}）。接続はできます。問題が起きたら同じバージョンにしてください。</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item can't be given away.</t>
+          <t>{0} has another version of Elin ({1}, yours is {2}). You can still join. If something goes wrong, use the same version.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>emp_trade_npcprop</t>
+          <t>emp_ui_sv_cfg_same_game_version</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>取引は中止されました：NPCの持ち物が含まれています</t>
+          <t>同じ Elin のバージョンを必須にする</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item belongs to an NPC.</t>
+          <t>Require the same Elin version</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>emp_trade_gifted</t>
+          <t>emp_ui_sv_desc_same_game_version</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>取引は中止されました：贈り物は取引できません</t>
+          <t>Elin のバージョンが違うプレイヤーは入れません。オフ：警告つきで入れます。MODのバージョンは常に同じである必要があります。</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Trade cancelled: a gift can't be traded.</t>
+          <t>Players with another Elin version can't join. Unticked, they join with a warning. The mod version must always match.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>emp_trade_bound</t>
+          <t>emp_ui_sv_cfg_guest_build</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>取引は中止されました：キャラに結びついた物があります</t>
+          <t>ほかのプレイヤーも建築できる</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Trade cancelled: an item is bound to a character.</t>
+          <t>Other players can build</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>emp_trade_full</t>
+          <t>emp_ui_sv_desc_guest_build</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>取引は中止されました：バッグの空きが足りません</t>
+          <t>拠点の建築モード（床、壁、家具、採掘、伐採）を使えます。お金と素材は本人が払います。オフ：建築できるのはホストだけ。</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Trade cancelled: a bag is full.</t>
+          <t>Others can use build mode in the base: floors, walls, furniture, mining, cutting. They pay the gold and materials. Unticked, only the host builds.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>emp_travel_recalled_by</t>
+          <t>emp_ui_depot_gh_help</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
-        <is>
-          <t>{@Peer} がここに来ます。合流のため画面を読み込み直します…</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>{@Peer} is coming here. The screen reloads to join them…</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>emp_ui_thing_gone</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>遅かった：ほかの人が先に取りました</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Too late. Someone else took it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>emp_base_refused</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>ホストに断られました：拠点か所持金では払えません。</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>The host refused. The base or your purse can't pay for this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>emp_base_pending</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>前の頼みが、まだホストの返事待ちです。</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Your last request is still waiting for the host.</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>emp_game_version_differs</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>{0} の Elin はバージョンが違います（{1}、自分は {2}）。接続はできます。問題が起きたら同じバージョンにしてください。</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>{0} has another version of Elin ({1}, yours is {2}). You can still join. If something goes wrong, use the same version.</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_cfg_same_game_version</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>同じ Elin のバージョンを必須にする</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Require the same Elin version</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_desc_same_game_version</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Elin のバージョンが違うプレイヤーは入れません。オフ：警告つきで入れます。MODのバージョンは常に同じである必要があります。</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Players with another Elin version can't join. Unticked, they join with a warning. The mod version must always match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_cfg_guest_build</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>ほかのプレイヤーも建築できる</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Other players can build</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>emp_ui_sv_desc_guest_build</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>拠点の建築モード（床、壁、家具、採掘、伐採）を使えます。お金と素材は本人が払います。オフ：建築できるのはホストだけ。</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Others can use build mode in the base: floors, walls, furniture, mining, cutting. They pay the gold and materials. Unticked, only the host builds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>emp_ui_depot_gh_help</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
         <is>
           <t>非公開の GitHub リポジトリを、デポにできます。サーバーも共有フォルダも要らず、友達に GitHub アカウントも要りません。
 1. github.com で、この世界専用の空の非公開リポジトリを作ります。
@@ -3890,7 +3737,7 @@
 4. 同じ2行を友達に送ります。友達もここに入力します。キーで開けるのはこのリポジトリだけです。</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>A private GitHub repository can be the depot. No server, no shared folder, and your friends need no GitHub account.
 1. On github.com, create an empty private repository just for this world.
@@ -3900,2058 +3747,2041 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_key</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>GitHub にアクセスキーを断られました。期限切れでないか、このリポジトリを含み「Contents: Read and write」であるかを確認して、クライアント設定でもう一度貼ってください。</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>GitHub refused the key. Check that it hasn't expired and covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_missing</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>GitHub でこのリポジトリが見つかりません。クライアント設定で名前（github:ユーザー/リポジトリ）を確認し、アクセスキーがそれを含んでいるか確認してください。</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>GitHub can't find the repository. Check its name (github:owner/repository) in Client Settings, and that your key covers it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_public</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>この GitHub リポジトリは公開です。世界とその履歴が誰にでも見えてしまいます。非公開に変えて（Settings、Danger Zone、Change visibility）、もう一度試してください。</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>This GitHub repository is public. Everyone could see your world and its history. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_big</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>この世界は20MBを超えていて、GitHub には大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに残っています。</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>This world is over 20 MB, too big for GitHub. Use Elin Together Server or a shared folder. The save stays on this PC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_changed</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>接続が切れている間に、別の人が世界をホストしてセーブしました。あなたのセーブはこのPCに残り、これ以上デポに送られません。タイトルに戻って、世界を取り直してください。</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Someone else hosted the world and saved while you were cut off. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>emp_ui_depot_gh_down</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>GitHub が応答しません。接続を確認して、少し待ってからもう一度試してください。</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_player_kill</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>プレイヤー同士で倒せる</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Players can kill each other</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_player_kill</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>プレイヤーや仲間の攻撃で、ほかのプレイヤーを倒せます。オフ：致命傷でもHP0で生き残ります。</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Players and their companions can kill other players. Unticked, a deadly blow leaves them alive at 0 HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_host_manages_base</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>拠点を管理できるのはホストだけ</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Only the host manages the base</t>
+        </is>
+      </c>
+    </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_key</t>
+          <t>emp_ui_sv_desc_host_manages_base</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>GitHub にアクセスキーを断られました。期限切れでないか、このリポジトリを含み「Contents: Read and write」であるかを確認して、クライアント設定でもう一度貼ってください。</t>
+          <t>ほかのプレイヤーの拠点操作（研究、炉の技能、方針、名前、設定、住人、建築）は断られます。オフ：全員がホストと同じように管理できます。拠点を完全に手放せるのは常にホストだけです。</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>GitHub refused the key. Check that it hasn't expired and covers this repository with "Contents: Read and write", then paste it again in Client Settings.</t>
+          <t>Others can't change the base: research, hearth skills, policies, names, settings, residents, build mode. Unticked, all can. Only the host can give up the base for good.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_missing</t>
+          <t>emp_ui_sv_cfg_duels</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>GitHub でこのリポジトリが見つかりません。クライアント設定で名前（github:ユーザー/リポジトリ）を確認し、アクセスキーがそれを含んでいるか確認してください。</t>
+          <t>プレイヤー同士の決闘</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>GitHub can't find the repository. Check its name (github:owner/repository) in Client Settings, and that your key covers it.</t>
+          <t>Duels between players</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_public</t>
+          <t>emp_ui_sv_desc_duels</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>この GitHub リポジトリは公開です。世界とその履歴が誰にでも見えてしまいます。非公開に変えて（Settings、Danger Zone、Change visibility）、もう一度試してください。</t>
+          <t>相手のキャラのメニューから決闘を申し込めます。誰も死なず、終わると全員回復し、何も失いません。</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>This GitHub repository is public. Everyone could see your world and its history. Make it private (Settings, Danger Zone, Change visibility), then try again.</t>
+          <t>Challenge another player from the menu on their character. Nobody dies, both are healed and nothing is lost.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_big</t>
+          <t>emp_act_duel</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>この世界は20MBを超えていて、GitHub には大きすぎます。Elin Together Server か共有フォルダを使ってください。セーブはこのPCに残っています。</t>
+          <t>決闘を申し込む</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>This world is over 20 MB, too big for GitHub. Use Elin Together Server or a shared folder. The save stays on this PC.</t>
+          <t>Challenge to a duel</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_changed</t>
+          <t>emp_duel_invite</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>接続が切れている間に、別の人が世界をホストしてセーブしました。あなたのセーブはこのPCに残り、これ以上デポに送られません。タイトルに戻って、世界を取り直してください。</t>
+          <t>{0}が決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Someone else hosted the world and saved while you were cut off. Your saves stay on this PC and no longer reach the depot. Go back to the title screen and take the world again.</t>
+          <t>{0} challenges you to a duel. Nobody dies, but what you use up stays used. Accept?</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>emp_ui_depot_gh_down</t>
+          <t>emp_duel_asked</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>GitHub が応答しません。接続を確認して、少し待ってからもう一度試してください。</t>
+          <t>{0} に決闘を申し込みました…</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>GitHub does not answer. Check your connection and try again in a moment.</t>
+          <t>You challenge {0} to a duel…</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_player_kill</t>
+          <t>emp_duel_countdown</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>プレイヤー同士で倒せる</t>
+          <t>{0} と {1} が向かい合います。3秒後に決闘開始。</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Players can kill each other</t>
+          <t>{0} and {1} face each other. The duel starts in 3 seconds.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_player_kill</t>
+          <t>emp_duel_fight</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>プレイヤーや仲間の攻撃で、ほかのプレイヤーを倒せます。オフ：致命傷でもHP0で生き残ります。</t>
+          <t>始め！</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Players and their companions can kill other players. Unticked, a deadly blow leaves them alive at 0 HP.</t>
+          <t>Fight!</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_host_manages_base</t>
+          <t>emp_duel_declined</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>拠点を管理できるのはホストだけ</t>
+          <t>決闘を断られました。</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Only the host manages the base</t>
+          <t>Your challenge was declined.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_host_manages_base</t>
+          <t>emp_duel_noanswer</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーの拠点操作（研究、炉の技能、方針、名前、設定、住人、建築）は断られます。オフ：全員がホストと同じように管理できます。拠点を完全に手放せるのは常にホストだけです。</t>
+          <t>決闘の返事がありません。</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Others can't change the base: research, hearth skills, policies, names, settings, residents, build mode. Unticked, all can. Only the host can give up the base for good.</t>
+          <t>Nobody answered your challenge.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_duels</t>
+          <t>emp_duel_busy</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>プレイヤー同士の決闘</t>
+          <t>そのプレイヤーは決闘中か取引中です。</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Duels between players</t>
+          <t>That player is busy in a duel or a trade.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_duels</t>
+          <t>emp_duel_over</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>相手のキャラのメニューから決闘を申し込めます。誰も死なず、終わると全員回復し、何も失いません。</t>
+          <t>決闘は引き分けです。</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Challenge another player from the menu on their character. Nobody dies, both are healed and nothing is lost.</t>
+          <t>The duel ends in a draw.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>emp_act_duel</t>
+          <t>emp_handover_failed</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>決闘を申し込む</t>
+          <t>キャラ {0} はこの世界に入れませんでした（死亡しています）。セーブのキャラで遊びます。</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Challenge to a duel</t>
+          <t>Your character {0} can't join this world because it is dead. You play the character of the save.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>emp_duel_invite</t>
+          <t>emp_ui_depot_held_btn</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{0}が決闘を申し込んできた。誰も死なないが、使った物は戻らない。受けますか？</t>
+          <t>{0} が世界をホスト中</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>{0} challenges you to a duel. Nobody dies, but what you use up stays used. Accept?</t>
+          <t>{0} is hosting the world</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>emp_duel_asked</t>
+          <t>emp_error_connection</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{0} に決闘を申し込みました…</t>
+          <t>接続できません：ゲームが応答しません。ゲームが開いているか確認して、もう一度試してください。</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>You challenge {0} to a duel…</t>
+          <t>Could not connect. The game does not answer. Check that it is open, then try again.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>emp_duel_countdown</t>
+          <t>emp_not_allowed</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{0} と {1} が向かい合います。3秒後に決闘開始。</t>
+          <t>このゲームには、Steam ロビーから参加したプレイヤーしか入れません。</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>{0} and {1} face each other. The duel starts in 3 seconds.</t>
+          <t>Only players who join through its Steam lobby can enter this game.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>emp_duel_fight</t>
+          <t>emp_connection_no_server</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>始め！</t>
+          <t>そのゲームはまだ開いていません。少し待ってからもう一度試してください。</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Fight!</t>
+          <t>That game is not open yet. Try again in a moment.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>emp_duel_declined</t>
+          <t>emp_zone_session_empty</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>決闘を断られました。</t>
+          <t>ここにはもう誰もいません</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Your challenge was declined.</t>
+          <t>Nobody else is here anymore.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>emp_duel_noanswer</t>
+          <t>emp_ui_timeout_steam</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>決闘の返事がありません。</t>
+          <t>ゲームが応答しません。相手が抜けたか、接続が切れたのかもしれません。</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Nobody answered your challenge.</t>
+          <t>The game does not answer. The player may have left or lost the connection.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>emp_duel_busy</t>
+          <t>emp_ui_reconnecting</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>そのプレイヤーは決闘中か取引中です。</t>
+          <t>接続が切れました。ゲームに戻っています…</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>That player is busy in a duel or a trade.</t>
+          <t>Connection lost. Going back into the game…</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>emp_duel_over</t>
+          <t>emp_ui_reconnect_cancel</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>決闘は引き分けです。</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>The duel ends in a draw.</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>emp_handover_failed</t>
+          <t>emp_ui_reconnect_failed</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>キャラ {0} はこの世界に入れませんでした（死亡しています）。セーブのキャラで遊びます。</t>
+          <t>ゲームに戻れませんでした。3分間応答がなく、終わった可能性があります。</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Your character {0} can't join this world because it is dead. You play the character of the save.</t>
+          <t>Could not get back into the game. It didn't answer for 3 minutes and may be over.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>emp_ui_depot_held_btn</t>
+          <t>emp_ui_save_kept</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>{0} が世界をホスト中</t>
+          <t>進行状況は、参加したゲームが保存します。</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>{0} is hosting the world</t>
+          <t>The game you joined keeps your progress.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>emp_error_connection</t>
+          <t>emp_ui_sv_cfg_auto_reconnect</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>接続できません：ゲームが応答しません。ゲームが開いているか確認して、もう一度試してください。</t>
+          <t>切れたプレイヤーは自動で戻る</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Could not connect. The game does not answer. Check that it is open, then try again.</t>
+          <t>Players rejoin by themselves after a drop</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>emp_not_allowed</t>
+          <t>emp_ui_sv_desc_auto_reconnect</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>このゲームには、Steam ロビーから参加したプレイヤーしか入れません。</t>
+          <t>接続が切れたプレイヤーは、3分間自動で再参加を試みます。オフ：タイトルに戻ります。</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Only players who join through its Steam lobby can enter this game.</t>
+          <t>A player who drops tries to rejoin for 3 minutes. Unticked, they go back to the title screen.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>emp_connection_no_server</t>
+          <t>emp_ui_sv_cfg_auto_host</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>そのゲームはまだ開いていません。少し待ってからもう一度試してください。</t>
+          <t>世界を読み込むと自動でフレンドに公開</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>That game is not open yet. Try again in a moment.</t>
+          <t>Open the game to friends when a world loads</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>emp_zone_session_empty</t>
+          <t>emp_ui_sv_desc_auto_host</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ここにはもう誰もいません</t>
+          <t>世界を読み込むとすぐ、サーバーを手で始めなくてもフレンドが参加できます（所有した土地が必要）。オフ：ホストが自分でサーバーを始めます。</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Nobody else is here anymore.</t>
+          <t>Friends can join as soon as the world loads, with no need to start the server. The world needs a claimed land. Unticked, the host starts the server.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>emp_ui_timeout_steam</t>
+          <t>emp_ui_sv_cfg_auto_save</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ゲームが応答しません。相手が抜けたか、接続が切れたのかもしれません。</t>
+          <t>他のプレイヤーがいる間は自動でセーブ</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>The game does not answer. The player may have left or lost the connection.</t>
+          <t>Save automatically while others play</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>emp_trade_nothing_to_offer</t>
+          <t>emp_ui_sv_desc_auto_save</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>渡せる物がありません。</t>
+          <t>他のプレイヤーがいる間は2分ごと（遅いときは5分ごと）と、最後の人が抜けたときにセーブします。オフ：ホストがセーブしたときだけ。</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>You have nothing to offer.</t>
+          <t>Saves every 2 minutes while others are in the game (5 if saving is slow), and when the last one leaves. Unticked, only when the host saves.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>emp_ui_reconnecting</t>
+          <t>emp_ui_load_blocked</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>接続が切れました。ゲームに戻っています…</t>
+          <t>みんなで遊んでいる間は、セーブをロードできません。</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Connection lost. Going back into the game…</t>
+          <t>You can't load a save while players are together.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect_cancel</t>
+          <t>emp_ui_depot_join_btn</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>{0} に参加</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Join {0}</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>emp_ui_reconnect_failed</t>
+          <t>emp_ui_depot_join_fail</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>ゲームに戻れませんでした。3分間応答がなく、終わった可能性があります。</t>
+          <t>{0} が世界を持っていますが、そのゲームはまだ開いていません。少し待ってからもう一度試してください。ゲームが止まっていたら、3分以内に世界は空きます。</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Could not get back into the game. It didn't answer for 3 minutes and may be over.</t>
+          <t>{0} has the world, but their game is not open yet. Try again in a moment. If their game stopped, the world is free again within 3 minutes.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>emp_ui_save_kept</t>
+          <t>emp_ui_box_far</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>進行状況は、参加したゲームが保存します。</t>
+          <t>この箱は世界全体のもので、ホストが預かっています。ホストから離れていても入れた物はホストに届きますが、ホストのマップに戻るまで表示されません。</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>The game you joined keeps your progress.</t>
+          <t>This chest belongs to the whole world and the host keeps it. If you are away from the host, what you put in still arrives, but you only see it again back on the host's map.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_reconnect</t>
+          <t>emp_ui_sv_cfg_own_sleep</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>切れたプレイヤーは自動で戻る</t>
+          <t>各自で眠る</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Players rejoin by themselves after a drop</t>
+          <t>Everyone sleeps on their own</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_reconnect</t>
+          <t>emp_ui_sv_desc_own_sleep</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>接続が切れたプレイヤーは、3分間自動で再参加を試みます。オフ：タイトルに戻ります。</t>
+          <t>ベッドに入ったプレイヤーはすぐ眠れます。夜が明けるのは、全員が同時に眠っているときだけです。オフ：全員が揃うまで待ちます。</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>A player who drops tries to rejoin for 3 minutes. Unticked, they go back to the title screen.</t>
+          <t>A player in bed sleeps at once. The night passes only when everyone sleeps at the same time. Unticked, everyone waits for everyone.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_host</t>
+          <t>emp_ui_sv_cfg_time_jumps_together</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>世界を読み込むと自動でフレンドに公開</t>
+          <t>全員一緒のときだけ時間が進む</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Open the game to friends when a world loads</t>
+          <t>Time moves only when all travel together</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_host</t>
+          <t>emp_ui_sv_desc_time_jumps_together</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>世界を読み込むとすぐ、サーバーを手で始めなくてもフレンドが参加できます（所有した土地が必要）。オフ：ホストが自分でサーバーを始めます。</t>
+          <t>ワールドマップの一歩で日付が進むのは、全員が一緒に旅しているときだけです。そうでなければ旅人だけがターンを消費します。オフ：誰かの一歩ごとに全員が3時間進みます。</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Friends can join as soon as the world loads, with no need to start the server. The world needs a claimed land. Unticked, the host starts the server.</t>
+          <t>On the world map, the date moves only when all players travel together. Otherwise only the traveller's turns pass. Unticked, every step by anyone adds 3 hours for all.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_save</t>
+          <t>emp_ui_sv_cfg_dump_spares_belt</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>他のプレイヤーがいる間は自動でセーブ</t>
+          <t>自動整理で手持ちとツールベルトを残す</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Save automatically while others play</t>
+          <t>Auto-dump leaves your hands and tool belt alone</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_save</t>
+          <t>emp_ui_sv_desc_dump_spares_belt</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>他のプレイヤーがいる間は2分ごと（遅いときは5分ごと）と、最後の人が抜けたときにセーブします。オフ：ホストがセーブしたときだけ。</t>
+          <t>手に持っている物とツールベルトの中身は、ホットバーと同じように、まとめて入れても残ります。オフ：元のゲームと同じ。</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Saves every 2 minutes while others are in the game (5 if saving is slow), and when the last one leaves. Unticked, only when the host saves.</t>
+          <t>Dump spares keeps what you hold and what is in your tool belt, like the hotbar. Unticked, it works as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>emp_ui_load_blocked</t>
+          <t>emp_ui_travel_no_date</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>みんなで遊んでいる間は、セーブをロードできません。</t>
+          <t>仲間は別の場所にいます。あなたの旅では日付は進みません。</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>You can't load a save while players are together.</t>
+          <t>Your friends are elsewhere. Your trip doesn't move the date.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>emp_ui_depot_join_btn</t>
+          <t>emp_ui_bill_paid</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>{0} に参加</t>
+          <t>{0}が請求書を支払いました：{1}（{2}）</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Join {0}</t>
+          <t>{0} paid a bill: {1} ({2})</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>emp_ui_depot_join_fail</t>
+          <t>emp_ui_bill_already_paid</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>{0} が世界を持っていますが、そのゲームはまだ開いていません。少し待ってからもう一度試してください。ゲームが止まっていたら、3分以内に世界は空きます。</t>
+          <t>この請求書はもう払われています。お金は引かれていません。</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>{0} has the world, but their game is not open yet. Try again in a moment. If their game stopped, the world is free again within 3 minutes.</t>
+          <t>This bill is already paid. Nothing was taken from you.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>emp_ui_box_far</t>
+          <t>emp_ui_sleep_alone</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>この箱は世界全体のもので、ホストが預かっています。ホストから離れていても入れた物はホストに届きますが、ホストのマップに戻るまで表示されません。</t>
+          <t>あなたは眠りました。世界は進みません：{0} がまだ起きています。</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>This chest belongs to the whole world and the host keeps it. If you are away from the host, what you put in still arrives, but you only see it again back on the host's map.</t>
+          <t>You slept. The world did not move on, as {0} is still awake.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_own_sleep</t>
+          <t>emp_ui_sleep_count</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>各自で眠る</t>
+          <t>{0} は眠っている（{1}/{2}）</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Everyone sleeps on their own</t>
+          <t>{0} is asleep ({1} of {2})</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_own_sleep</t>
+          <t>emp_ui_sleep_all</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>ベッドに入ったプレイヤーはすぐ眠れます。夜が明けるのは、全員が同時に眠っているときだけです。オフ：全員が揃うまで待ちます。</t>
+          <t>全員が眠りました。夜が明けます。</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>A player in bed sleeps at once. The night passes only when everyone sleeps at the same time. Unticked, everyone waits for everyone.</t>
+          <t>Everyone is asleep. The night passes.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_time_jumps_together</t>
+          <t>emp_ui_resync</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>全員一緒のときだけ時間が進む</t>
+          <t>マップを整えています…</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Time moves only when all travel together</t>
+          <t>Fixing the map…</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_time_jumps_together</t>
+          <t>emp_ui_sv_cfg_auto_resync</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ワールドマップの一歩で日付が進むのは、全員が一緒に旅しているときだけです。そうでなければ旅人だけがターンを消費します。オフ：誰かの一歩ごとに全員が3時間進みます。</t>
+          <t>マップを自動で直す</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>On the world map, the date moves only when all players travel together. Otherwise only the traveller's turns pass. Unticked, every step by anyone adds 3 hours for all.</t>
+          <t>Fix the map automatically</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_dump_spares_belt</t>
+          <t>emp_ui_sv_desc_auto_resync</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>自動整理で手持ちとツールベルトを残す</t>
+          <t>マップがホストと食い違う（物やキャラが足りない）と、自動で読み込み直します。30秒に1回まで。オフ：違いはログに書くだけ。</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Auto-dump leaves your hands and tool belt alone</t>
+          <t>If a player's map differs from the host's, with an item or character missing, it loads again by itself, at most every 30 seconds. Unticked, the difference is only logged.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_dump_spares_belt</t>
+          <t>emp_ui_bank_deposit</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>手に持っている物とツールベルトの中身は、ホットバーと同じように、まとめて入れても残ります。オフ：元のゲームと同じ。</t>
+          <t>{0}が銀行に{1}を預けました</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Dump spares keeps what you hold and what is in your tool belt, like the hotbar. Unticked, it works as in the base game.</t>
+          <t>{0} put {1} in the bank</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>emp_ui_travel_no_date</t>
+          <t>emp_ui_bank_withdraw</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>仲間は別の場所にいます。あなたの旅では日付は進みません。</t>
+          <t>{0}が銀行から{1}を引き出しました</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Your friends are elsewhere. Your trip doesn't move the date.</t>
+          <t>{0} took {1} out of the bank</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>emp_ui_bill_paid</t>
+          <t>emp_ui_sv_cfg_world_copy</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>{0}が請求書を支払いました：{1}（{2}）</t>
+          <t>ほかのプレイヤーも世界のコピーを持つ</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>{0} paid a bill: {1} ({2})</t>
+          <t>Other players keep a copy of the world</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>emp_ui_bill_already_paid</t>
+          <t>emp_ui_sv_desc_world_copy</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>この請求書はもう払われています。お金は引かれていません。</t>
+          <t>自動セーブのたびに、全員のPCが自分のセーブとは別に世界のコピーを保管します。オフ：世界はホストのPCにしかありません。</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>This bill is already paid. Nothing was taken from you.</t>
+          <t>After each automatic save, every player's PC keeps a copy of the world, apart from their own saves. Unticked, only the host's PC has it.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_alone</t>
+          <t>emp_ui_sv_cfg_shared_tax</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>あなたは眠りました。世界は進みません：{0} がまだ起きています。</t>
+          <t>税金は最も有名なプレイヤーで計算</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>You slept. The world did not move on, as {0} is still awake.</t>
+          <t>Tax follows the most famous player</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_count</t>
+          <t>emp_ui_sv_desc_shared_tax</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>{0} は眠っている（{1}/{2}）</t>
+          <t>毎月の税金は、接続中のプレイヤーでいちばん高い名声で計算します。オフ：ホストの名声で計算（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>{0} is asleep ({1} of {2})</t>
+          <t>Monthly tax uses the highest fame among the players. Unticked, it uses the host's fame, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>emp_ui_sleep_all</t>
+          <t>emp_ui_sv_cfg_soft_recall</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>全員が眠りました。夜が明けます。</t>
+          <t>合流のとき世界を読み込み直さない</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Everyone is asleep. The night passes.</t>
+          <t>Rejoin without reloading the world</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>emp_ui_resync</t>
+          <t>emp_ui_sv_desc_soft_recall</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>マップを整えています…</t>
+          <t>ホストとプレイヤーが同じマップになるとき、世界全体は読み込み直さず、そのまま、またはそのマップだけを読み込みます。合わないときは従来どおり読み込み直します。オフ：毎回読み込み直します。</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Fixing the map…</t>
+          <t>When the host and a player meet on one map, the whole world does not reload. Only that map loads, or nothing. If something doesn't match, the world reloads as before. Unticked, it always reloads.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_resync</t>
+          <t>emp_ui_sv_cfg_publish_mods</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>マップを自動で直す</t>
+          <t>ゲームのMOD一覧をプレイヤーに見せる</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Fix the map automatically</t>
+          <t>Show the game's mods to players</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_resync</t>
+          <t>emp_ui_sv_desc_publish_mods</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>マップがホストと食い違う（物やキャラが足りない）と、自動で読み込み直します。30秒に1回まで。オフ：違いはログに書くだけ。</t>
+          <t>参加前（ゲーム一覧）と参加時にMOD一覧が分かり、断られたときは違うMODが名前で表示されます。デポから取った世界では、デポの一覧（modlist.txt）を使います。オフ：何も伝えません。</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>If a player's map differs from the host's, with an item or character missing, it loads again by itself, at most every 30 seconds. Unticked, the difference is only logged.</t>
+          <t>Players see the mod list before joining and when joining. If refused, they are told which mods differ. For a world from a depot, the depot's list (modlist.txt) is used. Unticked, nothing is shown.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>emp_ui_bank_deposit</t>
+          <t>emp_ui_cl_fetch_mods</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>{0}が銀行に{1}を預けました</t>
+          <t>ゲームのMODをダウンロードする</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>{0} put {1} in the bank</t>
+          <t>Download the game's mods</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>emp_ui_bank_withdraw</t>
+          <t>emp_ui_cl_desc_fetch_mods</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>{0}が銀行から{1}を引き出しました</t>
+          <t>参加するゲームのMODで足りない Workshop のものを、購読せずにダウンロードします。Elin は一度再起動し、自動でゲームに戻ります。MOD一覧は次の起動で元に戻ります。オフ：違うMODを知らせるだけ。</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>{0} took {1} out of the bank</t>
+          <t>Missing Workshop mods of the game you join are downloaded without subscribing. Elin restarts once with those mods and comes back by itself. Your own list returns at the next start. Unticked, you are only told which mods differ.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_world_copy</t>
+          <t>emp_ui_mods_lobby</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>ほかのプレイヤーも世界のコピーを持つ</t>
+          <t>Mod {0} 個</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Other players keep a copy of the world</t>
+          <t>{0} mods</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_world_copy</t>
+          <t>emp_ui_mods_lobby_missing</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>自動セーブのたびに、全員のPCが自分のセーブとは別に世界のコピーを保管します。オフ：世界はホストのPCにしかありません。</t>
+          <t>{0} 個のMOD（{1} 個が足りません）</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>After each automatic save, every player's PC keeps a copy of the world, apart from their own saves. Unticked, only the host's PC has it.</t>
+          <t>{0} mods, {1} missing</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_shared_tax</t>
+          <t>emp_ui_mods_world</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>税金は最も有名なプレイヤーで計算</t>
+          <t>この世界のMODのうち {0} 個が読み込まれていません：{1}。一覧はログにあります。</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Tax follows the most famous player</t>
+          <t>{0} mods of this world are not loaded: {1}. The full list is in the log.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_shared_tax</t>
+          <t>emp_ui_mods_missing</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>毎月の税金は、接続中のプレイヤーでいちばん高い名声で計算します。オフ：ホストの名声で計算（元のゲームと同じ）。</t>
+          <t>ホストのMODで足りないもの（{0}）：{1}</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Monthly tax uses the highest fame among the players. Unticked, it uses the host's fame, as in the base game.</t>
+          <t>Host mods you don't have ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_soft_recall</t>
+          <t>emp_ui_mods_hand</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>合流のとき世界を読み込み直さない</t>
+          <t>手動で入れるMOD（{0}）：{1}</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Rejoin without reloading the world</t>
+          <t>Mods to install yourself ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_soft_recall</t>
+          <t>emp_ui_mods_extra</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ホストとプレイヤーが同じマップになるとき、世界全体は読み込み直さず、そのまま、またはそのマップだけを読み込みます。合わないときは従来どおり読み込み直します。オフ：毎回読み込み直します。</t>
+          <t>ホストにないMOD（{0}）：{1}</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>When the host and a player meet on one map, the whole world does not reload. Only that map loads, or nothing. If something doesn't match, the world reloads as before. Unticked, it always reloads.</t>
+          <t>Mods the host doesn't have ({0}): {1}</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_publish_mods</t>
+          <t>emp_ui_mods_fetching</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ゲームのMOD一覧をプレイヤーに見せる</t>
+          <t>ゲームのMODをダウンロード中 {0}/{1}：{2} {3}%（Escで中止）</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Show the game's mods to players</t>
+          <t>Downloading the game's mods {0}/{1}: {2} {3}% (Esc to cancel)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_publish_mods</t>
+          <t>emp_ui_mods_fetch_failed</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>参加前（ゲーム一覧）と参加時にMOD一覧が分かり、断られたときは違うMODが名前で表示されます。デポから取った世界では、デポの一覧（modlist.txt）を使います。オフ：何も伝えません。</t>
+          <t>ゲームのMODをダウンロードできませんでした。何も変更していません。</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Players see the mod list before joining and when joining. If refused, they are told which mods differ. For a world from a depot, the depot's list (modlist.txt) is used. Unticked, nothing is shown.</t>
+          <t>Could not download the mods. Nothing was changed.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>emp_ui_cl_fetch_mods</t>
+          <t>emp_ui_mods_restart</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ゲームのMODをダウンロードする</t>
+          <t>Elin はゲームのMODで再起動し、自動でゲームに戻ります。起動しないときは、Elin をもう一度起動してください。</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Download the game's mods</t>
+          <t>Elin restarts with the game's mods and comes back by itself. If it doesn't start, start Elin again.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_fetch_mods</t>
+          <t>emp_ui_mods_restart_manual</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>参加するゲームのMODで足りない Workshop のものを、購読せずにダウンロードします。Elin は一度再起動し、自動でゲームに戻ります。MOD一覧は次の起動で元に戻ります。オフ：違うMODを知らせるだけ。</t>
+          <t>Elin を閉じます。もう一度起動すると、ゲームのMODで自動でゲームに戻ります。</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Missing Workshop mods of the game you join are downloaded without subscribing. Elin restarts once with those mods and comes back by itself. Your own list returns at the next start. Unticked, you are only told which mods differ.</t>
+          <t>Elin closes. Start it again and it comes back to the game by itself, with its mods.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>emp_ui_mods_lobby</t>
+          <t>emp_ui_mods_session</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Mod {0} 個</t>
+          <t>今回の Elin は、マルチプレイのMODで動いています。MOD一覧は次の起動で元に戻ります。次回の再起動を省くには、クライアント設定の「ゲームのMODを残す」にチェックしてください。</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>{0} mods</t>
+          <t>This time Elin runs with the game's mods. Your own list returns at the next start. To skip this restart next time, tick "Keep the game's mods" in Client Settings.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>emp_ui_mods_lobby_missing</t>
+          <t>emp_ui_mods_session_locked</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>{0} 個のMOD（{1} 個が足りません）</t>
+          <t>今回はMOD一覧を保存しません。次の起動で元の一覧に戻ります。</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>{0} mods, {1} missing</t>
+          <t>The mod list is not saved this time. Yours returns at the next start of Elin.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>emp_ui_mods_world</t>
+          <t>emp_ui_cl_keep_mods</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>この世界のMODのうち {0} 個が読み込まれていません：{1}。一覧はログにあります。</t>
+          <t>ゲームのMODを残す（Workshop で購読）</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>{0} mods of this world are not loaded: {1}. The full list is in the log.</t>
+          <t>Keep the game's mods (subscribe on the Workshop)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>emp_ui_mods_missing</t>
+          <t>emp_ui_cl_desc_keep_mods</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>ホストのMODで足りないもの（{0}）：{1}</t>
+          <t>参加するゲームのMODを Steam アカウントで購読し、自分のMOD一覧に残します。最初の一度だけ再起動し、以降は Elin を閉じても再起動なしで同じゲームに入れます。取り消すには Workshop で購読を解除します。オフ：購読せず取得し、起動後の最初の参加で毎回再起動します。</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Host mods you don't have ({0}): {1}</t>
+          <t>Your Steam account subscribes to the mods of the game you join and keeps them on. Elin restarts once, the first time. After that you rejoin the same game with no restart. To undo, unsubscribe on the Workshop. Unticked, Elin restarts at the first join of every start.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>emp_ui_mods_hand</t>
+          <t>emp_ui_sv_cfg_takeover</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>手動で入れるMOD（{0}）：{1}</t>
+          <t>ホストが抜けたら別のプレイヤーが引き継ぐ</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Mods to install yourself ({0}): {1}</t>
+          <t>Another player takes over when the host leaves</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>emp_ui_mods_extra</t>
+          <t>emp_ui_sv_desc_takeover</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>ホストにないMOD（{0}）：{1}</t>
+          <t>ホストが抜けると、プレイヤーのひとりが自分のコピーから世界を開き、そこでゲームが続きます（「世界のコピー」が必要）。オフ：ホストが抜けるとゲームは終わります。</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Mods the host doesn't have ({0}): {1}</t>
+          <t>When the host leaves, a player opens the world from their copy and the game goes on. Needs the world copy option. Unticked, the game ends with the host.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>emp_ui_mods_fetching</t>
+          <t>emp_takeover_begin</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>ゲームのMODをダウンロード中 {0}/{1}：{2} {3}%（Escで中止）</t>
+          <t>ホストが抜けました。あなたが世界を引き継ぎます。まもなくここでゲームが続きます。</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Downloading the game's mods {0}/{1}: {2} {3}% (Esc to cancel)</t>
+          <t>The host left. You take over the world. The game goes on here in a moment.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>emp_ui_mods_fetch_failed</t>
+          <t>emp_takeover_leaving</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>ゲームのMODをダウンロードできませんでした。何も変更していません。</t>
+          <t>退出中：ほかのプレイヤーに最後のセーブを渡しています…</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Could not download the mods. Nothing was changed.</t>
+          <t>Leaving. Giving the last save to the others…</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>emp_ui_mods_restart</t>
+          <t>emp_ui_limited_bought</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Elin はゲームのMODで再起動し、自動でゲームに戻ります。起動しないときは、Elin をもう一度起動してください。</t>
+          <t>それはもう買いました。</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Elin restarts with the game's mods and comes back by itself. If it doesn't start, start Elin again.</t>
+          <t>You already bought this one.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>emp_ui_mods_restart_manual</t>
+          <t>emp_story_share</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Elin を閉じます。もう一度起動すると、ゲームのMODで自動でゲームに戻ります。</t>
+          <t>{0}の分け前</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Elin closes. Start it again and it comes back to the game by itself, with its mods.</t>
+          <t>{0}'s share</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>emp_ui_mods_session</t>
+          <t>emp_ui_sv_cfg_once_per_player</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>今回の Elin は、マルチプレイのMODで動いています。MOD一覧は次の起動で元に戻ります。次回の再起動を省くには、クライアント設定の「ゲームのMODを残す」にチェックしてください。</t>
+          <t>一度きりの報酬をプレイヤーごとに</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>This time Elin runs with the game's mods. Your own list returns at the next start. To skip this restart next time, tick "Keep the game's mods" in Client Settings.</t>
+          <t>One-time rewards for every player</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>emp_ui_mods_session_locked</t>
+          <t>emp_ui_sv_desc_once_per_player</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>今回はMOD一覧を保存しません。次の起動で元の一覧に戻ります。</t>
+          <t>店の限定品と、ストーリーでもらえる物（依頼の報酬、会話の贈り物）が、プレイヤーごとに1回ずつ手に入ります。オフ：最初のひとりだけ（元のゲームと同じ）。</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>The mod list is not saved this time. Yours returns at the next start of Elin.</t>
+          <t>One-time shop goods and story gifts, like quest rewards, go once to each player. Unticked, only the first player gets them, as in the base game.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>emp_ui_cl_keep_mods</t>
+          <t>emp_takeover_rejoin</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>ゲームのMODを残す（Workshop で購読）</t>
+          <t>別のプレイヤーがこの世界を引き継ぎました。そのゲームに参加します…</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Keep the game's mods (subscribe on the Workshop)</t>
+          <t>Another player took over this world. Joining them…</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>emp_ui_cl_desc_keep_mods</t>
+          <t>emp_story_share_got</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>参加するゲームのMODを Steam アカウントで購読し、自分のMOD一覧に残します。最初の一度だけ再起動し、以降は Elin を閉じても再起動なしで同じゲームに入れます。取り消すには Workshop で購読を解除します。オフ：購読せず取得し、起動後の最初の参加で毎回再起動します。</t>
+          <t>ストーリーでもらえた物のうち、あなたの分を受け取りました：{0}。</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Your Steam account subscribes to the mods of the game you join and keeps them on. Elin restarts once, the first time. After that you rejoin the same game with no restart. To undo, unsubscribe on the Workshop. Unticked, Elin restarts at the first join of every start.</t>
+          <t>You get your share of what the story gave: {0}.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_takeover</t>
+          <t>emp_story_share_mail</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ホストが抜けたら別のプレイヤーが引き継ぐ</t>
+          <t>ストーリーでもらえた物のうち、あなたの分（{0}）を拠点の郵便に送りました。</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Another player takes over when the host leaves</t>
+          <t>Your share of what the story gave ({0}) was sent to the base's mail.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_takeover</t>
+          <t>emp_ui_report</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>ホストが抜けると、プレイヤーのひとりが自分のコピーから世界を開き、そこでゲームが続きます（「世界のコピー」が必要）。オフ：ホストが抜けるとゲームは終わります。</t>
+          <t>不具合レポートを作成</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>When the host leaves, a player opens the world from their copy and the game goes on. Needs the world copy option. Unticked, the game ends with the host.</t>
+          <t>Prepare a bug report</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>emp_takeover_begin</t>
+          <t>emp_ui_report_desc</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ホストが抜けました。あなたが世界を引き継ぎます。まもなくここでゲームが続きます。</t>
+          <t>ゲームとMODのログをまとめた zip をデスクトップに作ります。セーブと設定ファイルは含みません。不具合を報告するときに送ってください。</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>The host left. You take over the world. The game goes on here in a moment.</t>
+          <t>Writes a zip with the game and mod logs on your desktop. No save, no settings. Send it when you report a problem.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>emp_takeover_leaving</t>
+          <t>emp_ui_report_done</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>退出中：ほかのプレイヤーに最後のセーブを渡しています…</t>
+          <t>レポートを作成しました：{0}</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Leaving. Giving the last save to the others…</t>
+          <t>Bug report written: {0}</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>emp_ui_limited_bought</t>
+          <t>emp_ui_report_failed</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>それはもう買いました。</t>
+          <t>レポートを作成できませんでした。</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>You already bought this one.</t>
+          <t>The bug report could not be written.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>emp_story_share</t>
+          <t>emp_ui_sv_bills</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>{0}の分け前</t>
+          <t>未払いの税金請求書：カウント {0}、実在 {1}（修復する）</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>{0}'s share</t>
+          <t>Unpaid tax bills: counted {0}, existing {1} (repair)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_once_per_player</t>
+          <t>emp_ui_sv_bills_desc</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>一度きりの報酬をプレイヤーごとに</t>
+          <t>カウントが実際の請求書より多いとき（古い不具合）、実際の数に合わせます。増やすことはありません。</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>One-time rewards for every player</t>
+          <t>If the count is above the bills that exist (an old bug), it is set to the real number. It is never raised.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_once_per_player</t>
+          <t>emp_ui_sv_bills_done</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>店の限定品と、ストーリーでもらえる物（依頼の報酬、会話の贈り物）が、プレイヤーごとに1回ずつ手に入ります。オフ：最初のひとりだけ（元のゲームと同じ）。</t>
+          <t>支払えない請求書 {0} 件をカウントから外しました。</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>One-time shop goods and story gifts, like quest rewards, go once to each player. Unticked, only the first player gets them, as in the base game.</t>
+          <t>{0} bill(s) that nothing could pay were taken off the count.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>emp_takeover_rejoin</t>
+          <t>emp_ui_sv_bills_none</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>別のプレイヤーがこの世界を引き継ぎました。そのゲームに参加します…</t>
+          <t>カウントは実在する請求書と一致しています。</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Another player took over this world. Joining them…</t>
+          <t>The count matches the bills that exist.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>emp_story_share_got</t>
+          <t>emp_ui_chara_delete</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ストーリーでもらえた物のうち、あなたの分を受け取りました：{0}。</t>
+          <t>キャラクターを削除する</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>You get your share of what the story gave: {0}.</t>
+          <t>Delete a character</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>emp_story_share_mail</t>
+          <t>emp_ui_chara_delete_confirm</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>ストーリーでもらえた物のうち、あなたの分（{0}）を拠点の郵便に送りました。</t>
+          <t>#1 を削除しますか？持ち物も一緒に消えます。仲間はこの世界に残ります。</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Your share of what the story gave ({0}) was sent to the base's mail.</t>
+          <t>Delete #1? Its belongings go with it. Its companions stay in this world.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>emp_ui_report</t>
+          <t>emp_ui_chara_deleted</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>不具合レポートを作成</t>
+          <t>キャラクターを削除しました。</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Prepare a bug report</t>
+          <t>The character was deleted.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>emp_ui_report_desc</t>
+          <t>emp_ui_sv_cfg_delete_chara</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>ゲームとMODのログをまとめた zip をデスクトップに作ります。セーブと設定ファイルは含みません。不具合を報告するときに送ってください。</t>
+          <t>プレイヤーが自分のキャラを削除できる</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Writes a zip with the game and mod logs on your desktop. No save, no settings. Send it when you report a problem.</t>
+          <t>Players can delete their characters</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>emp_ui_report_done</t>
+          <t>emp_ui_sv_desc_delete_chara</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>レポートを作成しました：{0}</t>
+          <t>キャラの一覧から削除します（確認は2回）。持ち物も消え、仲間は世界に残ります。</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Bug report written: {0}</t>
+          <t>Done from the character list, with two confirmations. Belongings go too. Companions stay in the world.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>emp_ui_report_failed</t>
+          <t>emp_world_setting_host</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>レポートを作成できませんでした。</t>
+          <t>世界の設定はホストのものです。変更は保存されませんでした。</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>The bug report could not be written.</t>
+          <t>World settings belong to the host. Your changes were not kept.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills</t>
+          <t>emp_ui_sv_cfg_auto_combat_per_player</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>未払いの税金請求書：カウント {0}、実在 {1}（修復する）</t>
+          <t>自動戦闘はそれぞれ自分の仲間を守る</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Unpaid tax bills: counted {0}, existing {1} (repair)</t>
+          <t>Each player's auto combat protects their own</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills_desc</t>
+          <t>emp_ui_sv_desc_auto_combat_per_player</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>カウントが実際の請求書より多いとき（古い不具合）、実際の数に合わせます。増やすことはありません。</t>
+          <t>自動戦闘を使うプレイヤーと仲間を、そのプレイヤー自身の戦術とスタミナで致命傷から守ります。オフ：ホストの自動戦闘が全員を守り、ゲストのは誰も守りません。</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>If the count is above the bills that exist (an old bug), it is set to the real number. It is never raised.</t>
+          <t>Auto combat saves the player using it, and their companions, from a deadly hit, with their own tactics and stamina. Unticked, the host's auto combat protects everyone and a guest's protects no one.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills_done</t>
+          <t>emp_duel_win</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>支払えない請求書 {0} 件をカウントから外しました。</t>
+          <t>{0}との決闘に勝った！</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>{0} bill(s) that nothing could pay were taken off the count.</t>
+          <t>You win the duel against {0}!</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>emp_ui_sv_bills_none</t>
+          <t>emp_duel_lose</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>カウントは実在する請求書と一致しています。</t>
+          <t>{0}との決闘に負けた。</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>The count matches the bills that exist.</t>
+          <t>You lose the duel against {0}.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>emp_ui_chara_delete</t>
+          <t>emp_duel_wait</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>キャラクターを削除する</t>
+          <t>まだ {0} に決闘を申し込めません。</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Delete a character</t>
+          <t>You can't challenge {0} again so soon.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>emp_ui_chara_delete_confirm</t>
+          <t>emp_trade_gold_button</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>#1 を削除しますか？持ち物も一緒に消えます。仲間はこの世界に残ります。</t>
+          <t>お金</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Delete #1? Its belongings go with it. Its companions stay in this world.</t>
+          <t>Gold</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>emp_ui_chara_deleted</t>
+          <t>emp_trade_locked</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>キャラクターを削除しました。</t>
+          <t>変更があったばかりだ。少し待ってから確定しよう。</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>The character was deleted.</t>
+          <t>The offer just changed. Wait a moment before validating.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_delete_chara</t>
+          <t>emp_trade_log_add</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>プレイヤーが自分のキャラを削除できる</t>
+          <t>{0}が{1}を差し出した。</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Players can delete their characters</t>
+          <t>{0} offers {1}.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_delete_chara</t>
+          <t>emp_trade_log_remove</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>キャラの一覧から削除します（確認は2回）。持ち物も消え、仲間は世界に残ります。</t>
+          <t>{0}が{1}を引っ込めた。</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Done from the character list, with two confirmations. Belongings go too. Companions stay in the world.</t>
+          <t>{0} takes back {1}.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>emp_world_setting_host</t>
+          <t>emp_trade_log_gold</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>世界の設定はホストのものです。変更は保存されませんでした。</t>
+          <t>{0}の提示額は{1}オレンになった。</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>World settings belong to the host. Your changes were not kept.</t>
+          <t>{0} now offers {1} gold.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>emp_ui_sv_cfg_auto_combat_per_player</t>
+          <t>emp_trade_cant_offer</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>自動戦闘はそれぞれ自分の仲間を守る</t>
+          <t>{0}は差し出せない。</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Each player's auto combat protects their own</t>
+          <t>You can't offer {0}.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>emp_ui_sv_desc_auto_combat_per_player</t>
+          <t>emp_trade_status</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>自動戦闘を使うプレイヤーと仲間を、そのプレイヤー自身の戦術とスタミナで致命傷から守ります。オフ：ホストの自動戦闘が全員を守り、ゲストのは誰も守りません。</t>
+          <t>{0}: {1}オレン、{2}</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
-        <is>
-          <t>Auto combat saves the player using it, and their companions, from a deadly hit, with their own tactics and stamina. Unticked, the host's auto combat protects everyone and a guest's protects no one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>emp_duel_win</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>{0}との決闘に勝った！</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>You win the duel against {0}!</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>emp_duel_lose</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>{0}との決闘に負けた。</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>You lose the duel against {0}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>emp_duel_wait</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>まだ {0} に決闘を申し込めません。</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>You can't challenge {0} again so soon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>emp_trade_gold_button</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>お金</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>emp_trade_locked</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>変更があったばかりだ。少し待ってから確定しよう。</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>The offer just changed. Wait a moment before validating.</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>emp_trade_log_add</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>{0}が{1}を差し出した。</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>{0} offers {1}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>emp_trade_log_remove</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>{0}が{1}を引っ込めた。</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>{0} takes back {1}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>emp_trade_log_gold</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>{0}の提示額は{1}オレンになった。</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>{0} now offers {1} gold.</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>emp_trade_cant_offer</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>{0}は差し出せない。</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>You can't offer {0}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>emp_trade_status</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>{0}: {1}オレン、{2}</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
         <is>
           <t>{0}: {1} gold, {2}</t>
         </is>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5787,40 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_town_life</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>全プレイヤーの周りで町の人が暮らす</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Town life around every player</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_town_life</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>町の人は、ホストの画面の近くだけでなく、すべてのプレイヤーの近くで雑談し、あいさつし、噂し、石を投げます。噂と石は、その相手のプレイヤー自身のカルマで決まります。オフにすると、ホストの近くだけで、ホストのカルマで決まります（バニラと同じ）。</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Townspeople chat, greet, gossip and throw stones near every player, not only near the host's screen. Gossip and stones go by the karma of the player they are about. Unticked: only near the host, by the host's karma (as in vanilla).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5787,40 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_town_boards</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>町の掲示板を全員の分で作る</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Town boards from every player present</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_town_boards</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ゲームが町の掲示板の依頼を引き直すとき、マップにいる全員の中で最も高い名声が名声が必要な依頼を開き、難易度は在場のプレイヤーの平均になります。オフの場合はホストのキャラだけで決まります（原作どおり）。</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>When the game draws a town board's offers again, the highest fame among the players on the map opens the offers that need fame, and the difficulty follows the players present. Unticked, the board is drawn for the host's character alone (as in the base game).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5787,40 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_nearest_spawns</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>スポーンはいちばん近いプレイヤーから</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Spawns from the nearest player</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_nearest_spawns</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>マップのスポーン（伝説の個体の確率、サンタなどの敵味方、進化個体、ビッグダディ、祠）は、ホストではなくスポーン地点にいちばん近いプレイヤーの特性で決まります。オフならホストの特性（元のゲームと同じ）。</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>What a map spawns (legendary chance, friend or foe of Santa and the like, evolved, big daddy, shrines) reads the feats of the player nearest to the spawn, not always the host's. Unticked: the host's, as in the game.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5787,40 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_shops_from_every_player</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>全員の進行に合わせた店</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Shops from every player present</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_shops_from_every_player</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>店の仕入れ量は地図上で最も強いプレイヤーの特性で決まり、特別な棚（結婚とカセットの店、ロイテルのマート、異国の商人）は店を開いたプレイヤーの進行に従います。オフの場合は常にホストの進行（原作と同じ）。</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>A shop restocks with the stock bonus of the best player on the map, and its special shelves (marriage and tape shop, Loytel's mart, exotic merchant) follow the player who opens it. Off: always the host's progress, as the game does.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -5846,12 +5846,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ゲームが町の掲示板の依頼を引き直すとき、マップにいる全員の中で最も高い名声が名声が必要な依頼を開き、難易度は在場のプレイヤーの平均になります。オフの場合はホストのキャラだけで決まります（原作どおり）。</t>
+          <t>ゲームが町の掲示板の依頼を引き直すとき、マップにいる全員の中で最も高い名声が名声が必要な依頼を開き、難易度は在場のプレイヤーの平均になります。オフの場合はホストのキャラだけで決まります（原作どおり）。（個人クエストが有効な場合のみ。）</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>When the game draws a town board's offers again, the highest fame among the players on the map opens the offers that need fame, and the difficulty follows the players present. Unticked, the board is drawn for the host's character alone (as in the base game).</t>
+          <t>When the game draws a town board's offers again, the highest fame among the players on the map opens the offers that need fame, and the difficulty follows the players present. Unticked, the board is drawn for the host's character alone (as in the base game). Needs personal quests.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5787,40 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_enforce_ownership</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>他人のキャラクターへの操作を拒否</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Refuse acts on others' characters</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_enforce_ownership</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>ゲストのゲームが、自分のキャラクターでも仲間でもないキャラクターについて送ってきたもの（作業、ダメージ、スキル、パーティ）を拒否する。オフのときはログに書くだけ。取引、他のプレイヤーへの贈り物、自分の仲間への命令は拒否されない。</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>What a guest's game sends about a character that is neither its own nor one of its companions (its task, its damage, its skills, its party) is refused. Unchecked, it is only written to the log. A trade, a gift to another player or an order to one's own companion is never refused.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5787,40 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_activities_from_actor</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>樽と母乳はそのプレイヤーのもの</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Barrels and milk follow the player</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_activities_from_actor</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>オン：樽で醸造された酒は樽に一番近いプレイヤーの技能で作られ、母乳を飲んだ幼いペットは飼い主の調教で育ち、飼い主が経験を得る。オフ：ホストのキャラクターによる（一人で遊ぶ時と同じ）</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>On: what a barrel brews is made with the skills of the player nearest to it, and a baby pet drinking its mother's milk grows by its owner's taming, and its owner learns from it. Off: both follow the host's character, as for a player alone</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5787,6 +5787,74 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_summons_follow_master</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>召喚物は召喚者についていく</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Summons follow their summoner</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_summons_follow_master</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>プレイヤーが召喚したものは、ホストと一緒でも単独でも、そのプレイヤーが行く所へ行く。オフ：ホストがマップを離れると他のプレイヤーの召喚物は消える</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>What a player summoned goes where that player goes, with the host or on its own. Off: the summons of the others vanish when the host leaves the map</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_players_at_base</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>拠点はすべてのプレイヤーを数える</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>The base counts every player</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_players_at_base</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>拠点のマップにいる誰かが起きていれば襲撃が来る。幸運の月は誰か一人の神に従う。プレイヤーと過ごした日数はプレイヤーのいる所で数える。オフ：拠点のマップを動かすゲームのプレイヤーだけ</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Raids come while any player on the base map is awake, the lucky month follows the god of any of them, days with a player count wherever a player is. Off: only the player whose game runs the base map</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D330"/>
+  <dimension ref="A1:D335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6059,6 +6059,91 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_world_map_time</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>ワールドマップの時間：{0}</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>World map time: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_world_map_time</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>クリックで切り替え。共有時計：ワールドマップも他のマップと同じで、誰の一歩でも日付が進む。他のプレイヤーは時間に追いつくが、満腹度もクエストの時間も失わない（戦闘中・読み込み中・会話中は最大60秒待つ）。一緒に旅：全員がワールドマップにいる時だけ、誰の一歩でも日付が進む。そうでなければ旅人は自分のターンだけを払い、日付は進まない。</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Click to change. Shared clock: the world map is a map like any other, every step of anyone moves the date; the others catch up without losing hunger or quest time (waiting up to 60 s while they fight, load or talk). Travel together: a step moves the date only while all the players are on the world map, whoever steps; otherwise the traveller pays its own turns and the date stays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_wmt_SharedClock</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>共有時計</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Shared clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_wmt_TravelTogether</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>一緒に旅</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Travel together</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>emp_ui_travel_bystander</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>{0}が{1}時間旅をした。世界は進んだが、あなたは何も失っていない。</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>{0} travelled {1} h. The world moved on; you lost nothing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D335"/>
+  <dimension ref="A1:D381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -952,12 +952,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>平均速度を共有</t>
+          <t>全員が平均速度で動く</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Shared Average Speed</t>
+          <t>Everyone moves at the average speed</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ターン制戦闘</t>
+          <t>戦闘ではプレイヤーが順番に行動する</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Turn-Based Combat</t>
+          <t>Players take turns in a fight</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>サーバー設定</t>
+          <t>ワールドのルール</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Server Setting</t>
+          <t>World rules</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2115,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>単独行動を許可</t>
+          <t>プレイヤーは一人で旅ができる</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Allow travelling alone</t>
+          <t>Players can travel alone</t>
         </is>
       </c>
     </row>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>参加時にキャラを選ぶ</t>
+          <t>友人は参加時にキャラクターを選ぶ</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Choose a character when joining</t>
+          <t>Friends choose a character when they join</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>プレイヤー同士の取引</t>
+          <t>プレイヤー同士で取引できる</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Trade between players</t>
+          <t>Players can trade</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>戦闘中、プレイヤーは順番に動きます。「戦闘はプレイヤーごとの時間で」がオンのときは無効です。</t>
+          <t>戦闘中、プレイヤーは順番に行動します。各自のペースの戦闘がオンの間は何もしません。</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>In a fight, players take turns. Does nothing while "Combat at each player's pace" is ticked.</t>
+          <t>In a fight, players take turns. Does nothing while combat at each player's pace is on.</t>
         </is>
       </c>
     </row>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>参加するプレイヤーのゲームが、ホストと同じであるべきもの。「なし」：誰でも。「すべて」：データとMODが同じ。</t>
+          <t>参加するプレイヤーのゲームがあなたと同じでなければならないもの。「なし」：誰でも。「すべて」：同じデータとMOD。「なし」と「すべて」は単独で選びます。</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods.</t>
+          <t>What a joining player's game must share with yours. None: anyone. All: same data and mods. None and All stand alone.</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ゲストも、ホストと同じなめらかさで動けます。上の項目がオンのときに使えます。</t>
+          <t>友人もホストと同じように滑らかに動きます。各自のペースの戦闘が必要です。</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Guests move as smoothly as the host. Needs the option above.</t>
+          <t>Friends move as smoothly as the host. Needs combat at each player's pace.</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>自分のセーブのキャラを連れてこられる</t>
+          <t>友人は自分のセーブからキャラクターを連れてこられる</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Players can bring a character from their saves</t>
+          <t>Friends can bring a character from their own saves</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>時間の影響を一度だけ起こす</t>
+          <t>天気、税、手紙はワールドで一度だけ起こる</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Time affects the world only once</t>
+          <t>Weather, taxes and letters happen once for the world</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>同じ Elin のバージョンを必須にする</t>
+          <t>友人も同じElinのバージョンが必要</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Require the same Elin version</t>
+          <t>Friends need the same Elin version</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>マップを自動で直す</t>
+          <t>ホストと違うマップは自動で読み込み直される</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Fix the map automatically</t>
+          <t>A map that differs from the host's loads again by itself</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>自動戦闘を使うプレイヤーと仲間を、そのプレイヤー自身の戦術とスタミナで致命傷から守ります。オフ：ホストの自動戦闘が全員を守り、ゲストのは誰も守りません。</t>
+          <t>自動戦闘は、使っているプレイヤーとその仲間を、自分の戦術とスタミナで致命的な一撃から守ります。オフのときは、ホストの自動戦闘が全員を守り、友人の自動戦闘は誰も守りません。</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Auto combat saves the player using it, and their companions, from a deadly hit, with their own tactics and stamina. Unticked, the host's auto combat protects everyone and a guest's protects no one.</t>
+          <t>Auto combat saves the player using it, and their companions, from a deadly hit, with their own tactics and stamina. Unticked, the host's auto combat protects everyone and a friend's protects no one.</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5931,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>他人のキャラクターへの操作を拒否</t>
+          <t>他人のキャラクターについての情報を拒否する</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Refuse acts on others' characters</t>
+          <t>Refuse what a player's game says about someone else's character</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>ゲストのゲームが、自分のキャラクターでも仲間でもないキャラクターについて送ってきたもの（作業、ダメージ、スキル、パーティ）を拒否する。オフのときはログに書くだけ。取引、他のプレイヤーへの贈り物、自分の仲間への命令は拒否されない。</t>
+          <t>自分のキャラクターでも自分の仲間でもないキャラクターについて、プレイヤーのゲームが送る情報（行動、ダメージ、スキル、パーティ）を拒否します。オフのときはログに書くだけです。取引、他のプレイヤーへの贈り物、自分の仲間への命令は拒否されません。</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>What a guest's game sends about a character that is neither its own nor one of its companions (its task, its damage, its skills, its party) is refused. Unchecked, it is only written to the log. A trade, a gift to another player or an order to one's own companion is never refused.</t>
+          <t>What a player's game sends about a character that is neither theirs nor one of their companions (its task, damage, skills, party) is refused. Unticked, it is only written to the log. A trade, a gift to another player or an order to one's own companion is never refused.</t>
         </is>
       </c>
     </row>
@@ -6141,6 +6141,788 @@
       <c r="D335" t="inlineStr">
         <is>
           <t>{0} travelled {1} h. The world moved on; you lost nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_joining</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>参加</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Joining</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_together</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>一緒に遊ぶ</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Playing together</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_host_leaves</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ホストが抜けたとき</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>When the host leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_fallbacks</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>従来のホスト中心のルール</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Classic host-led fallbacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_time_details</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>時間の詳細</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Time details</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_comfort</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>快適さ</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Comfort</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_repair</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>接続と修復</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Connection and repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_advanced</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>詳細な設定を表示</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Show advanced options</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_custom</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>カスタム（詳細な設定を参照）</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Custom (see Advanced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_apply_join</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>次に参加するプレイヤーから適用されます。</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Applies to players who join next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_apply_load</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>ワールドの読み込み時に適用されます。</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Applies when a world loads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_who_joins</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>参加できる人</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Who can join</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_who_joins</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>参加するために、友人のゲームがあなたのゲームと同じでなければならないもの。Elin Together のバージョンは常に一致が必要です。</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>What a friend's game must share with yours to join. The Elin Together version must always match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_who_joins_anyone</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>誰でも</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Anyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_who_joins_mods</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>同じMOD</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Same mods</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_who_joins_data</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>同じゲームデータ</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Same game data</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_who_joins_both</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>同じMODとゲームデータ</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Same mods and game data</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_world_map_choice</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>ワールドマップでの時間</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Time on the world map</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_world_map_choice</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>共有時計：ワールドマップで誰かが一歩進むたびに日付が進み、他の人は満腹度やクエストの時間を失わずに追いつきます。一緒に旅：全員がワールドマップにいるときだけ日付が進みます。</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Shared clock: every step of anyone on the world map moves the date; the others catch up without losing hunger or quest time. Travel together: the date moves only while all players are on the world map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_world_map_choice_SharedClock</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>共有時計</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Shared clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_world_map_choice_TravelTogether</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>一緒に旅</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Travel together</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_combat_pace</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>戦闘のペース</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Combat pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_combat_pace</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>各自のペース：モンスターは戦っているプレイヤーが行動したときに行動し、誰も待たず、全員がソロのように歩きます。ターン制：戦闘中はプレイヤーが順番に行動します。平均速度：全員が平均の速度で動きます。従来どおり：ホストのゲームと同じです。</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Own pace: a monster acts when the player it fights acts, nobody waits, everyone walks as in a solo game. Turn-based: players take turns in a fight. Shared average: everyone moves at the average speed. Classic: as the game runs for the host.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_combat_pace_own</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>各自のペース</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Each player's own pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_combat_pace_turns</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>ターン制</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Turn-based</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_combat_pace_average</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>全員の平均速度</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Shared average speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_combat_pace_classic</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>従来どおり</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Classic</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_own_everything</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>全員が自分のクエスト、店、報酬、町の暮らしを持つ</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Every player gets their own quests, shops, rewards and town life</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_own_everything</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>クエスト、名声、出荷のお金、一度きりの報酬、税、掲示板、店、出現、樽、自動戦闘、拠点、召喚がそれぞれのプレイヤーに従います。いいえ：基本のゲームと同じく、ホストのキャラクターに従います。個別の項目は詳細な設定にあります。</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Quests, fame, shipping money, one-time rewards, tax, town boards, shops, spawns, barrels, auto combat, the base and summons follow each player. No: they follow the host's character, as in the base game. Each one is in Advanced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_own_everything_yes</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_own_everything_no</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>いいえ、全員ホストのキャラクター基準</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>No, the host's character for all</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_building</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>建築と拠点</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Building and base</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_building</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>拠点で建築モードを使い、拠点を管理（研究、方針、名前、住人）できる人。友人は自分のお金と素材を払います。</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Who can use build mode in the base and manage it: research, policies, names, residents. Friends pay their own gold and materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_building_all</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>全員が建築と管理</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Everyone builds and manages</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_building_manage</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>全員が管理、建築はホストのみ</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Everyone manages, only the host builds</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_building_host</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>ホストのみ</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Only the host</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_fights</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>プレイヤー同士の戦い</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Fights between players</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_fights</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>決闘：相手のキャラクターのメニューから挑戦でき、誰も死にません。本当に倒す：プレイヤーの致命的な一撃で他のプレイヤーが死ぬことがあります。</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Duels: challenge another player from the menu on their character; nobody dies. Real kills: a deadly blow from a player can kill another player.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_fights_off</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_fights_duels</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>決闘のみ</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Duels only</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_fights_kills</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>決闘と本当に倒す</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Duels and real kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_host_leaves</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ホストが抜けたら</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>If the host leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_host_leaves</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>ワールドは待つ：ワールドはホストのPCだけにあります。友人がバックアップを持つ：自動保存のたびに、友人のPCにもコピーが残ります。他のプレイヤーが続ける：友人がそのコピーからワールドを開き、ゲームが続きます。</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>The world waits: it is on the host's PC only. Friends keep a backup: after each automatic save, every friend's PC keeps a copy. Another player carries on: a friend opens the world from that copy and the game goes on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_host_leaves_waits</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>ワールドは待つ</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>The world waits</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_host_leaves_backup</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>友人がバックアップを持つ</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Friends keep a backup</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_host_leaves_carry_on</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>他のプレイヤーが続ける</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Another player carries on</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D381"/>
+  <dimension ref="A1:D391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6926,6 +6926,176 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_sec_preset</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>一緒に遊ぶ方法</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>How you play together</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_preset</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>ルール</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_preset_recommended</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>おすすめの協力プレイ</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Recommended co-op</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_preset_classic</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>従来のホスト主導</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Classic host-led</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_preset_custom</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>カスタム</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_preset_recommended</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>全員が一人前のプレイヤーとして遊びます。自分のクエスト、店、報酬、自分のペースで。</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Everyone plays as a full player: their own quests, shops and rewards, at their own pace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_preset_classic</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>ホストが導きます。全員がホストについて行き、戦闘はターン制、建築と拠点はホストのみ、クエストや報酬はホストのキャラクター基準です。</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>The host leads: everyone follows the host, fights are turn-based, only the host builds and manages the base, quests and rewards go by the host's character.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_diff</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>おすすめとの違い {0} 件：{1}</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>{0} differences from recommended: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_reset</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>おすすめに戻す</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Reset to recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_undo</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>最後の変更を元に戻す</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Undo the last change</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D391"/>
+  <dimension ref="A1:D392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7096,6 +7096,23 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_more</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>その他の設定は Elin Together のウィンドウ（「ワールドのルール」タブ）にあります。</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>More options in the Elin Together window (World rules tab).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D392"/>
+  <dimension ref="A1:D398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7113,6 +7113,108 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_sec_controls</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_sec_mods</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>ワークショップのMOD</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Workshop mods</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_sec_depot</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>共有のセーブフォルダ（任意）</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Shared save folder (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_sec_help</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>ヘルプ</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_desc_ping</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>このキーを押すと、マップ上の場所を他のプレイヤーに知らせます。</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Press this key to show a spot on the map to the other players.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>emp_ui_cl_desc_depot</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ワールドを置いておく場所で、誰でもホストになれます。一緒に遊ぶだけなら必要ありません。</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Where the world is kept so that any of you can host it. Not needed to play together.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D398"/>
+  <dimension ref="A1:D405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7215,6 +7215,125 @@
         </is>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_title</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>このワールドのルール</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>This world's rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_note</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>ホストが決めたルールです。変更は全員に同時に適用されます。</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Set by the host. A change applies to everyone at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_line</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>{0}：{1}</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>{0}: {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_changed</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ホストが「{0}」を変更しました：{1} → {2}</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>The host changed "{0}": {1} -&gt; {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_yes</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_no</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>emp_ui_rules_custom</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>カスタム</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D405"/>
+  <dimension ref="A1:D414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>共有時計：ワールドマップで誰かが一歩進むたびに日付が進み、他の人は満腹度やクエストの時間を失わずに追いつきます。一緒に旅：全員がワールドマップにいるときだけ日付が進みます。</t>
+          <t>共有時計：ワールドマップで誰かが一歩進むたびに日付が進み、他の人は満腹度やクエストの時間を失わずに追いつきます。一緒に旅：全員がワールドマップにいるときだけ日付が進みます。自分のペース：共有時計と同じですが、仲間が別の場所にいる間に旅するプレイヤーは世界より先に進みます。その時間は本人の満腹度と自分のクエストが払い、日付は全員がワールドマップに揃うか同じ夜に眠るまで待ちます。</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Shared clock: every step of anyone on the world map moves the date; the others catch up without losing hunger or quest time. Travel together: the date moves only while all players are on the world map.</t>
+          <t>Shared clock: every step of anyone on the world map moves the date; the others catch up without losing hunger or quest time. Travel together: the date moves only while all players are on the world map. Personal pace: as the shared clock, but a player travelling while the others are elsewhere runs ahead of the world: its hunger and its own quests pay the hours, and the date waits until everyone is on the world map together or sleeps the same night.</t>
         </is>
       </c>
     </row>
@@ -7331,6 +7331,159 @@
       <c r="D405" t="inlineStr">
         <is>
           <t>Custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_world_map_choice_PersonalPace</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>自分のペース</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Personal pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_world_map_lead</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>一人旅で世界より先に進める時間（自分のペース）</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>How far a player travelling alone may run ahead (personal pace)</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_world_map_lead</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>自分のペース：この時間を超えると、一人旅の時間は共有時計と同じように全員の日付を進めます。</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Personal pace: past this lead, the hours of a player travelling alone move the date for everyone, as with the shared clock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_world_map_lead_12</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>12時間</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>12 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_world_map_lead_24</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>24時間</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>24 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_world_map_lead_48</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>48時間</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_opt_world_map_lead_72</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>72時間</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>72 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>emp_ui_travel_lead</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>あなたは世界より{0}時間先にいます（旅の時間は満腹度とクエストが払いました。日付は仲間を待っています）。</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>You are +{0} h ahead of the world (your hunger and your quests paid the trip; the date waits for your friends).</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>emp_ui_travel_lead_paid</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>世界があなたの旅に追いつきました。</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>The world caught up with your trip.</t>
         </is>
       </c>
     </row>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D414"/>
+  <dimension ref="A1:D416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7487,6 +7487,40 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_global_chat</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>全員にチャットを届ける</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Chat is read by every player</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_global_chat</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>プレイヤーが入力したチャットは、別のマップ、ワールドマップ、単独行動中など、どこにいる全員にも届きます。オフ：同じマップのプレイヤーにだけ届きます。住民やゲームのセリフは常にそのマップだけです</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>What a player types in the chat is read by every player, wherever they are: on another map, on the world map, away on their own. Off: only the players on the same map as the speaker read it. Lines of townspeople and the game stay on their map either way</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D416"/>
+  <dimension ref="A1:D424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7521,6 +7521,142 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>emp_act_follow</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>ついていく</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Follow</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>emp_follow_start</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>#1についていく。何かキーを押すと止まる。</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>You follow #1. Press any key to stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>emp_follow_stop</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>#1についていくのをやめた。</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>You stop following #1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>emp_follow_left</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>#1はこのマップを離れた。ついていくのをやめた。</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>#1 left the map. You stop following.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>emp_follow_lost</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>#1を見失った。</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>You lost sight of #1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>emp_follow_danger</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>危険だ。ついていくのをやめた。</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Danger! You stop following.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_follow</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>ほかのプレイヤーについていける</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Players can follow each other</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_follow</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>ほかのプレイヤーをクリックして「ついていく」を選ぶと、同じマップの中で自動で後を歩きます。キー、攻撃、敵、相手のマップ移動で止まります。</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Click another player and choose Follow: your character walks after it on the same map. A key, a blow, a monster in sight or the other player leaving the map stops it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/package/LangMod/EN/emp_localization.xlsx
+++ b/package/LangMod/EN/emp_localization.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D424"/>
+  <dimension ref="A1:D434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7657,6 +7657,176 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>emp_people_players</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>プレイヤー</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Players</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>emp_people_offline</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>オフライン</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>emp_act_talk</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>話す</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>emp_whisper_with</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>#1との内緒話</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Private chat with #1</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>emp_whisper_offline</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>#1は接続していない。</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>#1 is not connected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>emp_whisper_from</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>#1（内緒話）</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>#1 (private)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>emp_whisper_to</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>#1へ</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>To #1</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>emp_whisper_you</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>あなた</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>You</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_cfg_private_chat</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>内緒話</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Private chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>emp_ui_sv_desc_private_chat</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>他のプレイヤーのキャラに「話す」と、そのプレイヤーとの内緒話が開く。そのプレイヤーにだけ届く</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Talk on another player's character opens a private chat with that player. Only that player gets the lines, wherever they are</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
